--- a/Lakshmi.xlsx
+++ b/Lakshmi.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H452"/>
+  <dimension ref="A1:H564"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="24.33203125" customWidth="1" style="1" min="1" max="1"/>
@@ -14037,6 +14037,2694 @@
       </c>
       <c r="F452" t="n">
         <v>676</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-01-27 10:35:03</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>NIFTY2620324650PE</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="D453" t="n">
+        <v>100.55</v>
+      </c>
+      <c r="E453" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F453" t="n">
+        <v>-6864</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-01-27 10:40:17</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>NIFTY2620324650PE</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="D454" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="E454" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F454" t="n">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-01-27 10:41:47</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>NIFTY2620324650PE</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="D455" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="E455" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F455" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-01-27 10:46:56</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>NIFTY2620325600CE</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="D456" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="E456" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F456" t="n">
+        <v>-208</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-01-27 11:02:54</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>NIFTY2620325600CE</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="D457" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="E457" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F457" t="n">
+        <v>-208</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-01-27 11:04:41</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>NIFTY2620325550CE</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="D458" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="E458" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F458" t="n">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-01-27 11:08:10</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>NIFTY2620325550CE</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="D459" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="E459" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F459" t="n">
+        <v>-1508</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-01-27 11:09:40</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>NIFTY2620325550CE</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="D460" t="n">
+        <v>118</v>
+      </c>
+      <c r="E460" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F460" t="n">
+        <v>4940</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-01-27 11:12:42</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>NIFTY2620325650CE</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="D461" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="E461" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F461" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-01-28 11:35:54</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>105.95</v>
+      </c>
+      <c r="D462" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="E462" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F462" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-01-28 11:38:19</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="D463" t="n">
+        <v>111.45</v>
+      </c>
+      <c r="E463" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F463" t="n">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-01-28 11:45:20</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>NIFTY2620325000PE</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="D464" t="n">
+        <v>104.2</v>
+      </c>
+      <c r="E464" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F464" t="n">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-01-28 11:52:02</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>NIFTY2620325650CE</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>100.2</v>
+      </c>
+      <c r="D465" t="n">
+        <v>100.8</v>
+      </c>
+      <c r="E465" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F465" t="n">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-01-28 12:01:36</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>NIFTY2620325650CE</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>100.15</v>
+      </c>
+      <c r="D466" t="n">
+        <v>101</v>
+      </c>
+      <c r="E466" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F466" t="n">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-01-28 12:07:12</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>NIFTY2620325650CE</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="D467" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="E467" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F467" t="n">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-01-28 12:15:48</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>NIFTY2620325600CE</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="D468" t="n">
+        <v>111</v>
+      </c>
+      <c r="E468" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F468" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-01-28 12:23:07</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>126.25</v>
+      </c>
+      <c r="D469" t="n">
+        <v>129</v>
+      </c>
+      <c r="E469" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F469" t="n">
+        <v>4468.75</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-01-28 12:24:47</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>130.15</v>
+      </c>
+      <c r="D470" t="n">
+        <v>131.9</v>
+      </c>
+      <c r="E470" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F470" t="n">
+        <v>2843.75</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-01-28 12:30:10</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="D471" t="n">
+        <v>120.55</v>
+      </c>
+      <c r="E471" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F471" t="n">
+        <v>-568.75</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-01-28 12:38:29</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="D472" t="n">
+        <v>132.75</v>
+      </c>
+      <c r="E472" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F472" t="n">
+        <v>406.25</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-01-28 12:40:09</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>133.9</v>
+      </c>
+      <c r="D473" t="n">
+        <v>134</v>
+      </c>
+      <c r="E473" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F473" t="n">
+        <v>162.5</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-01-28 12:45:17</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>128.05</v>
+      </c>
+      <c r="D474" t="n">
+        <v>129.1</v>
+      </c>
+      <c r="E474" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F474" t="n">
+        <v>1706.25</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-01-28 12:50:38</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="D475" t="n">
+        <v>122.9</v>
+      </c>
+      <c r="E475" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F475" t="n">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-01-28 12:52:25</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>125.15</v>
+      </c>
+      <c r="D476" t="n">
+        <v>125.35</v>
+      </c>
+      <c r="E476" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F476" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-01-28 13:00:40</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="D477" t="n">
+        <v>119.75</v>
+      </c>
+      <c r="E477" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F477" t="n">
+        <v>-10481.25</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-01-28 13:06:38</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>136</v>
+      </c>
+      <c r="D478" t="n">
+        <v>137.05</v>
+      </c>
+      <c r="E478" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F478" t="n">
+        <v>1706.25</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-01-28 13:08:46</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="D479" t="n">
+        <v>120.75</v>
+      </c>
+      <c r="E479" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F479" t="n">
+        <v>406.25</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-01-28 13:27:21</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>132.25</v>
+      </c>
+      <c r="D480" t="n">
+        <v>132.2</v>
+      </c>
+      <c r="E480" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F480" t="n">
+        <v>-81.25</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-01-28 13:40:35</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>131.35</v>
+      </c>
+      <c r="D481" t="n">
+        <v>132.3</v>
+      </c>
+      <c r="E481" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F481" t="n">
+        <v>1543.75</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-01-28 13:42:10</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>130.45</v>
+      </c>
+      <c r="D482" t="n">
+        <v>131.45</v>
+      </c>
+      <c r="E482" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F482" t="n">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-01-28 13:48:02</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>NIFTY2620324950PE</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="D483" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="E483" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F483" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-01-28 13:53:54</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>122.05</v>
+      </c>
+      <c r="D484" t="n">
+        <v>123.3</v>
+      </c>
+      <c r="E484" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F484" t="n">
+        <v>2031.25</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-01-28 13:55:42</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>125.1</v>
+      </c>
+      <c r="D485" t="n">
+        <v>125.45</v>
+      </c>
+      <c r="E485" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F485" t="n">
+        <v>568.75</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-01-28 13:58:33</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>NIFTY2620325000PE</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="D486" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="E486" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F486" t="n">
+        <v>-9912.5</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-01-28 14:03:27</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="D487" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="E487" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F487" t="n">
+        <v>-9912.5</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-01-28 14:05:44</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>NIFTY2620324950PE</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="D488" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="E488" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F488" t="n">
+        <v>3168.75</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-01-28 14:11:43</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="D489" t="n">
+        <v>131.75</v>
+      </c>
+      <c r="E489" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F489" t="n">
+        <v>406.25</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-01-28 14:13:18</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>NIFTY2620325000PE</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>122</v>
+      </c>
+      <c r="D490" t="n">
+        <v>122</v>
+      </c>
+      <c r="E490" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F490" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-01-28 14:14:56</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>134.9</v>
+      </c>
+      <c r="D491" t="n">
+        <v>135.25</v>
+      </c>
+      <c r="E491" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F491" t="n">
+        <v>568.75</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-01-28 14:18:49</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>NIFTY2620325000PE</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>123.3</v>
+      </c>
+      <c r="D492" t="n">
+        <v>123.1</v>
+      </c>
+      <c r="E492" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F492" t="n">
+        <v>-325</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-01-28 14:27:51</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>124.25</v>
+      </c>
+      <c r="D493" t="n">
+        <v>124.7</v>
+      </c>
+      <c r="E493" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F493" t="n">
+        <v>731.25</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-01-28 14:29:50</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C494" t="n">
+        <v>126.95</v>
+      </c>
+      <c r="D494" t="n">
+        <v>128.75</v>
+      </c>
+      <c r="E494" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F494" t="n">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-01-28 14:31:38</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C495" t="n">
+        <v>133.4</v>
+      </c>
+      <c r="D495" t="n">
+        <v>133.65</v>
+      </c>
+      <c r="E495" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F495" t="n">
+        <v>406.25</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-01-28 14:36:40</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C496" t="n">
+        <v>130</v>
+      </c>
+      <c r="D496" t="n">
+        <v>132</v>
+      </c>
+      <c r="E496" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F496" t="n">
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-01-28 14:43:18</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>NIFTY2620325050PE</t>
+        </is>
+      </c>
+      <c r="C497" t="n">
+        <v>127.35</v>
+      </c>
+      <c r="D497" t="n">
+        <v>121.2</v>
+      </c>
+      <c r="E497" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F497" t="n">
+        <v>-9993.75</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-01-28 14:44:15</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>NIFTY2620325550CE</t>
+        </is>
+      </c>
+      <c r="C498" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="D498" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="E498" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F498" t="n">
+        <v>893.75</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-01-28 14:54:11</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>NIFTY2620325500CE</t>
+        </is>
+      </c>
+      <c r="C499" t="n">
+        <v>134.9</v>
+      </c>
+      <c r="D499" t="n">
+        <v>138.85</v>
+      </c>
+      <c r="E499" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F499" t="n">
+        <v>6418.75</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-01-29 11:55:12</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>NIFTY2620325100PE</t>
+        </is>
+      </c>
+      <c r="C500" t="n">
+        <v>123.85</v>
+      </c>
+      <c r="D500" t="n">
+        <v>123.15</v>
+      </c>
+      <c r="E500" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F500" t="n">
+        <v>-1137.5</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-01-29 12:05:40</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>NIFTY2620325150PE</t>
+        </is>
+      </c>
+      <c r="C501" t="n">
+        <v>136.1</v>
+      </c>
+      <c r="D501" t="n">
+        <v>130.1</v>
+      </c>
+      <c r="E501" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F501" t="n">
+        <v>-9750</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-01-29 12:10:19</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C502" t="n">
+        <v>124.55</v>
+      </c>
+      <c r="D502" t="n">
+        <v>124.4</v>
+      </c>
+      <c r="E502" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F502" t="n">
+        <v>-243.75</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-01-29 12:17:30</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C503" t="n">
+        <v>123.25</v>
+      </c>
+      <c r="D503" t="n">
+        <v>117.15</v>
+      </c>
+      <c r="E503" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F503" t="n">
+        <v>-9912.5</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:42:46</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C504" t="n">
+        <v>137.4</v>
+      </c>
+      <c r="D504" t="n">
+        <v>135.25</v>
+      </c>
+      <c r="E504" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F504" t="n">
+        <v>-3493.75</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-01-30 10:58:44</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>NIFTY2620325450CE</t>
+        </is>
+      </c>
+      <c r="C505" t="n">
+        <v>134.55</v>
+      </c>
+      <c r="D505" t="n">
+        <v>135.6</v>
+      </c>
+      <c r="E505" t="n">
+        <v>1625</v>
+      </c>
+      <c r="F505" t="n">
+        <v>1706.25</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:40:49</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C506" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="D506" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="E506" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F506" t="n">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:40:50</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C507" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="D507" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="E507" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F507" t="n">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:40:52</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C508" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="D508" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="E508" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F508" t="n">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:40:57</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C509" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="D509" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="E509" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F509" t="n">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:41:00</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C510" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="D510" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="E510" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F510" t="n">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:42:18</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C511" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="D511" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="E511" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F511" t="n">
+        <v>-3360.5</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:43:35</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C512" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="D512" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="E512" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F512" t="n">
+        <v>-7150</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:43:37</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C513" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="D513" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="E513" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F513" t="n">
+        <v>-2431</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:43:39</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C514" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="D514" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="E514" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F514" t="n">
+        <v>-3503.5</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:26</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C515" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D515" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="E515" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F515" t="n">
+        <v>1215.5</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:26</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C516" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D516" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="E516" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F516" t="n">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:27</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C517" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D517" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="E517" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F517" t="n">
+        <v>-500.5</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:27</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C518" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D518" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="E518" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F518" t="n">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:27</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C519" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D519" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="E519" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F519" t="n">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:28</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C520" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D520" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="E520" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F520" t="n">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:30</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C521" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D521" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="E521" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F521" t="n">
+        <v>2359.5</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:32</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C522" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D522" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="E522" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F522" t="n">
+        <v>1930.5</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:34</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C523" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D523" t="n">
+        <v>103</v>
+      </c>
+      <c r="E523" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F523" t="n">
+        <v>2216.5</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:35</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C524" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D524" t="n">
+        <v>101.65</v>
+      </c>
+      <c r="E524" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F524" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:38</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C525" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D525" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="E525" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F525" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:40</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C526" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D526" t="n">
+        <v>101.55</v>
+      </c>
+      <c r="E526" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F526" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:42</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C527" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D527" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="E527" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F527" t="n">
+        <v>-2288</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:43</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C528" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D528" t="n">
+        <v>98.55</v>
+      </c>
+      <c r="E528" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F528" t="n">
+        <v>-4147</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:44</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C529" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D529" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="E529" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F529" t="n">
+        <v>-3789.5</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:46</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C530" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D530" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="E530" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F530" t="n">
+        <v>-3789.5</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:47</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C531" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D531" t="n">
+        <v>97.95</v>
+      </c>
+      <c r="E531" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F531" t="n">
+        <v>-5005</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:48</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C532" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D532" t="n">
+        <v>97.55</v>
+      </c>
+      <c r="E532" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F532" t="n">
+        <v>-5577</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:50</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C533" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D533" t="n">
+        <v>97.45</v>
+      </c>
+      <c r="E533" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F533" t="n">
+        <v>-5720</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:51</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C534" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D534" t="n">
+        <v>97.45</v>
+      </c>
+      <c r="E534" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F534" t="n">
+        <v>-5720</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:53</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C535" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D535" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="E535" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F535" t="n">
+        <v>-4719</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:46:54</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C536" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D536" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="E536" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F536" t="n">
+        <v>-3217.5</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:48:11</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C537" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D537" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="E537" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F537" t="n">
+        <v>-3217.5</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-02-02 12:54:06</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C538" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="D538" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="E538" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F538" t="n">
+        <v>-71.5</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-02-02 13:06:32</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C539" t="n">
+        <v>140.7</v>
+      </c>
+      <c r="D539" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="E539" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F539" t="n">
+        <v>16874</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-02-02 13:08:21</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C540" t="n">
+        <v>151.05</v>
+      </c>
+      <c r="D540" t="n">
+        <v>151.55</v>
+      </c>
+      <c r="E540" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F540" t="n">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-02-02 13:10:35</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C541" t="n">
+        <v>151.4</v>
+      </c>
+      <c r="D541" t="n">
+        <v>150.9</v>
+      </c>
+      <c r="E541" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F541" t="n">
+        <v>-715</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-02-02 13:13:38</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900PE</t>
+        </is>
+      </c>
+      <c r="C542" t="n">
+        <v>95.95</v>
+      </c>
+      <c r="D542" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="E542" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F542" t="n">
+        <v>3074.5</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-02-02 13:14:14</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900CE</t>
+        </is>
+      </c>
+      <c r="C543" t="n">
+        <v>132.6</v>
+      </c>
+      <c r="D543" t="n">
+        <v>137.35</v>
+      </c>
+      <c r="E543" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F543" t="n">
+        <v>6792.5</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-02-02 13:16:14</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900PE</t>
+        </is>
+      </c>
+      <c r="C544" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="D544" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E544" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F544" t="n">
+        <v>929.5</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-02-02 13:16:48</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900PE</t>
+        </is>
+      </c>
+      <c r="C545" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="D545" t="n">
+        <v>108</v>
+      </c>
+      <c r="E545" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F545" t="n">
+        <v>6721</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-02-02 13:17:25</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900PE</t>
+        </is>
+      </c>
+      <c r="C546" t="n">
+        <v>103.85</v>
+      </c>
+      <c r="D546" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="E546" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F546" t="n">
+        <v>357.5</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-02-02 13:19:03</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900PE</t>
+        </is>
+      </c>
+      <c r="C547" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="D547" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="E547" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F547" t="n">
+        <v>1501.5</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-02-02 13:19:30</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900PE</t>
+        </is>
+      </c>
+      <c r="C548" t="n">
+        <v>118.35</v>
+      </c>
+      <c r="D548" t="n">
+        <v>119.15</v>
+      </c>
+      <c r="E548" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F548" t="n">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-02-02 13:20:39</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900PE</t>
+        </is>
+      </c>
+      <c r="C549" t="n">
+        <v>122.6</v>
+      </c>
+      <c r="D549" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="E549" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F549" t="n">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-02-02 13:22:09</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900PE</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>125.75</v>
+      </c>
+      <c r="D550" t="n">
+        <v>128.05</v>
+      </c>
+      <c r="E550" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F550" t="n">
+        <v>3289</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-02-02 13:25:32</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>NIFTY2620324900PE</t>
+        </is>
+      </c>
+      <c r="C551" t="n">
+        <v>127.75</v>
+      </c>
+      <c r="D551" t="n">
+        <v>133.7</v>
+      </c>
+      <c r="E551" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F551" t="n">
+        <v>8508.5</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-02-05 12:52:55</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>NIFTY2621025700CE</t>
+        </is>
+      </c>
+      <c r="C552" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="D552" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="E552" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F552" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-02-06 10:31:41</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>NIFTY2621025500PE</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>104.35</v>
+      </c>
+      <c r="D553" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="E553" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F553" t="n">
+        <v>3503.5</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-02-06 10:32:25</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>NIFTY2621025500PE</t>
+        </is>
+      </c>
+      <c r="C554" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="D554" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="E554" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F554" t="n">
+        <v>643.5</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-02-06 10:37:13</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>NIFTY2621025500CE</t>
+        </is>
+      </c>
+      <c r="C555" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="D555" t="n">
+        <v>127.35</v>
+      </c>
+      <c r="E555" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F555" t="n">
+        <v>4075.5</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-02-06 10:40:02</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>NIFTY2621025500CE</t>
+        </is>
+      </c>
+      <c r="C556" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="D556" t="n">
+        <v>127.65</v>
+      </c>
+      <c r="E556" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F556" t="n">
+        <v>1215.5</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-02-06 10:41:27</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>NIFTY2621025500PE</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="D557" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="E557" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F557" t="n">
+        <v>2788.5</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-02-06 10:44:00</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>NIFTY2621025500PE</t>
+        </is>
+      </c>
+      <c r="C558" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="D558" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="E558" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F558" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-02-06 10:44:58</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>NIFTY2621025500PE</t>
+        </is>
+      </c>
+      <c r="C559" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="D559" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="E559" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F559" t="n">
+        <v>500.5</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-02-06 11:25:04</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>NIFTY2621025500CE</t>
+        </is>
+      </c>
+      <c r="C560" t="n">
+        <v>162.7</v>
+      </c>
+      <c r="D560" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="E560" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F560" t="n">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-02-06 11:26:09</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>NIFTY2621025600CE</t>
+        </is>
+      </c>
+      <c r="C561" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="D561" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="E561" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F561" t="n">
+        <v>-786.5</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-02-06 11:26:37</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>NIFTY2621025600CE</t>
+        </is>
+      </c>
+      <c r="C562" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="D562" t="n">
+        <v>106.6</v>
+      </c>
+      <c r="E562" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F562" t="n">
+        <v>-1072.5</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-02-06 11:27:19</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>NIFTY2621025600CE</t>
+        </is>
+      </c>
+      <c r="C563" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="D563" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="E563" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F563" t="n">
+        <v>357.5</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-02-06 11:27:51</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>NIFTY2621025600PE</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>114.15</v>
+      </c>
+      <c r="D564" t="n">
+        <v>113.15</v>
+      </c>
+      <c r="E564" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F564" t="n">
+        <v>-1430</v>
       </c>
     </row>
   </sheetData>

--- a/Lakshmi.xlsx
+++ b/Lakshmi.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H564"/>
+  <dimension ref="A1:H658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="24.33203125" customWidth="1" style="1" min="1" max="1"/>
@@ -16725,6 +16725,2262 @@
       </c>
       <c r="F564" t="n">
         <v>-1430</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-02-09 11:22:44</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>NIFTY2621025800CE</t>
+        </is>
+      </c>
+      <c r="C565" t="n">
+        <v>119</v>
+      </c>
+      <c r="D565" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="E565" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F565" t="n">
+        <v>2717</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-02-09 11:25:24</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>NIFTY2621025800CE</t>
+        </is>
+      </c>
+      <c r="C566" t="n">
+        <v>122.85</v>
+      </c>
+      <c r="D566" t="n">
+        <v>124.4</v>
+      </c>
+      <c r="E566" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F566" t="n">
+        <v>2216.5</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-02-11 12:30:17</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>SENSEX2621283500CE</t>
+        </is>
+      </c>
+      <c r="C567" t="n">
+        <v>795.9</v>
+      </c>
+      <c r="D567" t="n">
+        <v>794</v>
+      </c>
+      <c r="E567" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F567" t="n">
+        <v>-1900</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-02-11 12:31:39</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>SENSEX2621284500CE</t>
+        </is>
+      </c>
+      <c r="C568" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="D568" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="E568" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F568" t="n">
+        <v>-1200</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-02-11 12:32:51</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>SENSEX2621284000PE</t>
+        </is>
+      </c>
+      <c r="C569" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="D569" t="n">
+        <v>113.35</v>
+      </c>
+      <c r="E569" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F569" t="n">
+        <v>7450</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-02-11 12:37:57</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>SENSEX2621283900PE</t>
+        </is>
+      </c>
+      <c r="C570" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="D570" t="n">
+        <v>99</v>
+      </c>
+      <c r="E570" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F570" t="n">
+        <v>7850</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-02-11 12:38:44</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>SENSEX2621283900PE</t>
+        </is>
+      </c>
+      <c r="C571" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="D571" t="n">
+        <v>96.15000000000001</v>
+      </c>
+      <c r="E571" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F571" t="n">
+        <v>-1100</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-02-11 12:40:28</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>SENSEX2621283900PE</t>
+        </is>
+      </c>
+      <c r="C572" t="n">
+        <v>101</v>
+      </c>
+      <c r="D572" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="E572" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F572" t="n">
+        <v>-1300</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-02-12 11:43:01</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>SENSEX2621283800CE</t>
+        </is>
+      </c>
+      <c r="C573" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="D573" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="E573" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F573" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-02-12 11:46:18</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>SENSEX2621283800CE</t>
+        </is>
+      </c>
+      <c r="C574" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="D574" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="E574" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F574" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-02-12 11:46:40</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>SENSEX2621283800CE</t>
+        </is>
+      </c>
+      <c r="C575" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="D575" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="E575" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F575" t="n">
+        <v>-650</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-02-13 11:34:01</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>NIFTY2621725550PE</t>
+        </is>
+      </c>
+      <c r="C576" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="D576" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="E576" t="n">
+        <v>975</v>
+      </c>
+      <c r="F576" t="n">
+        <v>1803.75</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-02-13 11:35:12</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>NIFTY2621725550PE</t>
+        </is>
+      </c>
+      <c r="C577" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="D577" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="E577" t="n">
+        <v>975</v>
+      </c>
+      <c r="F577" t="n">
+        <v>1462.5</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-02-16 12:18:30</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>NIFTY2621725550CE</t>
+        </is>
+      </c>
+      <c r="C578" t="n">
+        <v>87.65000000000001</v>
+      </c>
+      <c r="D578" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="E578" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F578" t="n">
+        <v>-500.5</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-02-16 12:19:15</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>NIFTY2621725500CE</t>
+        </is>
+      </c>
+      <c r="C579" t="n">
+        <v>122</v>
+      </c>
+      <c r="D579" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="E579" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F579" t="n">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-02-16 12:20:15</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>NIFTY2621725500CE</t>
+        </is>
+      </c>
+      <c r="C580" t="n">
+        <v>122.15</v>
+      </c>
+      <c r="D580" t="n">
+        <v>122.6</v>
+      </c>
+      <c r="E580" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F580" t="n">
+        <v>643.5</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-02-16 12:35:57</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>NIFTY2621725500CE</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>133.45</v>
+      </c>
+      <c r="D581" t="n">
+        <v>135.45</v>
+      </c>
+      <c r="E581" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F581" t="n">
+        <v>2860</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-02-16 12:50:01</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>NIFTY2621725650PE</t>
+        </is>
+      </c>
+      <c r="C582" t="n">
+        <v>118.75</v>
+      </c>
+      <c r="D582" t="n">
+        <v>125.05</v>
+      </c>
+      <c r="E582" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F582" t="n">
+        <v>9009</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-02-16 12:53:38</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>NIFTY2621725500CE</t>
+        </is>
+      </c>
+      <c r="C583" t="n">
+        <v>122.7</v>
+      </c>
+      <c r="D583" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="E583" t="n">
+        <v>1430</v>
+      </c>
+      <c r="F583" t="n">
+        <v>4290</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-02-17 09:50:57</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25750CE</t>
+        </is>
+      </c>
+      <c r="C584" t="n">
+        <v>118.75</v>
+      </c>
+      <c r="D584" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="E584" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F584" t="n">
+        <v>-195</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-02-17 09:52:40</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>NIFTY2621725550CE</t>
+        </is>
+      </c>
+      <c r="C585" t="n">
+        <v>117.15</v>
+      </c>
+      <c r="D585" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="E585" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F585" t="n">
+        <v>7865</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-02-17 09:53:27</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25750CE</t>
+        </is>
+      </c>
+      <c r="C586" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="D586" t="n">
+        <v>124.65</v>
+      </c>
+      <c r="E586" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F586" t="n">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-02-17 09:54:06</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25750CE</t>
+        </is>
+      </c>
+      <c r="C587" t="n">
+        <v>123.8</v>
+      </c>
+      <c r="D587" t="n">
+        <v>124</v>
+      </c>
+      <c r="E587" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F587" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-02-17 09:57:39</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25750CE</t>
+        </is>
+      </c>
+      <c r="C588" t="n">
+        <v>124.75</v>
+      </c>
+      <c r="D588" t="n">
+        <v>125.25</v>
+      </c>
+      <c r="E588" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F588" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-02-17 10:09:12</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25750CE</t>
+        </is>
+      </c>
+      <c r="C589" t="n">
+        <v>128.6</v>
+      </c>
+      <c r="D589" t="n">
+        <v>129.45</v>
+      </c>
+      <c r="E589" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F589" t="n">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-02-17 10:26:39</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25750CE</t>
+        </is>
+      </c>
+      <c r="C590" t="n">
+        <v>139.8</v>
+      </c>
+      <c r="D590" t="n">
+        <v>139.8</v>
+      </c>
+      <c r="E590" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F590" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-02-17 10:27:03</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25750CE</t>
+        </is>
+      </c>
+      <c r="C591" t="n">
+        <v>148.65</v>
+      </c>
+      <c r="D591" t="n">
+        <v>148.75</v>
+      </c>
+      <c r="E591" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F591" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-02-17 10:27:26</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25750CE</t>
+        </is>
+      </c>
+      <c r="C592" t="n">
+        <v>151</v>
+      </c>
+      <c r="D592" t="n">
+        <v>151</v>
+      </c>
+      <c r="E592" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F592" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-02-17 10:27:59</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25750CE</t>
+        </is>
+      </c>
+      <c r="C593" t="n">
+        <v>154.7</v>
+      </c>
+      <c r="D593" t="n">
+        <v>155.35</v>
+      </c>
+      <c r="E593" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F593" t="n">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-02-17 10:29:05</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>NIFTY2621725650CE</t>
+        </is>
+      </c>
+      <c r="C594" t="n">
+        <v>98</v>
+      </c>
+      <c r="D594" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="E594" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F594" t="n">
+        <v>6565</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-02-17 10:32:41</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>NIFTY2621725650CE</t>
+        </is>
+      </c>
+      <c r="C595" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="D595" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="E595" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F595" t="n">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-02-17 10:36:05</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>NIFTY2621725800PE</t>
+        </is>
+      </c>
+      <c r="C596" t="n">
+        <v>111.95</v>
+      </c>
+      <c r="D596" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="E596" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F596" t="n">
+        <v>-195</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-02-17 10:36:29</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>NIFTY2621725800PE</t>
+        </is>
+      </c>
+      <c r="C597" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="D597" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="E597" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F597" t="n">
+        <v>-65</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-02-17 10:37:28</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>NIFTY2621725800PE</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="D598" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="E598" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F598" t="n">
+        <v>-1365</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-02-17 10:38:01</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>NIFTY2621725800PE</t>
+        </is>
+      </c>
+      <c r="C599" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="D599" t="n">
+        <v>117.35</v>
+      </c>
+      <c r="E599" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F599" t="n">
+        <v>3185</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-02-17 10:40:45</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>NIFTY2621725800PE</t>
+        </is>
+      </c>
+      <c r="C600" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="D600" t="n">
+        <v>122.35</v>
+      </c>
+      <c r="E600" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F600" t="n">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-02-17 10:41:51</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>NIFTY2621725800PE</t>
+        </is>
+      </c>
+      <c r="C601" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="D601" t="n">
+        <v>122.6</v>
+      </c>
+      <c r="E601" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F601" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-02-17 10:43:38</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>NIFTY2621725800PE</t>
+        </is>
+      </c>
+      <c r="C602" t="n">
+        <v>127.85</v>
+      </c>
+      <c r="D602" t="n">
+        <v>134.25</v>
+      </c>
+      <c r="E602" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F602" t="n">
+        <v>8320</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-02-17 11:33:11</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>NIFTY2621725600CE</t>
+        </is>
+      </c>
+      <c r="C603" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="D603" t="n">
+        <v>114.45</v>
+      </c>
+      <c r="E603" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F603" t="n">
+        <v>15535</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-02-17 12:40:30</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>NIFTY2621725850PE</t>
+        </is>
+      </c>
+      <c r="C604" t="n">
+        <v>125.1</v>
+      </c>
+      <c r="D604" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="E604" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F604" t="n">
+        <v>-11570</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-02-18 09:47:31</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25700PE</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="D605" t="n">
+        <v>116.15</v>
+      </c>
+      <c r="E605" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F605" t="n">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-02-18 09:53:15</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25700PE</t>
+        </is>
+      </c>
+      <c r="C606" t="n">
+        <v>119.75</v>
+      </c>
+      <c r="D606" t="n">
+        <v>122.85</v>
+      </c>
+      <c r="E606" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F606" t="n">
+        <v>4030</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-02-18 09:54:59</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25700PE</t>
+        </is>
+      </c>
+      <c r="C607" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="D607" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="E607" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F607" t="n">
+        <v>-260</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-02-18 09:55:30</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25700PE</t>
+        </is>
+      </c>
+      <c r="C608" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="D608" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="E608" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F608" t="n">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-02-18 09:56:04</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25700PE</t>
+        </is>
+      </c>
+      <c r="C609" t="n">
+        <v>135</v>
+      </c>
+      <c r="D609" t="n">
+        <v>141.75</v>
+      </c>
+      <c r="E609" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F609" t="n">
+        <v>8775</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-02-18 10:18:12</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25600PE</t>
+        </is>
+      </c>
+      <c r="C610" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="D610" t="n">
+        <v>108</v>
+      </c>
+      <c r="E610" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F610" t="n">
+        <v>-9360</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-02-18 10:34:16</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25750CE</t>
+        </is>
+      </c>
+      <c r="C611" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="D611" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="E611" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F611" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-02-18 10:37:11</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25600PE</t>
+        </is>
+      </c>
+      <c r="C612" t="n">
+        <v>101.35</v>
+      </c>
+      <c r="D612" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="E612" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F612" t="n">
+        <v>-7865</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-02-20 10:58:33</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C613" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="D613" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="E613" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F613" t="n">
+        <v>-11765</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-02-20 10:59:33</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C614" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="D614" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="E614" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F614" t="n">
+        <v>4420</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:01:04</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C615" t="n">
+        <v>114.85</v>
+      </c>
+      <c r="D615" t="n">
+        <v>115.7</v>
+      </c>
+      <c r="E615" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F615" t="n">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:07:42</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C616" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="D616" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="E616" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F616" t="n">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:13:17</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C617" t="n">
+        <v>114.15</v>
+      </c>
+      <c r="D617" t="n">
+        <v>114.45</v>
+      </c>
+      <c r="E617" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F617" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:14:10</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C618" t="n">
+        <v>113.65</v>
+      </c>
+      <c r="D618" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="E618" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F618" t="n">
+        <v>-12025</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:14:49</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25550PE</t>
+        </is>
+      </c>
+      <c r="C619" t="n">
+        <v>120.4</v>
+      </c>
+      <c r="D619" t="n">
+        <v>121.15</v>
+      </c>
+      <c r="E619" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F619" t="n">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-02-20 11:15:45</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C620" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="D620" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="E620" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F620" t="n">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-02-20 12:12:50</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C621" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="D621" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="E621" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F621" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-02-20 12:14:22</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C622" t="n">
+        <v>112.55</v>
+      </c>
+      <c r="D622" t="n">
+        <v>114</v>
+      </c>
+      <c r="E622" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F622" t="n">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-02-20 14:35:53</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C623" t="n">
+        <v>114.65</v>
+      </c>
+      <c r="D623" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="E623" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F623" t="n">
+        <v>5135</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-02-20 14:36:16</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C624" t="n">
+        <v>118.95</v>
+      </c>
+      <c r="D624" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="E624" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F624" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-02-20 14:37:10</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C625" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="D625" t="n">
+        <v>115.95</v>
+      </c>
+      <c r="E625" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F625" t="n">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-02-20 14:38:26</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C626" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="D626" t="n">
+        <v>112</v>
+      </c>
+      <c r="E626" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F626" t="n">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-02-20 14:39:37</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C627" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="D627" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="E627" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F627" t="n">
+        <v>2925</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-02-20 14:40:48</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C628" t="n">
+        <v>118.45</v>
+      </c>
+      <c r="D628" t="n">
+        <v>119</v>
+      </c>
+      <c r="E628" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F628" t="n">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-02-20 14:41:24</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25500CE</t>
+        </is>
+      </c>
+      <c r="C629" t="n">
+        <v>206.45</v>
+      </c>
+      <c r="D629" t="n">
+        <v>208.65</v>
+      </c>
+      <c r="E629" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F629" t="n">
+        <v>2860</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-02-20 14:42:08</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25500CE</t>
+        </is>
+      </c>
+      <c r="C630" t="n">
+        <v>206.9</v>
+      </c>
+      <c r="D630" t="n">
+        <v>211</v>
+      </c>
+      <c r="E630" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F630" t="n">
+        <v>5330</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-02-20 14:42:32</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25500CE</t>
+        </is>
+      </c>
+      <c r="C631" t="n">
+        <v>208.95</v>
+      </c>
+      <c r="D631" t="n">
+        <v>209.75</v>
+      </c>
+      <c r="E631" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F631" t="n">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-02-20 14:43:14</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25500CE</t>
+        </is>
+      </c>
+      <c r="C632" t="n">
+        <v>209.85</v>
+      </c>
+      <c r="D632" t="n">
+        <v>212.9</v>
+      </c>
+      <c r="E632" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F632" t="n">
+        <v>3965</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-02-20 14:43:36</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25500CE</t>
+        </is>
+      </c>
+      <c r="C633" t="n">
+        <v>210.9</v>
+      </c>
+      <c r="D633" t="n">
+        <v>211.4</v>
+      </c>
+      <c r="E633" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F633" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-02-20 14:44:30</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25500CE</t>
+        </is>
+      </c>
+      <c r="C634" t="n">
+        <v>222.95</v>
+      </c>
+      <c r="D634" t="n">
+        <v>228.3</v>
+      </c>
+      <c r="E634" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F634" t="n">
+        <v>6955</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-02-20 14:44:57</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25500CE</t>
+        </is>
+      </c>
+      <c r="C635" t="n">
+        <v>223.15</v>
+      </c>
+      <c r="D635" t="n">
+        <v>222.75</v>
+      </c>
+      <c r="E635" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F635" t="n">
+        <v>-520</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-02-20 14:45:41</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25500CE</t>
+        </is>
+      </c>
+      <c r="C636" t="n">
+        <v>223.95</v>
+      </c>
+      <c r="D636" t="n">
+        <v>226.85</v>
+      </c>
+      <c r="E636" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F636" t="n">
+        <v>3770</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-02-23 11:48:34</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C637" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="D637" t="n">
+        <v>100.15</v>
+      </c>
+      <c r="E637" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F637" t="n">
+        <v>-12090</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-02-23 11:49:42</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650PE</t>
+        </is>
+      </c>
+      <c r="C638" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="D638" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="E638" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F638" t="n">
+        <v>8125</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-02-23 11:50:11</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650PE</t>
+        </is>
+      </c>
+      <c r="C639" t="n">
+        <v>97</v>
+      </c>
+      <c r="D639" t="n">
+        <v>99.55</v>
+      </c>
+      <c r="E639" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F639" t="n">
+        <v>3315</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-02-23 11:50:28</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650PE</t>
+        </is>
+      </c>
+      <c r="C640" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="D640" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="E640" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F640" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-02-23 11:51:13</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650PE</t>
+        </is>
+      </c>
+      <c r="C641" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="D641" t="n">
+        <v>110</v>
+      </c>
+      <c r="E641" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F641" t="n">
+        <v>7280</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-02-23 11:53:43</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C642" t="n">
+        <v>96.55</v>
+      </c>
+      <c r="D642" t="n">
+        <v>103.45</v>
+      </c>
+      <c r="E642" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F642" t="n">
+        <v>8970</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-02-23 11:54:39</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C643" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="D643" t="n">
+        <v>105.85</v>
+      </c>
+      <c r="E643" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F643" t="n">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-02-23 12:11:57</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C644" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="D644" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="E644" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F644" t="n">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-02-23 12:14:12</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25650CE</t>
+        </is>
+      </c>
+      <c r="C645" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="D645" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E645" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F645" t="n">
+        <v>-12155</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:57:14</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25550PE</t>
+        </is>
+      </c>
+      <c r="C646" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="D646" t="n">
+        <v>110.45</v>
+      </c>
+      <c r="E646" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F646" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:57:48</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25550PE</t>
+        </is>
+      </c>
+      <c r="C647" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="D647" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="E647" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F647" t="n">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>2026-02-24 10:58:07</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25550PE</t>
+        </is>
+      </c>
+      <c r="C648" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="D648" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="E648" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F648" t="n">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:06:07</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>NIFTY2630225300PE</t>
+        </is>
+      </c>
+      <c r="C649" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="D649" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="E649" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F649" t="n">
+        <v>3510</v>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:07:22</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25400CE</t>
+        </is>
+      </c>
+      <c r="C650" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="D650" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="E650" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F650" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:08:48</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB83500CE</t>
+        </is>
+      </c>
+      <c r="C651" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="D651" t="n">
+        <v>117.65</v>
+      </c>
+      <c r="E651" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F651" t="n">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:30:18</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25450CE</t>
+        </is>
+      </c>
+      <c r="C652" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="D652" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="E652" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F652" t="n">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:49:06</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25600PE</t>
+        </is>
+      </c>
+      <c r="C653" t="n">
+        <v>119.25</v>
+      </c>
+      <c r="D653" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="E653" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F653" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:51:06</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25600PE</t>
+        </is>
+      </c>
+      <c r="C654" t="n">
+        <v>118.15</v>
+      </c>
+      <c r="D654" t="n">
+        <v>121.2</v>
+      </c>
+      <c r="E654" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F654" t="n">
+        <v>3965</v>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>2026-02-24 11:56:43</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25600PE</t>
+        </is>
+      </c>
+      <c r="C655" t="n">
+        <v>121.3</v>
+      </c>
+      <c r="D655" t="n">
+        <v>122</v>
+      </c>
+      <c r="E655" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F655" t="n">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>2026-02-24 12:01:14</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25550PE</t>
+        </is>
+      </c>
+      <c r="C656" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="D656" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="E656" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F656" t="n">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>2026-02-24 12:01:38</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25550PE</t>
+        </is>
+      </c>
+      <c r="C657" t="n">
+        <v>104.15</v>
+      </c>
+      <c r="D657" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="E657" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F657" t="n">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>2026-02-24 12:03:35</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25550PE</t>
+        </is>
+      </c>
+      <c r="C658" t="n">
+        <v>104.7</v>
+      </c>
+      <c r="D658" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="E658" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F658" t="n">
+        <v>4355</v>
       </c>
     </row>
   </sheetData>

--- a/Lakshmi.xlsx
+++ b/Lakshmi.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H658"/>
+  <dimension ref="A1:H741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="24.33203125" customWidth="1" style="1" min="1" max="1"/>
@@ -18981,6 +18981,1998 @@
       </c>
       <c r="F658" t="n">
         <v>4355</v>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>2026-02-24 12:19:13</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25550PE</t>
+        </is>
+      </c>
+      <c r="C659" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="D659" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="E659" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F659" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>2026-02-24 12:19:43</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25550PE</t>
+        </is>
+      </c>
+      <c r="C660" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="D660" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="E660" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F660" t="n">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>2026-02-24 12:20:19</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25550PE</t>
+        </is>
+      </c>
+      <c r="C661" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="D661" t="n">
+        <v>110</v>
+      </c>
+      <c r="E661" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F661" t="n">
+        <v>-1690</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2026-02-24 12:21:00</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25550PE</t>
+        </is>
+      </c>
+      <c r="C662" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="D662" t="n">
+        <v>123.6</v>
+      </c>
+      <c r="E662" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F662" t="n">
+        <v>14950</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2026-02-24 12:27:34</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>NIFTY26FEB25500PE</t>
+        </is>
+      </c>
+      <c r="C663" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="D663" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="E663" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F663" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:55:37</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>NIFTY2630225700CE</t>
+        </is>
+      </c>
+      <c r="C664" t="n">
+        <v>116</v>
+      </c>
+      <c r="D664" t="n">
+        <v>116.45</v>
+      </c>
+      <c r="E664" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F664" t="n">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:56:03</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>NIFTY2630225700CE</t>
+        </is>
+      </c>
+      <c r="C665" t="n">
+        <v>114.85</v>
+      </c>
+      <c r="D665" t="n">
+        <v>115.35</v>
+      </c>
+      <c r="E665" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F665" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:58:13</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB83300CE</t>
+        </is>
+      </c>
+      <c r="C666" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="D666" t="n">
+        <v>107.85</v>
+      </c>
+      <c r="E666" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F666" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-02-25 10:59:03</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB83300CE</t>
+        </is>
+      </c>
+      <c r="C667" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="D667" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="E667" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F667" t="n">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:00:03</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB82400PE</t>
+        </is>
+      </c>
+      <c r="C668" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="D668" t="n">
+        <v>109.65</v>
+      </c>
+      <c r="E668" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F668" t="n">
+        <v>5250</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:01:42</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB83300CE</t>
+        </is>
+      </c>
+      <c r="C669" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="D669" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="E669" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F669" t="n">
+        <v>4350</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:02:23</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB83300CE</t>
+        </is>
+      </c>
+      <c r="C670" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="D670" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="E670" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F670" t="n">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-02-25 11:04:29</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB83300CE</t>
+        </is>
+      </c>
+      <c r="C671" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="D671" t="n">
+        <v>96.25</v>
+      </c>
+      <c r="E671" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F671" t="n">
+        <v>-9150</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:09:26</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB82200PE</t>
+        </is>
+      </c>
+      <c r="C672" t="n">
+        <v>292.85</v>
+      </c>
+      <c r="D672" t="n">
+        <v>294.05</v>
+      </c>
+      <c r="E672" t="n">
+        <v>40</v>
+      </c>
+      <c r="F672" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:10:19</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB82200PE</t>
+        </is>
+      </c>
+      <c r="C673" t="n">
+        <v>289.45</v>
+      </c>
+      <c r="D673" t="n">
+        <v>289.95</v>
+      </c>
+      <c r="E673" t="n">
+        <v>40</v>
+      </c>
+      <c r="F673" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:17:55</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>NIFTY2630225400PE</t>
+        </is>
+      </c>
+      <c r="C674" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="D674" t="n">
+        <v>109.05</v>
+      </c>
+      <c r="E674" t="n">
+        <v>65</v>
+      </c>
+      <c r="F674" t="n">
+        <v>-562.25</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:19:45</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>NIFTY2630225550CE</t>
+        </is>
+      </c>
+      <c r="C675" t="n">
+        <v>125.8</v>
+      </c>
+      <c r="D675" t="n">
+        <v>126.7</v>
+      </c>
+      <c r="E675" t="n">
+        <v>65</v>
+      </c>
+      <c r="F675" t="n">
+        <v>58.5</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:20:54</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>NIFTY2630225550CE</t>
+        </is>
+      </c>
+      <c r="C676" t="n">
+        <v>125.4</v>
+      </c>
+      <c r="D676" t="n">
+        <v>125</v>
+      </c>
+      <c r="E676" t="n">
+        <v>65</v>
+      </c>
+      <c r="F676" t="n">
+        <v>-26</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:22:11</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>NIFTY2630225550CE</t>
+        </is>
+      </c>
+      <c r="C677" t="n">
+        <v>126.9</v>
+      </c>
+      <c r="D677" t="n">
+        <v>127.4</v>
+      </c>
+      <c r="E677" t="n">
+        <v>65</v>
+      </c>
+      <c r="F677" t="n">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:23:47</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>NIFTY2630225550CE</t>
+        </is>
+      </c>
+      <c r="C678" t="n">
+        <v>126.25</v>
+      </c>
+      <c r="D678" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="E678" t="n">
+        <v>65</v>
+      </c>
+      <c r="F678" t="n">
+        <v>16.25</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:24:47</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>NIFTY2630225550CE</t>
+        </is>
+      </c>
+      <c r="C679" t="n">
+        <v>124.35</v>
+      </c>
+      <c r="D679" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="E679" t="n">
+        <v>65</v>
+      </c>
+      <c r="F679" t="n">
+        <v>-276.25</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:25:34</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB82200PE</t>
+        </is>
+      </c>
+      <c r="C680" t="n">
+        <v>238.45</v>
+      </c>
+      <c r="D680" t="n">
+        <v>240.35</v>
+      </c>
+      <c r="E680" t="n">
+        <v>40</v>
+      </c>
+      <c r="F680" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:25:52</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB82200PE</t>
+        </is>
+      </c>
+      <c r="C681" t="n">
+        <v>240.6</v>
+      </c>
+      <c r="D681" t="n">
+        <v>241.5</v>
+      </c>
+      <c r="E681" t="n">
+        <v>40</v>
+      </c>
+      <c r="F681" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:26:33</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB82200PE</t>
+        </is>
+      </c>
+      <c r="C682" t="n">
+        <v>241.45</v>
+      </c>
+      <c r="D682" t="n">
+        <v>245.45</v>
+      </c>
+      <c r="E682" t="n">
+        <v>40</v>
+      </c>
+      <c r="F682" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:26:55</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB82200PE</t>
+        </is>
+      </c>
+      <c r="C683" t="n">
+        <v>244.55</v>
+      </c>
+      <c r="D683" t="n">
+        <v>242.75</v>
+      </c>
+      <c r="E683" t="n">
+        <v>40</v>
+      </c>
+      <c r="F683" t="n">
+        <v>-72</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:27:12</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB82200PE</t>
+        </is>
+      </c>
+      <c r="C684" t="n">
+        <v>243.1</v>
+      </c>
+      <c r="D684" t="n">
+        <v>244.35</v>
+      </c>
+      <c r="E684" t="n">
+        <v>40</v>
+      </c>
+      <c r="F684" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:27:40</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB82200PE</t>
+        </is>
+      </c>
+      <c r="C685" t="n">
+        <v>250.35</v>
+      </c>
+      <c r="D685" t="n">
+        <v>251.05</v>
+      </c>
+      <c r="E685" t="n">
+        <v>40</v>
+      </c>
+      <c r="F685" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:28:04</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB82200PE</t>
+        </is>
+      </c>
+      <c r="C686" t="n">
+        <v>250.88</v>
+      </c>
+      <c r="D686" t="n">
+        <v>251.65</v>
+      </c>
+      <c r="E686" t="n">
+        <v>40</v>
+      </c>
+      <c r="F686" t="n">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:31:08</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB82200PE</t>
+        </is>
+      </c>
+      <c r="C687" t="n">
+        <v>263.6</v>
+      </c>
+      <c r="D687" t="n">
+        <v>240.2</v>
+      </c>
+      <c r="E687" t="n">
+        <v>40</v>
+      </c>
+      <c r="F687" t="n">
+        <v>-936</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:31:31</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB82200PE</t>
+        </is>
+      </c>
+      <c r="C688" t="n">
+        <v>227.05</v>
+      </c>
+      <c r="D688" t="n">
+        <v>225.38</v>
+      </c>
+      <c r="E688" t="n">
+        <v>40</v>
+      </c>
+      <c r="F688" t="n">
+        <v>-66.8</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:32:05</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB82200PE</t>
+        </is>
+      </c>
+      <c r="C689" t="n">
+        <v>219.3</v>
+      </c>
+      <c r="D689" t="n">
+        <v>225.15</v>
+      </c>
+      <c r="E689" t="n">
+        <v>40</v>
+      </c>
+      <c r="F689" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:32:44</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB82200PE</t>
+        </is>
+      </c>
+      <c r="C690" t="n">
+        <v>227.8</v>
+      </c>
+      <c r="D690" t="n">
+        <v>229.7</v>
+      </c>
+      <c r="E690" t="n">
+        <v>40</v>
+      </c>
+      <c r="F690" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-02-25 14:33:09</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB82200PE</t>
+        </is>
+      </c>
+      <c r="C691" t="n">
+        <v>231.43</v>
+      </c>
+      <c r="D691" t="n">
+        <v>231.6</v>
+      </c>
+      <c r="E691" t="n">
+        <v>40</v>
+      </c>
+      <c r="F691" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-02-26 11:58:51</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB82000PE</t>
+        </is>
+      </c>
+      <c r="C692" t="n">
+        <v>89.65000000000001</v>
+      </c>
+      <c r="D692" t="n">
+        <v>91</v>
+      </c>
+      <c r="E692" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F692" t="n">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-02-26 11:59:36</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>SENSEX26FEB82300CE</t>
+        </is>
+      </c>
+      <c r="C693" t="n">
+        <v>89.95</v>
+      </c>
+      <c r="D693" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="E693" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F693" t="n">
+        <v>-9600</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-02-26 12:01:18</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>NIFTY2630225450PE</t>
+        </is>
+      </c>
+      <c r="C694" t="n">
+        <v>115.25</v>
+      </c>
+      <c r="D694" t="n">
+        <v>118.85</v>
+      </c>
+      <c r="E694" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F694" t="n">
+        <v>4680</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-02-27 10:06:08</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>NIFTY2630225350PE</t>
+        </is>
+      </c>
+      <c r="C695" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="D695" t="n">
+        <v>120.4</v>
+      </c>
+      <c r="E695" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F695" t="n">
+        <v>4550</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-02-27 10:06:24</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>NIFTY2630225350PE</t>
+        </is>
+      </c>
+      <c r="C696" t="n">
+        <v>121.4</v>
+      </c>
+      <c r="D696" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="E696" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F696" t="n">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-02-27 10:06:49</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>NIFTY2630225350PE</t>
+        </is>
+      </c>
+      <c r="C697" t="n">
+        <v>124.25</v>
+      </c>
+      <c r="D697" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="E697" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F697" t="n">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-02-27 10:07:25</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>NIFTY2630225350PE</t>
+        </is>
+      </c>
+      <c r="C698" t="n">
+        <v>128.15</v>
+      </c>
+      <c r="D698" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="E698" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F698" t="n">
+        <v>-65</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-02-27 11:36:52</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>NIFTY2630225250PE</t>
+        </is>
+      </c>
+      <c r="C699" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="D699" t="n">
+        <v>96</v>
+      </c>
+      <c r="E699" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F699" t="n">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-02-27 11:37:30</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>NIFTY2630225250PE</t>
+        </is>
+      </c>
+      <c r="C700" t="n">
+        <v>98.55</v>
+      </c>
+      <c r="D700" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="E700" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F700" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-02-27 11:40:38</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>NIFTY2630225250PE</t>
+        </is>
+      </c>
+      <c r="C701" t="n">
+        <v>98</v>
+      </c>
+      <c r="D701" t="n">
+        <v>88.55</v>
+      </c>
+      <c r="E701" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F701" t="n">
+        <v>-12285</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:05:34</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>NIFTY2630224900PE</t>
+        </is>
+      </c>
+      <c r="C702" t="n">
+        <v>98.65000000000001</v>
+      </c>
+      <c r="D702" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="E702" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F702" t="n">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-03-02 11:06:10</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>NIFTY2630224900PE</t>
+        </is>
+      </c>
+      <c r="C703" t="n">
+        <v>98.05</v>
+      </c>
+      <c r="D703" t="n">
+        <v>88.55</v>
+      </c>
+      <c r="E703" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F703" t="n">
+        <v>-12350</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-03-09 13:00:09</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>NIFTY2631024150CE</t>
+        </is>
+      </c>
+      <c r="C704" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="D704" t="n">
+        <v>104</v>
+      </c>
+      <c r="E704" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F704" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-03-09 13:00:32</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>NIFTY2631024150CE</t>
+        </is>
+      </c>
+      <c r="C705" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="D705" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="E705" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F705" t="n">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-03-09 13:01:48</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>NIFTY2631024150CE</t>
+        </is>
+      </c>
+      <c r="C706" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="D706" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="E706" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F706" t="n">
+        <v>2730</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-03-09 13:02:16</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>NIFTY2631024150CE</t>
+        </is>
+      </c>
+      <c r="C707" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="D707" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="E707" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F707" t="n">
+        <v>-1625</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-03-09 13:02:57</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>NIFTY2631024150CE</t>
+        </is>
+      </c>
+      <c r="C708" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="D708" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="E708" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F708" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-03-09 13:06:13</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>NIFTY2631024150CE</t>
+        </is>
+      </c>
+      <c r="C709" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="D709" t="n">
+        <v>102</v>
+      </c>
+      <c r="E709" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F709" t="n">
+        <v>-650</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:44:06</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>NIFTY2631024250PE</t>
+        </is>
+      </c>
+      <c r="C710" t="n">
+        <v>110.85</v>
+      </c>
+      <c r="D710" t="n">
+        <v>120.25</v>
+      </c>
+      <c r="E710" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F710" t="n">
+        <v>12220</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:44:37</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>NIFTY2631024250PE</t>
+        </is>
+      </c>
+      <c r="C711" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="D711" t="n">
+        <v>117.85</v>
+      </c>
+      <c r="E711" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F711" t="n">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:48:08</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>NIFTY2631024100CE</t>
+        </is>
+      </c>
+      <c r="C712" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="D712" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="E712" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F712" t="n">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:48:31</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>NIFTY2631024100CE</t>
+        </is>
+      </c>
+      <c r="C713" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="D713" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="E713" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F713" t="n">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:49:18</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>NIFTY2631024100CE</t>
+        </is>
+      </c>
+      <c r="C714" t="n">
+        <v>99.55</v>
+      </c>
+      <c r="D714" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="E714" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F714" t="n">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:53:10</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>NIFTY2631024100CE</t>
+        </is>
+      </c>
+      <c r="C715" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="D715" t="n">
+        <v>114</v>
+      </c>
+      <c r="E715" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F715" t="n">
+        <v>-12870</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-03-11 12:43:41</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>SENSEX2631278200CE</t>
+        </is>
+      </c>
+      <c r="C716" t="n">
+        <v>173.35</v>
+      </c>
+      <c r="D716" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="E716" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F716" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-03-11 12:44:26</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>SENSEX2631278200CE</t>
+        </is>
+      </c>
+      <c r="C717" t="n">
+        <v>175.9</v>
+      </c>
+      <c r="D717" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="E717" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F717" t="n">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-03-11 12:44:39</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>SENSEX2631278200CE</t>
+        </is>
+      </c>
+      <c r="C718" t="n">
+        <v>178.65</v>
+      </c>
+      <c r="D718" t="n">
+        <v>179</v>
+      </c>
+      <c r="E718" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F718" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-03-11 12:44:55</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>SENSEX2631278200CE</t>
+        </is>
+      </c>
+      <c r="C719" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="D719" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="E719" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F719" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-03-11 12:47:11</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>SENSEX2631276200PE</t>
+        </is>
+      </c>
+      <c r="C720" t="n">
+        <v>172.75</v>
+      </c>
+      <c r="D720" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="E720" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F720" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-03-11 12:47:35</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>SENSEX2631276200PE</t>
+        </is>
+      </c>
+      <c r="C721" t="n">
+        <v>176</v>
+      </c>
+      <c r="D721" t="n">
+        <v>177.05</v>
+      </c>
+      <c r="E721" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F721" t="n">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-03-11 12:48:14</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>SENSEX2631276200PE</t>
+        </is>
+      </c>
+      <c r="C722" t="n">
+        <v>177.35</v>
+      </c>
+      <c r="D722" t="n">
+        <v>179.05</v>
+      </c>
+      <c r="E722" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F722" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-03-11 12:48:59</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>SENSEX2631276200PE</t>
+        </is>
+      </c>
+      <c r="C723" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="D723" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="E723" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F723" t="n">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:21:57</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>SENSEX2631275900PE</t>
+        </is>
+      </c>
+      <c r="C724" t="n">
+        <v>162.3</v>
+      </c>
+      <c r="D724" t="n">
+        <v>152.55</v>
+      </c>
+      <c r="E724" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F724" t="n">
+        <v>-9750</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:23:54</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>SENSEX2631278100CE</t>
+        </is>
+      </c>
+      <c r="C725" t="n">
+        <v>184.05</v>
+      </c>
+      <c r="D725" t="n">
+        <v>184.45</v>
+      </c>
+      <c r="E725" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F725" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:24:15</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>SENSEX2631278100CE</t>
+        </is>
+      </c>
+      <c r="C726" t="n">
+        <v>185.45</v>
+      </c>
+      <c r="D726" t="n">
+        <v>185.15</v>
+      </c>
+      <c r="E726" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F726" t="n">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:24:28</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>SENSEX2631278100CE</t>
+        </is>
+      </c>
+      <c r="C727" t="n">
+        <v>184.35</v>
+      </c>
+      <c r="D727" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="E727" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F727" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:24:47</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>SENSEX2631278100CE</t>
+        </is>
+      </c>
+      <c r="C728" t="n">
+        <v>185.05</v>
+      </c>
+      <c r="D728" t="n">
+        <v>187.45</v>
+      </c>
+      <c r="E728" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F728" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:25:01</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>SENSEX2631278100CE</t>
+        </is>
+      </c>
+      <c r="C729" t="n">
+        <v>189.2</v>
+      </c>
+      <c r="D729" t="n">
+        <v>189.9</v>
+      </c>
+      <c r="E729" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F729" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:26:05</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>SENSEX2631278100CE</t>
+        </is>
+      </c>
+      <c r="C730" t="n">
+        <v>186.55</v>
+      </c>
+      <c r="D730" t="n">
+        <v>186.65</v>
+      </c>
+      <c r="E730" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F730" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:26:15</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>SENSEX2631278100CE</t>
+        </is>
+      </c>
+      <c r="C731" t="n">
+        <v>187.3</v>
+      </c>
+      <c r="D731" t="n">
+        <v>186.55</v>
+      </c>
+      <c r="E731" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F731" t="n">
+        <v>-750</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:29:33</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>NIFTY2631724350CE</t>
+        </is>
+      </c>
+      <c r="C732" t="n">
+        <v>142.95</v>
+      </c>
+      <c r="D732" t="n">
+        <v>144.4</v>
+      </c>
+      <c r="E732" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F732" t="n">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:30:07</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>SENSEX2631278100CE</t>
+        </is>
+      </c>
+      <c r="C733" t="n">
+        <v>201.9</v>
+      </c>
+      <c r="D733" t="n">
+        <v>208.45</v>
+      </c>
+      <c r="E733" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F733" t="n">
+        <v>6550</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:30:19</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>SENSEX2631278100CE</t>
+        </is>
+      </c>
+      <c r="C734" t="n">
+        <v>209.35</v>
+      </c>
+      <c r="D734" t="n">
+        <v>209.65</v>
+      </c>
+      <c r="E734" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F734" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:30:26</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>SENSEX2631278100CE</t>
+        </is>
+      </c>
+      <c r="C735" t="n">
+        <v>213.15</v>
+      </c>
+      <c r="D735" t="n">
+        <v>213.15</v>
+      </c>
+      <c r="E735" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F735" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-03-11 13:30:35</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>SENSEX2631278100CE</t>
+        </is>
+      </c>
+      <c r="C736" t="n">
+        <v>217.8</v>
+      </c>
+      <c r="D736" t="n">
+        <v>218.65</v>
+      </c>
+      <c r="E736" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F736" t="n">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-03-12 11:55:59</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>NIFTY2631724000CE</t>
+        </is>
+      </c>
+      <c r="C737" t="n">
+        <v>142.55</v>
+      </c>
+      <c r="D737" t="n">
+        <v>142.35</v>
+      </c>
+      <c r="E737" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F737" t="n">
+        <v>-260</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-03-12 11:56:51</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>NIFTY2631724000CE</t>
+        </is>
+      </c>
+      <c r="C738" t="n">
+        <v>144.75</v>
+      </c>
+      <c r="D738" t="n">
+        <v>146.5</v>
+      </c>
+      <c r="E738" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F738" t="n">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-03-12 11:57:24</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>NIFTY2631724000CE</t>
+        </is>
+      </c>
+      <c r="C739" t="n">
+        <v>149.8</v>
+      </c>
+      <c r="D739" t="n">
+        <v>150.2</v>
+      </c>
+      <c r="E739" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F739" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-03-12 11:58:23</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>SENSEX2631276600CE</t>
+        </is>
+      </c>
+      <c r="C740" t="n">
+        <v>149.1</v>
+      </c>
+      <c r="D740" t="n">
+        <v>152.25</v>
+      </c>
+      <c r="E740" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F740" t="n">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-03-12 11:59:07</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>SENSEX2631276600CE</t>
+        </is>
+      </c>
+      <c r="C741" t="n">
+        <v>154.95</v>
+      </c>
+      <c r="D741" t="n">
+        <v>151.65</v>
+      </c>
+      <c r="E741" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F741" t="n">
+        <v>-3300</v>
       </c>
     </row>
   </sheetData>

--- a/Lakshmi.xlsx
+++ b/Lakshmi.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H741"/>
+  <dimension ref="A1:H764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="24.33203125" customWidth="1" style="1" min="1" max="1"/>
@@ -20973,6 +20973,558 @@
       </c>
       <c r="F741" t="n">
         <v>-3300</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-03-12 12:18:26</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>NIFTY2631723500PE</t>
+        </is>
+      </c>
+      <c r="C742" t="n">
+        <v>156.35</v>
+      </c>
+      <c r="D742" t="n">
+        <v>156</v>
+      </c>
+      <c r="E742" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F742" t="n">
+        <v>-455</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-03-12 12:19:10</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>NIFTY2631723500PE</t>
+        </is>
+      </c>
+      <c r="C743" t="n">
+        <v>156.05</v>
+      </c>
+      <c r="D743" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="E743" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F743" t="n">
+        <v>2665</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-03-12 12:19:42</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>NIFTY2631723500PE</t>
+        </is>
+      </c>
+      <c r="C744" t="n">
+        <v>160.25</v>
+      </c>
+      <c r="D744" t="n">
+        <v>161.9</v>
+      </c>
+      <c r="E744" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F744" t="n">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-03-12 12:30:49</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>SENSEX2631276500PE</t>
+        </is>
+      </c>
+      <c r="C745" t="n">
+        <v>201.05</v>
+      </c>
+      <c r="D745" t="n">
+        <v>206.35</v>
+      </c>
+      <c r="E745" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F745" t="n">
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-03-12 12:31:13</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>SENSEX2631276500PE</t>
+        </is>
+      </c>
+      <c r="C746" t="n">
+        <v>205.05</v>
+      </c>
+      <c r="D746" t="n">
+        <v>206.9</v>
+      </c>
+      <c r="E746" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F746" t="n">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-03-12 12:31:39</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>SENSEX2631276500PE</t>
+        </is>
+      </c>
+      <c r="C747" t="n">
+        <v>204.4</v>
+      </c>
+      <c r="D747" t="n">
+        <v>206</v>
+      </c>
+      <c r="E747" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F747" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-03-12 12:32:19</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>SENSEX2631276500PE</t>
+        </is>
+      </c>
+      <c r="C748" t="n">
+        <v>206.4</v>
+      </c>
+      <c r="D748" t="n">
+        <v>215</v>
+      </c>
+      <c r="E748" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F748" t="n">
+        <v>8600</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-03-12 12:32:51</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>SENSEX2631276500PE</t>
+        </is>
+      </c>
+      <c r="C749" t="n">
+        <v>209.75</v>
+      </c>
+      <c r="D749" t="n">
+        <v>212.35</v>
+      </c>
+      <c r="E749" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F749" t="n">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-03-12 12:33:03</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>SENSEX2631276500PE</t>
+        </is>
+      </c>
+      <c r="C750" t="n">
+        <v>218.4</v>
+      </c>
+      <c r="D750" t="n">
+        <v>219</v>
+      </c>
+      <c r="E750" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F750" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-03-12 12:33:11</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>SENSEX2631276500PE</t>
+        </is>
+      </c>
+      <c r="C751" t="n">
+        <v>224.3</v>
+      </c>
+      <c r="D751" t="n">
+        <v>222.9</v>
+      </c>
+      <c r="E751" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F751" t="n">
+        <v>-1400</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-03-12 12:33:19</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>SENSEX2631276500PE</t>
+        </is>
+      </c>
+      <c r="C752" t="n">
+        <v>224</v>
+      </c>
+      <c r="D752" t="n">
+        <v>225.1</v>
+      </c>
+      <c r="E752" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F752" t="n">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-03-12 12:33:31</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>SENSEX2631276500PE</t>
+        </is>
+      </c>
+      <c r="C753" t="n">
+        <v>228</v>
+      </c>
+      <c r="D753" t="n">
+        <v>234.5</v>
+      </c>
+      <c r="E753" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F753" t="n">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-03-12 12:33:39</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>SENSEX2631276500PE</t>
+        </is>
+      </c>
+      <c r="C754" t="n">
+        <v>233</v>
+      </c>
+      <c r="D754" t="n">
+        <v>233.15</v>
+      </c>
+      <c r="E754" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F754" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-03-12 12:34:13</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>SENSEX2631276500PE</t>
+        </is>
+      </c>
+      <c r="C755" t="n">
+        <v>249.4</v>
+      </c>
+      <c r="D755" t="n">
+        <v>239.95</v>
+      </c>
+      <c r="E755" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F755" t="n">
+        <v>-9450</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-03-13 10:55:48</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>NIFTY2631722900PE</t>
+        </is>
+      </c>
+      <c r="C756" t="n">
+        <v>87</v>
+      </c>
+      <c r="D756" t="n">
+        <v>87.25</v>
+      </c>
+      <c r="E756" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F756" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-03-13 10:58:02</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>NIFTY2631722900PE</t>
+        </is>
+      </c>
+      <c r="C757" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="D757" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="E757" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F757" t="n">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-03-13 12:24:39</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>NIFTY2631723150PE</t>
+        </is>
+      </c>
+      <c r="C758" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="D758" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="E758" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F758" t="n">
+        <v>3510</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-03-13 12:25:01</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>NIFTY2631723150PE</t>
+        </is>
+      </c>
+      <c r="C759" t="n">
+        <v>185.3</v>
+      </c>
+      <c r="D759" t="n">
+        <v>188.4</v>
+      </c>
+      <c r="E759" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F759" t="n">
+        <v>4030</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-03-13 12:25:14</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>NIFTY2631723150PE</t>
+        </is>
+      </c>
+      <c r="C760" t="n">
+        <v>188.1</v>
+      </c>
+      <c r="D760" t="n">
+        <v>188.8</v>
+      </c>
+      <c r="E760" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F760" t="n">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-03-13 12:26:58</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>NIFTY2631723150PE</t>
+        </is>
+      </c>
+      <c r="C761" t="n">
+        <v>189.65</v>
+      </c>
+      <c r="D761" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="E761" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F761" t="n">
+        <v>-11765</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-03-13 12:31:23</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>NIFTY2631723400CE</t>
+        </is>
+      </c>
+      <c r="C762" t="n">
+        <v>190.45</v>
+      </c>
+      <c r="D762" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="E762" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F762" t="n">
+        <v>-12610</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-03-13 12:32:04</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>NIFTY2631723150PE</t>
+        </is>
+      </c>
+      <c r="C763" t="n">
+        <v>204.8</v>
+      </c>
+      <c r="D763" t="n">
+        <v>206.55</v>
+      </c>
+      <c r="E763" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F763" t="n">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-03-13 12:32:33</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>NIFTY2631723150PE</t>
+        </is>
+      </c>
+      <c r="C764" t="n">
+        <v>211.25</v>
+      </c>
+      <c r="D764" t="n">
+        <v>201.75</v>
+      </c>
+      <c r="E764" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F764" t="n">
+        <v>-12350</v>
       </c>
     </row>
   </sheetData>

--- a/Lakshmi.xlsx
+++ b/Lakshmi.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H766"/>
+  <dimension ref="A1:H835"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="24.33203125" customWidth="1" style="1" min="1" max="1"/>
@@ -21574,6 +21574,1902 @@
       </c>
       <c r="F766" t="n">
         <v>1665.3</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-04-13 10:26:29</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>NIFTY2641323600CE</t>
+        </is>
+      </c>
+      <c r="C767" t="n">
+        <v>135.27</v>
+      </c>
+      <c r="D767" t="n">
+        <v>138.15</v>
+      </c>
+      <c r="E767" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F767" t="n">
+        <v>3369.6</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-04-13 10:27:20</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>NIFTY2641323600CE</t>
+        </is>
+      </c>
+      <c r="C768" t="n">
+        <v>145.34</v>
+      </c>
+      <c r="D768" t="n">
+        <v>148.27</v>
+      </c>
+      <c r="E768" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F768" t="n">
+        <v>3428.1</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-04-13 10:29:28</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>NIFTY2641323650CE</t>
+        </is>
+      </c>
+      <c r="C769" t="n">
+        <v>108.87</v>
+      </c>
+      <c r="D769" t="n">
+        <v>112.04</v>
+      </c>
+      <c r="E769" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F769" t="n">
+        <v>4121</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-04-13 10:57:06</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>NIFTY2641323650CE</t>
+        </is>
+      </c>
+      <c r="C770" t="n">
+        <v>122.09</v>
+      </c>
+      <c r="D770" t="n">
+        <v>127.86</v>
+      </c>
+      <c r="E770" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F770" t="n">
+        <v>6000.8</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:25:47</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>NIFTY2641323650CE</t>
+        </is>
+      </c>
+      <c r="C771" t="n">
+        <v>119.61</v>
+      </c>
+      <c r="D771" t="n">
+        <v>122.99</v>
+      </c>
+      <c r="E771" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F771" t="n">
+        <v>3515.2</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:39:12</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>NIFTY2641323650CE</t>
+        </is>
+      </c>
+      <c r="C772" t="n">
+        <v>128.54</v>
+      </c>
+      <c r="D772" t="n">
+        <v>130.26</v>
+      </c>
+      <c r="E772" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F772" t="n">
+        <v>1788.8</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:40:37</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>NIFTY2641323650CE</t>
+        </is>
+      </c>
+      <c r="C773" t="n">
+        <v>127.12</v>
+      </c>
+      <c r="D773" t="n">
+        <v>127.58</v>
+      </c>
+      <c r="E773" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F773" t="n">
+        <v>478.4</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:41:38</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>NIFTY2641323650CE</t>
+        </is>
+      </c>
+      <c r="C774" t="n">
+        <v>124.32</v>
+      </c>
+      <c r="D774" t="n">
+        <v>124.55</v>
+      </c>
+      <c r="E774" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F774" t="n">
+        <v>239.2</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:45:59</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>NIFTY2641323650CE</t>
+        </is>
+      </c>
+      <c r="C775" t="n">
+        <v>125</v>
+      </c>
+      <c r="D775" t="n">
+        <v>127.27</v>
+      </c>
+      <c r="E775" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F775" t="n">
+        <v>2360.8</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:46:32</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>NIFTY2641323650CE</t>
+        </is>
+      </c>
+      <c r="C776" t="n">
+        <v>132.46</v>
+      </c>
+      <c r="D776" t="n">
+        <v>132.26</v>
+      </c>
+      <c r="E776" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F776" t="n">
+        <v>-208</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:50:03</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>NIFTY2641323650CE</t>
+        </is>
+      </c>
+      <c r="C777" t="n">
+        <v>134.71</v>
+      </c>
+      <c r="D777" t="n">
+        <v>145.13</v>
+      </c>
+      <c r="E777" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F777" t="n">
+        <v>10836.8</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:54:42</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>NIFTY2641323700CE</t>
+        </is>
+      </c>
+      <c r="C778" t="n">
+        <v>119.08</v>
+      </c>
+      <c r="D778" t="n">
+        <v>119.51</v>
+      </c>
+      <c r="E778" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F778" t="n">
+        <v>447.2</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:58:00</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>NIFTY2641323700CE</t>
+        </is>
+      </c>
+      <c r="C779" t="n">
+        <v>137.48</v>
+      </c>
+      <c r="D779" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="E779" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F779" t="n">
+        <v>-19427.2</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:01:08</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>NIFTY2641323700CE</t>
+        </is>
+      </c>
+      <c r="C780" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="D780" t="n">
+        <v>120.97</v>
+      </c>
+      <c r="E780" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F780" t="n">
+        <v>72.8</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:06:58</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>NIFTY2641323700CE</t>
+        </is>
+      </c>
+      <c r="C781" t="n">
+        <v>124.87</v>
+      </c>
+      <c r="D781" t="n">
+        <v>126.68</v>
+      </c>
+      <c r="E781" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F781" t="n">
+        <v>1882.4</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:10:23</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>NIFTY2641323700CE</t>
+        </is>
+      </c>
+      <c r="C782" t="n">
+        <v>124.8</v>
+      </c>
+      <c r="D782" t="n">
+        <v>125.09</v>
+      </c>
+      <c r="E782" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F782" t="n">
+        <v>301.6</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:25:57</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>NIFTY2641323700CE</t>
+        </is>
+      </c>
+      <c r="C783" t="n">
+        <v>130.89</v>
+      </c>
+      <c r="D783" t="n">
+        <v>131.53</v>
+      </c>
+      <c r="E783" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F783" t="n">
+        <v>665.6</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:27:00</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>NIFTY2641323700CE</t>
+        </is>
+      </c>
+      <c r="C784" t="n">
+        <v>133.48</v>
+      </c>
+      <c r="D784" t="n">
+        <v>146.25</v>
+      </c>
+      <c r="E784" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F784" t="n">
+        <v>13280.8</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-04-27 09:37:50</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24050CE</t>
+        </is>
+      </c>
+      <c r="C785" t="n">
+        <v>111.39</v>
+      </c>
+      <c r="D785" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="E785" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F785" t="n">
+        <v>1362.4</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-04-27 09:43:41</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24000PE</t>
+        </is>
+      </c>
+      <c r="C786" t="n">
+        <v>110</v>
+      </c>
+      <c r="D786" t="n">
+        <v>93.89</v>
+      </c>
+      <c r="E786" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F786" t="n">
+        <v>-16754.4</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-04-27 12:13:32</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24000CE</t>
+        </is>
+      </c>
+      <c r="C787" t="n">
+        <v>129.35</v>
+      </c>
+      <c r="D787" t="n">
+        <v>132.9</v>
+      </c>
+      <c r="E787" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F787" t="n">
+        <v>4615</v>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-04-27 12:14:01</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24000CE</t>
+        </is>
+      </c>
+      <c r="C788" t="n">
+        <v>130.65</v>
+      </c>
+      <c r="D788" t="n">
+        <v>131.35</v>
+      </c>
+      <c r="E788" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F788" t="n">
+        <v>910</v>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-04-27 12:14:37</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24000CE</t>
+        </is>
+      </c>
+      <c r="C789" t="n">
+        <v>129.85</v>
+      </c>
+      <c r="D789" t="n">
+        <v>131.45</v>
+      </c>
+      <c r="E789" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F789" t="n">
+        <v>2080</v>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-04-27 12:19:27</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100PE</t>
+        </is>
+      </c>
+      <c r="C790" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="D790" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="E790" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F790" t="n">
+        <v>-9880</v>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-04-27 12:26:41</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24050CE</t>
+        </is>
+      </c>
+      <c r="C791" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="D791" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="E791" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F791" t="n">
+        <v>1820</v>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-04-27 12:27:13</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24050CE</t>
+        </is>
+      </c>
+      <c r="C792" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="D792" t="n">
+        <v>109.05</v>
+      </c>
+      <c r="E792" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F792" t="n">
+        <v>1755</v>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-04-27 12:28:55</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24050CE</t>
+        </is>
+      </c>
+      <c r="C793" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="D793" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="E793" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F793" t="n">
+        <v>585</v>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-04-27 12:31:47</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24050CE</t>
+        </is>
+      </c>
+      <c r="C794" t="n">
+        <v>110.4</v>
+      </c>
+      <c r="D794" t="n">
+        <v>110.95</v>
+      </c>
+      <c r="E794" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F794" t="n">
+        <v>715</v>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-04-27 12:34:36</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24050CE</t>
+        </is>
+      </c>
+      <c r="C795" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="D795" t="n">
+        <v>120.45</v>
+      </c>
+      <c r="E795" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F795" t="n">
+        <v>3965</v>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-04-27 12:35:02</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24050CE</t>
+        </is>
+      </c>
+      <c r="C796" t="n">
+        <v>120.35</v>
+      </c>
+      <c r="D796" t="n">
+        <v>121.15</v>
+      </c>
+      <c r="E796" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F796" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-04-27 12:35:36</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24050CE</t>
+        </is>
+      </c>
+      <c r="C797" t="n">
+        <v>121.3</v>
+      </c>
+      <c r="D797" t="n">
+        <v>123</v>
+      </c>
+      <c r="E797" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F797" t="n">
+        <v>2210</v>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-04-27 12:36:40</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24050CE</t>
+        </is>
+      </c>
+      <c r="C798" t="n">
+        <v>125.65</v>
+      </c>
+      <c r="D798" t="n">
+        <v>128.2</v>
+      </c>
+      <c r="E798" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F798" t="n">
+        <v>3315</v>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-04-27 12:38:21</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C799" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="D799" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="E799" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F799" t="n">
+        <v>-9620</v>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:01:43</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24050CE</t>
+        </is>
+      </c>
+      <c r="C800" t="n">
+        <v>118</v>
+      </c>
+      <c r="D800" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="E800" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F800" t="n">
+        <v>-520</v>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:02:01</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24050CE</t>
+        </is>
+      </c>
+      <c r="C801" t="n">
+        <v>118.55</v>
+      </c>
+      <c r="D801" t="n">
+        <v>119.3</v>
+      </c>
+      <c r="E801" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F801" t="n">
+        <v>975</v>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:03:01</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24050CE</t>
+        </is>
+      </c>
+      <c r="C802" t="n">
+        <v>120.65</v>
+      </c>
+      <c r="D802" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="E802" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F802" t="n">
+        <v>2275</v>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:03:33</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24050CE</t>
+        </is>
+      </c>
+      <c r="C803" t="n">
+        <v>121.3</v>
+      </c>
+      <c r="D803" t="n">
+        <v>124.05</v>
+      </c>
+      <c r="E803" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F803" t="n">
+        <v>3575</v>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:12:25</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>NIFTY26APR23950CE</t>
+        </is>
+      </c>
+      <c r="C804" t="n">
+        <v>187.3</v>
+      </c>
+      <c r="D804" t="n">
+        <v>186.35</v>
+      </c>
+      <c r="E804" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F804" t="n">
+        <v>-1235</v>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:13:20</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24050CE</t>
+        </is>
+      </c>
+      <c r="C805" t="n">
+        <v>123.8</v>
+      </c>
+      <c r="D805" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="E805" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F805" t="n">
+        <v>130</v>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:13:38</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24050CE</t>
+        </is>
+      </c>
+      <c r="C806" t="n">
+        <v>125.65</v>
+      </c>
+      <c r="D806" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="E806" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F806" t="n">
+        <v>1885</v>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:14:31</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24050CE</t>
+        </is>
+      </c>
+      <c r="C807" t="n">
+        <v>129.55</v>
+      </c>
+      <c r="D807" t="n">
+        <v>131.25</v>
+      </c>
+      <c r="E807" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F807" t="n">
+        <v>2210</v>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:15:36</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C808" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="D808" t="n">
+        <v>103</v>
+      </c>
+      <c r="E808" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F808" t="n">
+        <v>-390</v>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:16:57</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C809" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="D809" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="E809" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F809" t="n">
+        <v>4810</v>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:17:18</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C810" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="D810" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="E810" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F810" t="n">
+        <v>650</v>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:22:21</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C811" t="n">
+        <v>101</v>
+      </c>
+      <c r="D811" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="E811" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F811" t="n">
+        <v>3445</v>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:23:04</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C812" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="D812" t="n">
+        <v>105.9</v>
+      </c>
+      <c r="E812" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F812" t="n">
+        <v>1105</v>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:23:33</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C813" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="D813" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="E813" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F813" t="n">
+        <v>390</v>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:27:19</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C814" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="D814" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="E814" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F814" t="n">
+        <v>2535</v>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:27:39</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C815" t="n">
+        <v>112.35</v>
+      </c>
+      <c r="D815" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="E815" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F815" t="n">
+        <v>1625</v>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:28:21</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C816" t="n">
+        <v>112.7</v>
+      </c>
+      <c r="D816" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="E816" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F816" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:32:30</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24150PE</t>
+        </is>
+      </c>
+      <c r="C817" t="n">
+        <v>119.75</v>
+      </c>
+      <c r="D817" t="n">
+        <v>121.1</v>
+      </c>
+      <c r="E817" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F817" t="n">
+        <v>1755</v>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:33:28</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C818" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="D818" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="E818" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F818" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:34:15</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C819" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="D819" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="E819" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F819" t="n">
+        <v>910</v>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:35:27</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C820" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="D820" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="E820" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F820" t="n">
+        <v>3575</v>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:37:35</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C821" t="n">
+        <v>112.05</v>
+      </c>
+      <c r="D821" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="E821" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F821" t="n">
+        <v>-11115</v>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:40:37</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C822" t="n">
+        <v>107</v>
+      </c>
+      <c r="D822" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="E822" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F822" t="n">
+        <v>3640</v>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:42:03</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C823" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="D823" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="E823" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F823" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:42:59</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C824" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="D824" t="n">
+        <v>111.55</v>
+      </c>
+      <c r="E824" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F824" t="n">
+        <v>325</v>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:43:16</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C825" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="D825" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="E825" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F825" t="n">
+        <v>975</v>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>2026-04-27 13:49:41</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C826" t="n">
+        <v>111.75</v>
+      </c>
+      <c r="D826" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="E826" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F826" t="n">
+        <v>-11635</v>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>2026-04-27 14:17:31</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C827" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="D827" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="E827" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F827" t="n">
+        <v>260</v>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>2026-04-27 14:17:46</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C828" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="D828" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="E828" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F828" t="n">
+        <v>65</v>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>2026-04-27 14:19:16</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C829" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="D829" t="n">
+        <v>113.45</v>
+      </c>
+      <c r="E829" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F829" t="n">
+        <v>455</v>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>2026-04-28 10:25:10</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C830" t="n">
+        <v>83.06</v>
+      </c>
+      <c r="D830" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="E830" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F830" t="n">
+        <v>353.6</v>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>2026-04-28 10:26:11</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C831" t="n">
+        <v>87.56999999999999</v>
+      </c>
+      <c r="D831" t="n">
+        <v>88.43000000000001</v>
+      </c>
+      <c r="E831" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F831" t="n">
+        <v>894.4</v>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>2026-04-28 10:28:10</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C832" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="D832" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="E832" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F832" t="n">
+        <v>-10244</v>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>2026-04-28 10:30:26</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>NIFTY26APR24100CE</t>
+        </is>
+      </c>
+      <c r="C833" t="n">
+        <v>81.55</v>
+      </c>
+      <c r="D833" t="n">
+        <v>81.78</v>
+      </c>
+      <c r="E833" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F833" t="n">
+        <v>239.2</v>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>2026-04-28 15:25:52</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>NIFTY2650523650PE</t>
+        </is>
+      </c>
+      <c r="C834" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="D834" t="n">
+        <v>83.75</v>
+      </c>
+      <c r="E834" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F834" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-05-06 14:09:12</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>SENSEX2650778000CE</t>
+        </is>
+      </c>
+      <c r="C835" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="D835" t="n">
+        <v>84.89</v>
+      </c>
+      <c r="E835" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F835" t="n">
+        <v>-10210</v>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -21688,7 +23584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H389"/>
+  <dimension ref="A1:H613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34149,6 +36045,7174 @@
         </is>
       </c>
     </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:44:16</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="C390" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="D390" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="E390" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="F390" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>⏳ WAIT</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Collecting data...</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:45:21</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="C391" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="D391" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="E391" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F391" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>⏳ WAIT</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>Collecting data...</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:46:26</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="C392" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="D392" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E392" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="F392" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.04%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:47:31</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="C393" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="D393" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E393" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="F393" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.02%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:48:37</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="C394" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="D394" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="E394" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="F394" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.04%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:49:42</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="C395" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="D395" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="E395" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="F395" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.04%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:50:47</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="C396" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="D396" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="E396" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="F396" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.04%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:51:52</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C397" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="D397" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E397" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="F397" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.07%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:52:57</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="C398" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="D398" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="E398" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="F398" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:54:02</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="C399" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="D399" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="E399" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="F399" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:55:07</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="C400" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="D400" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="E400" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="F400" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:56:12</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="C401" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="D401" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="E401" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="F401" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.07%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:57:17</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="C402" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="D402" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="E402" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="F402" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:58:22</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="C403" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="D403" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="E403" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="F403" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.04%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-04-13 11:59:27</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="C404" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="D404" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="E404" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="F404" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.02%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:00:32</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="C405" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="D405" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="E405" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="F405" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:01:36</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C406" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="D406" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="E406" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="F406" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:02:41</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C407" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="D407" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E407" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="F407" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:03:46</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C408" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="D408" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="E408" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="F408" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:04:51</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="C409" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="D409" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="E409" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="F409" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:05:56</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="C410" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="D410" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E410" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="F410" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:07:01</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="C411" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="D411" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="E411" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F411" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:08:06</t>
+        </is>
+      </c>
+      <c r="B412" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="C412" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="D412" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="E412" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="F412" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:09:11</t>
+        </is>
+      </c>
+      <c r="B413" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="C413" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="D413" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E413" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="F413" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.02%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:10:16</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="C414" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="D414" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="E414" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="F414" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:11:21</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="C415" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="D415" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="E415" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F415" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.02%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:12:26</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="C416" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="D416" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="E416" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="F416" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:13:31</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="C417" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="D417" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="E417" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="F417" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.05%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:14:37</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="C418" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="D418" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E418" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="F418" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:15:42</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="C419" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="D419" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="E419" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="F419" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.05%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:16:47</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="C420" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="D420" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E420" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F420" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:17:52</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="C421" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="D421" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E421" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F421" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:18:57</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="C422" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="D422" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="E422" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="F422" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:20:03</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C423" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="D423" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="E423" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="F423" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:21:08</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="C424" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="D424" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="E424" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="F424" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:22:13</t>
+        </is>
+      </c>
+      <c r="B425" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="C425" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="D425" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E425" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="F425" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:23:18</t>
+        </is>
+      </c>
+      <c r="B426" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="C426" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="D426" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="E426" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="F426" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.05%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:24:23</t>
+        </is>
+      </c>
+      <c r="B427" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="C427" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="D427" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="E427" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="F427" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.05%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:25:29</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="C428" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="D428" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="E428" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="F428" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:26:34</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="C429" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="D429" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="E429" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="F429" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:27:39</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="C430" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="D430" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="E430" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="F430" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.05%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:28:45</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="C431" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="D431" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="E431" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="F431" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.05%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-04-13 12:29:50</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="C432" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="D432" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="E432" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="F432" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-04-15 09:48:16</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C433" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="D433" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="E433" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F433" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>⏳ WAIT</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>Collecting data...</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-04-15 09:49:21</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C434" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="D434" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E434" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="F434" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>⏳ WAIT</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Collecting data...</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-04-15 09:50:26</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="C435" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="D435" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="E435" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F435" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.08%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-04-15 09:51:31</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C436" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="D436" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="E436" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="F436" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.04%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-04-15 09:52:35</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="C437" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D437" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E437" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F437" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-04-15 09:53:41</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="C438" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="D438" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E438" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F438" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.09%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-04-15 09:54:48</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="C439" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="D439" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E439" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F439" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.08%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-04-15 09:55:52</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="C440" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="D440" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E440" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F440" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-04-15 09:56:58</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="C441" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="D441" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="E441" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F441" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-04-15 09:58:03</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="C442" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D442" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="E442" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="F442" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-04-15 09:59:08</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="C443" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="D443" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="E443" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="F443" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:00:12</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="C444" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="D444" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="E444" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="F444" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:01:17</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C445" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="D445" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E445" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F445" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:02:31</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C446" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="D446" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E446" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="F446" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:03:35</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="C447" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="D447" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E447" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="F447" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:04:40</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="C448" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="D448" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E448" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="F448" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:05:45</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="C449" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D449" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="E449" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F449" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.04%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:06:50</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C450" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="D450" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="E450" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F450" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.04%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:07:54</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C451" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D451" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="E451" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="F451" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.05%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:08:59</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C452" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D452" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E452" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F452" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:10:04</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C453" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="D453" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="E453" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F453" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:11:09</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="C454" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="D454" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="E454" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="F454" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:12:13</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C455" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="D455" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="E455" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F455" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:13:18</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="C456" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D456" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E456" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F456" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:14:23</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C457" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D457" t="n">
+        <v>2</v>
+      </c>
+      <c r="E457" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="F457" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:15:27</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C458" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="D458" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E458" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="F458" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:16:32</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C459" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="D459" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E459" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="F459" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:17:37</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>2</v>
+      </c>
+      <c r="C460" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="D460" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="E460" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="F460" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.04%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:18:42</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>2</v>
+      </c>
+      <c r="C461" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="D461" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E461" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="F461" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:19:47</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="C462" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="D462" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E462" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F462" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:20:51</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C463" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="D463" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E463" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F463" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:21:56</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="C464" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="D464" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E464" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F464" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:23:01</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="C465" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="D465" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E465" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F465" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:24:06</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C466" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="D466" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E466" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F466" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:25:11</t>
+        </is>
+      </c>
+      <c r="B467" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="C467" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="D467" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E467" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F467" t="n">
+        <v>2</v>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.06%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:26:15</t>
+        </is>
+      </c>
+      <c r="B468" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="C468" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="D468" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E468" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F468" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:27:20</t>
+        </is>
+      </c>
+      <c r="B469" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="C469" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="D469" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E469" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="F469" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:28:25</t>
+        </is>
+      </c>
+      <c r="B470" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="C470" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="D470" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E470" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F470" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:29:30</t>
+        </is>
+      </c>
+      <c r="B471" t="n">
+        <v>2</v>
+      </c>
+      <c r="C471" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="D471" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E471" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F471" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:30:37</t>
+        </is>
+      </c>
+      <c r="B472" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C472" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="D472" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E472" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F472" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:31:41</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C473" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="D473" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E473" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F473" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:32:46</t>
+        </is>
+      </c>
+      <c r="B474" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="C474" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="D474" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E474" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F474" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:33:51</t>
+        </is>
+      </c>
+      <c r="B475" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="C475" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="D475" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E475" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F475" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:34:56</t>
+        </is>
+      </c>
+      <c r="B476" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C476" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="D476" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E476" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="F476" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:36:01</t>
+        </is>
+      </c>
+      <c r="B477" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="C477" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="D477" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E477" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F477" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:37:06</t>
+        </is>
+      </c>
+      <c r="B478" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C478" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="D478" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E478" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F478" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:38:10</t>
+        </is>
+      </c>
+      <c r="B479" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="C479" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="D479" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E479" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F479" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:39:15</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C480" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="D480" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E480" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F480" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:40:20</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="C481" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D481" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E481" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F481" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:41:28</t>
+        </is>
+      </c>
+      <c r="B482" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="C482" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D482" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E482" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F482" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:42:33</t>
+        </is>
+      </c>
+      <c r="B483" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="C483" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="D483" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E483" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F483" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:43:54</t>
+        </is>
+      </c>
+      <c r="B484" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="C484" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D484" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="E484" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F484" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:45:04</t>
+        </is>
+      </c>
+      <c r="B485" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="C485" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="D485" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E485" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F485" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:46:09</t>
+        </is>
+      </c>
+      <c r="B486" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="C486" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="D486" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E486" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F486" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:47:14</t>
+        </is>
+      </c>
+      <c r="B487" t="n">
+        <v>2</v>
+      </c>
+      <c r="C487" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="D487" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E487" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F487" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:48:18</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="C488" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="D488" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E488" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F488" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:49:23</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="C489" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D489" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E489" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F489" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.02%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:50:28</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="C490" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D490" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E490" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F490" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:51:33</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C491" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="D491" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E491" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="F491" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:52:38</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="C492" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D492" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E492" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="F492" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.10%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:53:43</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="C493" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="D493" t="n">
+        <v>2</v>
+      </c>
+      <c r="E493" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="F493" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.04%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:54:48</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="C494" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="D494" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="E494" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F494" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.06%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:55:53</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C495" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="D495" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E495" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F495" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:56:57</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="C496" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="D496" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E496" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F496" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.05%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:58:02</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="C497" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="D497" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E497" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F497" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-04-15 10:59:07</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C498" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D498" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E498" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="F498" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.02%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:00:12</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="C499" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="D499" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E499" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F499" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:01:17</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="C500" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="D500" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="E500" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F500" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.06%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:02:21</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C501" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="D501" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E501" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F501" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:03:26</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C502" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="D502" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E502" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F502" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-04-15 11:04:31</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="C503" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="D503" t="n">
+        <v>2</v>
+      </c>
+      <c r="E503" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="F503" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:36:57</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C504" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="D504" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E504" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F504" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>⏳ WAIT</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>Collecting data...</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:38:02</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C505" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="D505" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E505" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F505" t="n">
+        <v>0</v>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>⏳ WAIT</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>Collecting data...</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:39:07</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C506" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="D506" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E506" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F506" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:40:12</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C507" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="D507" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E507" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F507" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:41:17</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C508" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="D508" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E508" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F508" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:42:22</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C509" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="D509" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E509" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F509" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:43:27</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C510" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="D510" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E510" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="F510" t="n">
+        <v>0</v>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:44:31</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C511" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="D511" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E511" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F511" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.02%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:45:36</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C512" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="D512" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E512" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="F512" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:46:41</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="C513" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D513" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E513" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="F513" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.06%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:47:46</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C514" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="D514" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E514" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F514" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.05%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:48:50</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C515" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="D515" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E515" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="F515" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.04%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:49:56</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="C516" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="D516" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E516" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="F516" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:51:03</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C517" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="D517" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E517" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="F517" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:52:09</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="C518" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D518" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E518" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="F518" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:53:13</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="C519" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="D519" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E519" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="F519" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:54:18</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="C520" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D520" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E520" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F520" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:55:23</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C521" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="D521" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E521" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="F521" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:56:28</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C522" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="D522" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E522" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="F522" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:57:32</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C523" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="D523" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E523" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F523" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:58:37</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="C524" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="D524" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E524" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F524" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-04-22 11:59:42</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C525" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="D525" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E525" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F525" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.05%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:00:47</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C526" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="D526" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E526" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F526" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.05%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:01:52</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C527" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="D527" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E527" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F527" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:02:56</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C528" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="D528" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E528" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F528" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:04:01</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C529" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="D529" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E529" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="F529" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:05:06</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C530" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="D530" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E530" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F530" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:06:11</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C531" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D531" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E531" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F531" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:07:15</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C532" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="D532" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E532" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="F532" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:08:20</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C533" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="D533" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E533" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F533" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:09:25</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C534" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="D534" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E534" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F534" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:10:31</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C535" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="D535" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E535" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F535" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:11:36</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C536" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="D536" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E536" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F536" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:12:40</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C537" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="D537" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E537" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F537" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:13:45</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C538" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="D538" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E538" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F538" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:14:50</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C539" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="D539" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E539" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F539" t="n">
+        <v>0</v>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:15:55</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C540" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="D540" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E540" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F540" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:17:00</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C541" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D541" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E541" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="F541" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.02%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:18:04</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C542" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="D542" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E542" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F542" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:19:09</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C543" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="D543" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E543" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F543" t="n">
+        <v>0</v>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:20:14</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C544" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D544" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E544" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F544" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.02%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:21:18</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C545" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D545" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E545" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F545" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:22:23</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C546" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="D546" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E546" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F546" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:23:28</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C547" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="D547" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E547" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="F547" t="n">
+        <v>0</v>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:24:37</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C548" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D548" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E548" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F548" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.02%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:25:46</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C549" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D549" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E549" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F549" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:26:51</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C550" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="D550" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E550" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F550" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:27:55</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C551" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="D551" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E551" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="F551" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:29:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C552" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D552" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E552" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="F552" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:30:05</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C553" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="D553" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E553" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F553" t="n">
+        <v>0</v>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:31:09</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C554" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="D554" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E554" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F554" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:32:14</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C555" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="D555" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E555" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F555" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:33:19</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C556" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="D556" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E556" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F556" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:34:23</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C557" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="D557" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E557" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F557" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:35:28</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C558" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="D558" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E558" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F558" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:36:33</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C559" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="D559" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E559" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F559" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:37:38</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C560" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="D560" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E560" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F560" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:38:42</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C561" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="D561" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E561" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="F561" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:39:47</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C562" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="D562" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E562" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F562" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:40:52</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C563" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="D563" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E563" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F563" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:41:57</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C564" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="D564" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E564" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="F564" t="n">
+        <v>0</v>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:43:02</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C565" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="D565" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E565" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F565" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:44:06</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C566" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="D566" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E566" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F566" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:45:11</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C567" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="D567" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E567" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F567" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:46:16</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C568" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="D568" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E568" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F568" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.02%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:47:21</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C569" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="D569" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E569" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F569" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:48:26</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C570" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="D570" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E570" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="F570" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.04%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:49:30</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C571" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D571" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E571" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="F571" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:50:36</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C572" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="D572" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E572" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F572" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.02%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:51:41</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C573" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="D573" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E573" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="F573" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:52:46</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C574" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="D574" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E574" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="F574" t="n">
+        <v>0</v>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:53:51</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C575" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="D575" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E575" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F575" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.04%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:54:55</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="C576" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="D576" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E576" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F576" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:56:00</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C577" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="D577" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E577" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F577" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:57:05</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C578" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="D578" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E578" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F578" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:58:10</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C579" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="D579" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E579" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F579" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:59:15</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C580" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="D580" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E580" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F580" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:00:19</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C581" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="D581" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E581" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F581" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:01:24</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C582" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="D582" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E582" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F582" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:02:29</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C583" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="D583" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E583" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F583" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:03:34</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C584" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="D584" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E584" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F584" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:04:39</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C585" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="D585" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E585" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F585" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:05:43</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C586" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="D586" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E586" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F586" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:06:48</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C587" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="D587" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E587" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F587" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.04%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:07:53</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C588" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D588" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E588" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="F588" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:08:58</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C589" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="D589" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E589" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="F589" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:10:02</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C590" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="D590" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E590" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F590" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:11:07</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="C591" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="D591" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E591" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F591" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:12:12</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C592" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="D592" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E592" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F592" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.02%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:13:17</t>
+        </is>
+      </c>
+      <c r="B593" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C593" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="D593" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E593" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F593" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:14:22</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C594" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="D594" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E594" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F594" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:15:26</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="C595" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="D595" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E595" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F595" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:16:31</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C596" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="D596" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E596" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="F596" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:17:36</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C597" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="D597" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E597" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F597" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:18:41</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C598" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="D598" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E598" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F598" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.04%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:19:46</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C599" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="D599" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E599" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="F599" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.04%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:20:51</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C600" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="D600" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E600" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F600" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:21:56</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C601" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D601" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E601" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="F601" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.04%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:23:01</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C602" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D602" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E602" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F602" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.04%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:24:06</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="C603" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="D603" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E603" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="F603" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>🟠 BUY PUT</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>Moderate bearish trend (-0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:25:10</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="C604" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="D604" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E604" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="F604" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:26:15</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C605" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D605" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E605" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F605" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:27:20</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C606" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="D606" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E606" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="F606" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.02%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:28:25</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C607" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="D607" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E607" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="F607" t="n">
+        <v>0</v>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:29:29</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="C608" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="D608" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E608" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F608" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.03%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:30:34</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C609" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="D609" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E609" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F609" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>🟡 BUY CALL</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>Moderate bullish trend (+0.04%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:31:39</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C610" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="D610" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E610" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F610" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:32:43</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C611" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="D611" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E611" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="F611" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:33:48</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C612" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D612" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E612" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="F612" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:34:53</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C613" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="D613" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E613" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F613" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>⚪ NEUTRAL</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>No clear directional bias</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Lakshmi.xlsx
+++ b/Lakshmi.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H835"/>
+  <dimension ref="A1:H889"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="24.33203125" customWidth="1" style="1" min="1" max="1"/>
@@ -23469,6 +23469,1572 @@
       <c r="G835" t="inlineStr">
         <is>
           <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:21:52</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>NIFTY2651223900CE</t>
+        </is>
+      </c>
+      <c r="C836" t="n">
+        <v>145.3</v>
+      </c>
+      <c r="D836" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E836" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F836" t="n">
+        <v>-520</v>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:32:03</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>NIFTY2651224000CE</t>
+        </is>
+      </c>
+      <c r="C837" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="D837" t="n">
+        <v>88.55</v>
+      </c>
+      <c r="E837" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F837" t="n">
+        <v>3055</v>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:32:35</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>NIFTY2651223900CE</t>
+        </is>
+      </c>
+      <c r="C838" t="n">
+        <v>142</v>
+      </c>
+      <c r="D838" t="n">
+        <v>143.55</v>
+      </c>
+      <c r="E838" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F838" t="n">
+        <v>2015</v>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:33:32</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>NIFTY2651223900CE</t>
+        </is>
+      </c>
+      <c r="C839" t="n">
+        <v>136.7</v>
+      </c>
+      <c r="D839" t="n">
+        <v>137.85</v>
+      </c>
+      <c r="E839" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F839" t="n">
+        <v>1495</v>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:38:17</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C840" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="D840" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="E840" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F840" t="n">
+        <v>-10270</v>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:39:03</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C841" t="n">
+        <v>116.45</v>
+      </c>
+      <c r="D841" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="E841" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F841" t="n">
+        <v>845</v>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:41:00</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C842" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="D842" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="E842" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F842" t="n">
+        <v>2080</v>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:41:38</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C843" t="n">
+        <v>122.9</v>
+      </c>
+      <c r="D843" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="E843" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F843" t="n">
+        <v>1105</v>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:42:06</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C844" t="n">
+        <v>123.25</v>
+      </c>
+      <c r="D844" t="n">
+        <v>122.9</v>
+      </c>
+      <c r="E844" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F844" t="n">
+        <v>-455</v>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:42:39</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C845" t="n">
+        <v>123</v>
+      </c>
+      <c r="D845" t="n">
+        <v>125.15</v>
+      </c>
+      <c r="E845" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F845" t="n">
+        <v>2795</v>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:48:05</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C846" t="n">
+        <v>114</v>
+      </c>
+      <c r="D846" t="n">
+        <v>113.15</v>
+      </c>
+      <c r="E846" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F846" t="n">
+        <v>-1105</v>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:48:50</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C847" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="D847" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="E847" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F847" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:49:30</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C848" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="D848" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="E848" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F848" t="n">
+        <v>650</v>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:53:04</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C849" t="n">
+        <v>116.75</v>
+      </c>
+      <c r="D849" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="E849" t="n">
+        <v>2600</v>
+      </c>
+      <c r="F849" t="n">
+        <v>-21060</v>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:58:41</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C850" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="D850" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="E850" t="n">
+        <v>2600</v>
+      </c>
+      <c r="F850" t="n">
+        <v>650</v>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:00:43</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C851" t="n">
+        <v>112.85</v>
+      </c>
+      <c r="D851" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="E851" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F851" t="n">
+        <v>-130</v>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:03:31</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C852" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="D852" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="E852" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F852" t="n">
+        <v>-7605</v>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:19:36</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C853" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="D853" t="n">
+        <v>115.15</v>
+      </c>
+      <c r="E853" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F853" t="n">
+        <v>975</v>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:33:33</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C854" t="n">
+        <v>119.65</v>
+      </c>
+      <c r="D854" t="n">
+        <v>112.95</v>
+      </c>
+      <c r="E854" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F854" t="n">
+        <v>-8710</v>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:39:07</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C855" t="n">
+        <v>123.8</v>
+      </c>
+      <c r="D855" t="n">
+        <v>126.7</v>
+      </c>
+      <c r="E855" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F855" t="n">
+        <v>3770</v>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:40:47</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C856" t="n">
+        <v>125.4</v>
+      </c>
+      <c r="D856" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="E856" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F856" t="n">
+        <v>-11895</v>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:42:13</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C857" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="D857" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="E857" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F857" t="n">
+        <v>715</v>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:43:06</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C858" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="D858" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="E858" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F858" t="n">
+        <v>10400</v>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:45:33</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C859" t="n">
+        <v>118.05</v>
+      </c>
+      <c r="D859" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="E859" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F859" t="n">
+        <v>2275</v>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:52:16</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C860" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="D860" t="n">
+        <v>118.15</v>
+      </c>
+      <c r="E860" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F860" t="n">
+        <v>3705</v>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:54:15</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C861" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="D861" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="E861" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F861" t="n">
+        <v>-6760</v>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:54:53</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C862" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="D862" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="E862" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F862" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:55:35</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C863" t="n">
+        <v>111.65</v>
+      </c>
+      <c r="D863" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="E863" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F863" t="n">
+        <v>2535</v>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-05-11 12:57:23</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C864" t="n">
+        <v>115.35</v>
+      </c>
+      <c r="D864" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="E864" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F864" t="n">
+        <v>1235</v>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:09:43</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C865" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="D865" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="E865" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F865" t="n">
+        <v>4290</v>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:10:32</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C866" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="D866" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="E866" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F866" t="n">
+        <v>2275</v>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:14:32</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C867" t="n">
+        <v>110</v>
+      </c>
+      <c r="D867" t="n">
+        <v>110.55</v>
+      </c>
+      <c r="E867" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F867" t="n">
+        <v>715</v>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:14:47</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C868" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="D868" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="E868" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F868" t="n">
+        <v>2925</v>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:22:11</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C869" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="D869" t="n">
+        <v>117.65</v>
+      </c>
+      <c r="E869" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F869" t="n">
+        <v>1235</v>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:28:52</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C870" t="n">
+        <v>117.55</v>
+      </c>
+      <c r="D870" t="n">
+        <v>110.85</v>
+      </c>
+      <c r="E870" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F870" t="n">
+        <v>-8710</v>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:29:37</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C871" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="D871" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="E871" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F871" t="n">
+        <v>3055</v>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:35:46</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C872" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="D872" t="n">
+        <v>130</v>
+      </c>
+      <c r="E872" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F872" t="n">
+        <v>16120</v>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:36:29</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C873" t="n">
+        <v>135.75</v>
+      </c>
+      <c r="D873" t="n">
+        <v>138.15</v>
+      </c>
+      <c r="E873" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F873" t="n">
+        <v>3120</v>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:39:33</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>NIFTY2651224000PE</t>
+        </is>
+      </c>
+      <c r="C874" t="n">
+        <v>119.45</v>
+      </c>
+      <c r="D874" t="n">
+        <v>120.25</v>
+      </c>
+      <c r="E874" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F874" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:40:05</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>NIFTY2651224000PE</t>
+        </is>
+      </c>
+      <c r="C875" t="n">
+        <v>122.1</v>
+      </c>
+      <c r="D875" t="n">
+        <v>122.7</v>
+      </c>
+      <c r="E875" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F875" t="n">
+        <v>780</v>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:41:53</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>NIFTY2651224000PE</t>
+        </is>
+      </c>
+      <c r="C876" t="n">
+        <v>124</v>
+      </c>
+      <c r="D876" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="E876" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F876" t="n">
+        <v>-13975</v>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:42:55</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C877" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="D877" t="n">
+        <v>130.65</v>
+      </c>
+      <c r="E877" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F877" t="n">
+        <v>4095</v>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:45:23</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C878" t="n">
+        <v>129.55</v>
+      </c>
+      <c r="D878" t="n">
+        <v>131.9</v>
+      </c>
+      <c r="E878" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F878" t="n">
+        <v>3055</v>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:46:11</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C879" t="n">
+        <v>135.1</v>
+      </c>
+      <c r="D879" t="n">
+        <v>139.85</v>
+      </c>
+      <c r="E879" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F879" t="n">
+        <v>6175</v>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:46:58</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C880" t="n">
+        <v>138.05</v>
+      </c>
+      <c r="D880" t="n">
+        <v>139.4</v>
+      </c>
+      <c r="E880" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F880" t="n">
+        <v>1755</v>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:51:05</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950CE</t>
+        </is>
+      </c>
+      <c r="C881" t="n">
+        <v>142.25</v>
+      </c>
+      <c r="D881" t="n">
+        <v>129.2</v>
+      </c>
+      <c r="E881" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F881" t="n">
+        <v>-16965</v>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:59:05</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>NIFTY2651224000PE</t>
+        </is>
+      </c>
+      <c r="C882" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="D882" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="E882" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F882" t="n">
+        <v>-1300</v>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-05-11 13:59:31</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>NIFTY2651224000CE</t>
+        </is>
+      </c>
+      <c r="C883" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="D883" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="E883" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F883" t="n">
+        <v>1170</v>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-05-11 14:09:08</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>NIFTY2651223900CE</t>
+        </is>
+      </c>
+      <c r="C884" t="n">
+        <v>149.35</v>
+      </c>
+      <c r="D884" t="n">
+        <v>151.75</v>
+      </c>
+      <c r="E884" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F884" t="n">
+        <v>3120</v>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-05-11 14:09:54</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>NIFTY2651223900CE</t>
+        </is>
+      </c>
+      <c r="C885" t="n">
+        <v>152.75</v>
+      </c>
+      <c r="D885" t="n">
+        <v>145.3</v>
+      </c>
+      <c r="E885" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F885" t="n">
+        <v>-9685</v>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-05-11 14:11:36</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>NIFTY2651224050PE</t>
+        </is>
+      </c>
+      <c r="C886" t="n">
+        <v>140.45</v>
+      </c>
+      <c r="D886" t="n">
+        <v>140.55</v>
+      </c>
+      <c r="E886" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F886" t="n">
+        <v>130</v>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-05-11 14:12:11</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>NIFTY2651224050PE</t>
+        </is>
+      </c>
+      <c r="C887" t="n">
+        <v>143.05</v>
+      </c>
+      <c r="D887" t="n">
+        <v>143.8</v>
+      </c>
+      <c r="E887" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F887" t="n">
+        <v>975</v>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-05-11 14:13:47</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>NIFTY2651224050PE</t>
+        </is>
+      </c>
+      <c r="C888" t="n">
+        <v>144.55</v>
+      </c>
+      <c r="D888" t="n">
+        <v>145.35</v>
+      </c>
+      <c r="E888" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F888" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>2026-05-11 14:16:10</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>NIFTY2651224050PE</t>
+        </is>
+      </c>
+      <c r="C889" t="n">
+        <v>150.9</v>
+      </c>
+      <c r="D889" t="n">
+        <v>149.85</v>
+      </c>
+      <c r="E889" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F889" t="n">
+        <v>-1365</v>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>PAPER</t>
         </is>
       </c>
     </row>

--- a/Lakshmi.xlsx
+++ b/Lakshmi.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H889"/>
+  <dimension ref="A1:H895"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="24.33203125" customWidth="1" style="1" min="1" max="1"/>
@@ -25033,6 +25033,180 @@
         <v>-1365</v>
       </c>
       <c r="G889" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2026-05-11 14:28:00</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C890" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="D890" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="E890" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F890" t="n">
+        <v>4810</v>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2026-05-11 14:29:42</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C891" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="D891" t="n">
+        <v>103.35</v>
+      </c>
+      <c r="E891" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F891" t="n">
+        <v>195</v>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-05-11 14:44:58</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C892" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="D892" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="E892" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F892" t="n">
+        <v>1235</v>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-05-11 14:45:31</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C893" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="D893" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="E893" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F893" t="n">
+        <v>780</v>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-05-11 14:47:29</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C894" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="D894" t="n">
+        <v>119.75</v>
+      </c>
+      <c r="E894" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F894" t="n">
+        <v>10985</v>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-05-11 14:49:34</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C895" t="n">
+        <v>124.55</v>
+      </c>
+      <c r="D895" t="n">
+        <v>126.6</v>
+      </c>
+      <c r="E895" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F895" t="n">
+        <v>2665</v>
+      </c>
+      <c r="G895" t="inlineStr">
         <is>
           <t>PAPER</t>
         </is>

--- a/Lakshmi.xlsx
+++ b/Lakshmi.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H895"/>
+  <dimension ref="A1:H920"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="24.33203125" customWidth="1" style="1" min="1" max="1"/>
@@ -25207,6 +25207,731 @@
         <v>2665</v>
       </c>
       <c r="G895" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:00:11</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C896" t="n">
+        <v>128.05</v>
+      </c>
+      <c r="D896" t="n">
+        <v>130.95</v>
+      </c>
+      <c r="E896" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F896" t="n">
+        <v>3770</v>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:00:35</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C897" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="D897" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="E897" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F897" t="n">
+        <v>260</v>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:01:18</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C898" t="n">
+        <v>134</v>
+      </c>
+      <c r="D898" t="n">
+        <v>135.25</v>
+      </c>
+      <c r="E898" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F898" t="n">
+        <v>1625</v>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:01:36</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C899" t="n">
+        <v>135.7</v>
+      </c>
+      <c r="D899" t="n">
+        <v>134.9</v>
+      </c>
+      <c r="E899" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F899" t="n">
+        <v>-1040</v>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:02:45</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C900" t="n">
+        <v>137.35</v>
+      </c>
+      <c r="D900" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="E900" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F900" t="n">
+        <v>195</v>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:03:57</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C901" t="n">
+        <v>149</v>
+      </c>
+      <c r="D901" t="n">
+        <v>150.95</v>
+      </c>
+      <c r="E901" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F901" t="n">
+        <v>2535</v>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:04:20</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C902" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="D902" t="n">
+        <v>154.8</v>
+      </c>
+      <c r="E902" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F902" t="n">
+        <v>1170</v>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:04:35</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C903" t="n">
+        <v>155.05</v>
+      </c>
+      <c r="D903" t="n">
+        <v>157.2</v>
+      </c>
+      <c r="E903" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F903" t="n">
+        <v>2795</v>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:06:15</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>NIFTY2651223950PE</t>
+        </is>
+      </c>
+      <c r="C904" t="n">
+        <v>154.1</v>
+      </c>
+      <c r="D904" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="E904" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F904" t="n">
+        <v>7150</v>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:20:25</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>NIFTY2651223900PE</t>
+        </is>
+      </c>
+      <c r="C905" t="n">
+        <v>123.15</v>
+      </c>
+      <c r="D905" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="E905" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F905" t="n">
+        <v>1235</v>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:20:59</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>NIFTY2651223900PE</t>
+        </is>
+      </c>
+      <c r="C906" t="n">
+        <v>121.95</v>
+      </c>
+      <c r="D906" t="n">
+        <v>123</v>
+      </c>
+      <c r="E906" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F906" t="n">
+        <v>1365</v>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>2026-05-12 10:30:56</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>NIFTY2651923400PE</t>
+        </is>
+      </c>
+      <c r="C907" t="n">
+        <v>136</v>
+      </c>
+      <c r="D907" t="n">
+        <v>136.35</v>
+      </c>
+      <c r="E907" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F907" t="n">
+        <v>455</v>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>2026-05-12 10:33:21</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>NIFTY2651223700PE</t>
+        </is>
+      </c>
+      <c r="C908" t="n">
+        <v>103.55</v>
+      </c>
+      <c r="D908" t="n">
+        <v>105</v>
+      </c>
+      <c r="E908" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F908" t="n">
+        <v>1885</v>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>2026-05-12 10:35:22</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>NIFTY2651223700PE</t>
+        </is>
+      </c>
+      <c r="C909" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="D909" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="E909" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F909" t="n">
+        <v>2925</v>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>2026-05-12 10:38:11</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>NIFTY2651223700PE</t>
+        </is>
+      </c>
+      <c r="C910" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="D910" t="n">
+        <v>115.6</v>
+      </c>
+      <c r="E910" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F910" t="n">
+        <v>9425</v>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>2026-05-12 10:48:47</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>NIFTY2651223700PE</t>
+        </is>
+      </c>
+      <c r="C911" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="D911" t="n">
+        <v>106.45</v>
+      </c>
+      <c r="E911" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F911" t="n">
+        <v>2860</v>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>2026-05-12 10:56:18</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>NIFTY2651223700PE</t>
+        </is>
+      </c>
+      <c r="C912" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="D912" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="E912" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F912" t="n">
+        <v>-12740</v>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>2026-05-12 11:02:02</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>NIFTY2651223700PE</t>
+        </is>
+      </c>
+      <c r="C913" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="D913" t="n">
+        <v>113.15</v>
+      </c>
+      <c r="E913" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F913" t="n">
+        <v>5460</v>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>2026-05-12 11:02:28</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>NIFTY2651223700PE</t>
+        </is>
+      </c>
+      <c r="C914" t="n">
+        <v>116.75</v>
+      </c>
+      <c r="D914" t="n">
+        <v>120.15</v>
+      </c>
+      <c r="E914" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F914" t="n">
+        <v>4420</v>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>2026-05-12 11:12:19</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>NIFTY2651223700PE</t>
+        </is>
+      </c>
+      <c r="C915" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="D915" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="E915" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F915" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>2026-05-12 11:34:09</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>NIFTY2651223700PE</t>
+        </is>
+      </c>
+      <c r="C916" t="n">
+        <v>120.65</v>
+      </c>
+      <c r="D916" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="E916" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F916" t="n">
+        <v>-14560</v>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:07:37</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>NIFTY2651223700PE</t>
+        </is>
+      </c>
+      <c r="C917" t="n">
+        <v>118.85</v>
+      </c>
+      <c r="D917" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="E917" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F917" t="n">
+        <v>1365</v>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:08:18</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>NIFTY2651223700PE</t>
+        </is>
+      </c>
+      <c r="C918" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="D918" t="n">
+        <v>140.35</v>
+      </c>
+      <c r="E918" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F918" t="n">
+        <v>13585</v>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>2026-05-12 12:09:37</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>NIFTY2651223700PE</t>
+        </is>
+      </c>
+      <c r="C919" t="n">
+        <v>143.9</v>
+      </c>
+      <c r="D919" t="n">
+        <v>141.3</v>
+      </c>
+      <c r="E919" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F919" t="n">
+        <v>-3380</v>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>2026-05-12 14:15:15</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>NIFTY2651223600PE</t>
+        </is>
+      </c>
+      <c r="C920" t="n">
+        <v>138.45</v>
+      </c>
+      <c r="D920" t="n">
+        <v>141.15</v>
+      </c>
+      <c r="E920" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F920" t="n">
+        <v>3510</v>
+      </c>
+      <c r="G920" t="inlineStr">
         <is>
           <t>PAPER</t>
         </is>

--- a/Lakshmi.xlsx
+++ b/Lakshmi.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I931"/>
+  <dimension ref="A1:H921"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="24.33203125" customWidth="1" style="1" min="1" max="1"/>
@@ -25961,312 +25961,6 @@
         <v>3575</v>
       </c>
       <c r="G921" t="inlineStr">
-        <is>
-          <t>PAPER</t>
-        </is>
-      </c>
-    </row>
-    <row r="922">
-      <c r="A922" t="inlineStr">
-        <is>
-          <t>2026-05-13 13:29:51</t>
-        </is>
-      </c>
-      <c r="B922" t="inlineStr">
-        <is>
-          <t>NIFTY2651923300PE</t>
-        </is>
-      </c>
-      <c r="C922" t="n">
-        <v>136.5</v>
-      </c>
-      <c r="D922" t="n">
-        <v>137.75</v>
-      </c>
-      <c r="E922" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F922" t="n">
-        <v>1625</v>
-      </c>
-      <c r="G922" t="inlineStr">
-        <is>
-          <t>PAPER</t>
-        </is>
-      </c>
-    </row>
-    <row r="923">
-      <c r="A923" t="inlineStr">
-        <is>
-          <t>2026-05-13 13:31:35</t>
-        </is>
-      </c>
-      <c r="B923" t="inlineStr">
-        <is>
-          <t>NIFTY2651923300PE</t>
-        </is>
-      </c>
-      <c r="C923" t="n">
-        <v>139.65</v>
-      </c>
-      <c r="D923" t="n">
-        <v>131.7</v>
-      </c>
-      <c r="E923" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F923" t="n">
-        <v>-10335</v>
-      </c>
-      <c r="G923" t="inlineStr">
-        <is>
-          <t>PAPER</t>
-        </is>
-      </c>
-    </row>
-    <row r="924">
-      <c r="A924" t="inlineStr">
-        <is>
-          <t>2026-05-13 13:36:16</t>
-        </is>
-      </c>
-      <c r="B924" t="inlineStr">
-        <is>
-          <t>NIFTY2651923700CE</t>
-        </is>
-      </c>
-      <c r="C924" t="n">
-        <v>160</v>
-      </c>
-      <c r="D924" t="n">
-        <v>161.5</v>
-      </c>
-      <c r="E924" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F924" t="n">
-        <v>1950</v>
-      </c>
-      <c r="G924" t="inlineStr">
-        <is>
-          <t>PAPER</t>
-        </is>
-      </c>
-    </row>
-    <row r="925">
-      <c r="A925" t="inlineStr">
-        <is>
-          <t>2026-05-13 13:39:29</t>
-        </is>
-      </c>
-      <c r="B925" t="inlineStr">
-        <is>
-          <t>NIFTY2651923700CE</t>
-        </is>
-      </c>
-      <c r="C925" t="n">
-        <v>159.9</v>
-      </c>
-      <c r="D925" t="n">
-        <v>160.4</v>
-      </c>
-      <c r="E925" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F925" t="n">
-        <v>650</v>
-      </c>
-      <c r="G925" t="inlineStr">
-        <is>
-          <t>PAPER</t>
-        </is>
-      </c>
-    </row>
-    <row r="926">
-      <c r="A926" t="inlineStr">
-        <is>
-          <t>2026-05-13 13:48:15</t>
-        </is>
-      </c>
-      <c r="B926" t="inlineStr">
-        <is>
-          <t>NIFTY2651923700CE</t>
-        </is>
-      </c>
-      <c r="C926" t="n">
-        <v>158.2</v>
-      </c>
-      <c r="D926" t="n">
-        <v>159.3</v>
-      </c>
-      <c r="E926" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F926" t="n">
-        <v>1430</v>
-      </c>
-      <c r="G926" t="inlineStr">
-        <is>
-          <t>PAPER</t>
-        </is>
-      </c>
-    </row>
-    <row r="927">
-      <c r="A927" t="inlineStr">
-        <is>
-          <t>2026-05-13 13:56:09</t>
-        </is>
-      </c>
-      <c r="B927" t="inlineStr">
-        <is>
-          <t>NIFTY2651923300PE</t>
-        </is>
-      </c>
-      <c r="C927" t="n">
-        <v>140.5</v>
-      </c>
-      <c r="D927" t="n">
-        <v>145.2</v>
-      </c>
-      <c r="E927" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F927" t="n">
-        <v>6110</v>
-      </c>
-      <c r="G927" t="inlineStr">
-        <is>
-          <t>PAPER</t>
-        </is>
-      </c>
-    </row>
-    <row r="928">
-      <c r="A928" t="inlineStr">
-        <is>
-          <t>2026-05-13 13:58:36</t>
-        </is>
-      </c>
-      <c r="B928" t="inlineStr">
-        <is>
-          <t>NIFTY2651923700CE</t>
-        </is>
-      </c>
-      <c r="C928" t="n">
-        <v>148.35</v>
-      </c>
-      <c r="D928" t="n">
-        <v>148.05</v>
-      </c>
-      <c r="E928" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F928" t="n">
-        <v>-390</v>
-      </c>
-      <c r="G928" t="inlineStr">
-        <is>
-          <t>PAPER</t>
-        </is>
-      </c>
-    </row>
-    <row r="929">
-      <c r="A929" t="inlineStr">
-        <is>
-          <t>2026-05-13 14:02:29</t>
-        </is>
-      </c>
-      <c r="B929" t="inlineStr">
-        <is>
-          <t>NIFTY2651923700CE</t>
-        </is>
-      </c>
-      <c r="C929" t="n">
-        <v>147.75</v>
-      </c>
-      <c r="D929" t="n">
-        <v>141.65</v>
-      </c>
-      <c r="E929" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F929" t="n">
-        <v>-7930</v>
-      </c>
-      <c r="G929" t="inlineStr">
-        <is>
-          <t>PAPER</t>
-        </is>
-      </c>
-    </row>
-    <row r="930">
-      <c r="A930" t="inlineStr">
-        <is>
-          <t>2026-05-13 14:04:56</t>
-        </is>
-      </c>
-      <c r="B930" t="inlineStr">
-        <is>
-          <t>NIFTY2651923300PE</t>
-        </is>
-      </c>
-      <c r="C930" t="n">
-        <v>137.2</v>
-      </c>
-      <c r="D930" t="n">
-        <v>142.35</v>
-      </c>
-      <c r="E930" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F930" t="n">
-        <v>6695</v>
-      </c>
-      <c r="G930" t="n">
-        <v>178360</v>
-      </c>
-      <c r="H930" t="inlineStr">
-        <is>
-          <t>PROFIT</t>
-        </is>
-      </c>
-      <c r="I930" t="inlineStr">
-        <is>
-          <t>PAPER</t>
-        </is>
-      </c>
-    </row>
-    <row r="931">
-      <c r="A931" t="inlineStr">
-        <is>
-          <t>2026-05-13 14:57:17</t>
-        </is>
-      </c>
-      <c r="B931" t="inlineStr">
-        <is>
-          <t>NIFTY2651923700CE</t>
-        </is>
-      </c>
-      <c r="C931" t="n">
-        <v>134.6</v>
-      </c>
-      <c r="D931" t="n">
-        <v>135.75</v>
-      </c>
-      <c r="E931" t="n">
-        <v>1300</v>
-      </c>
-      <c r="F931" t="n">
-        <v>1495</v>
-      </c>
-      <c r="G931" t="n">
-        <v>174980</v>
-      </c>
-      <c r="H931" t="inlineStr">
-        <is>
-          <t>PROFIT</t>
-        </is>
-      </c>
-      <c r="I931" t="inlineStr">
         <is>
           <t>PAPER</t>
         </is>

--- a/Lakshmi.xlsx
+++ b/Lakshmi.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H920"/>
+  <dimension ref="A1:I931"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="24.33203125" customWidth="1" style="1" min="1" max="1"/>
@@ -25932,6 +25932,341 @@
         <v>3510</v>
       </c>
       <c r="G920" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>2026-05-13 12:18:00</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>NIFTY2651923300PE</t>
+        </is>
+      </c>
+      <c r="C921" t="n">
+        <v>140.35</v>
+      </c>
+      <c r="D921" t="n">
+        <v>143.1</v>
+      </c>
+      <c r="E921" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F921" t="n">
+        <v>3575</v>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>2026-05-13 13:29:51</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>NIFTY2651923300PE</t>
+        </is>
+      </c>
+      <c r="C922" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="D922" t="n">
+        <v>137.75</v>
+      </c>
+      <c r="E922" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F922" t="n">
+        <v>1625</v>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>2026-05-13 13:31:35</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>NIFTY2651923300PE</t>
+        </is>
+      </c>
+      <c r="C923" t="n">
+        <v>139.65</v>
+      </c>
+      <c r="D923" t="n">
+        <v>131.7</v>
+      </c>
+      <c r="E923" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F923" t="n">
+        <v>-10335</v>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>2026-05-13 13:36:16</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>NIFTY2651923700CE</t>
+        </is>
+      </c>
+      <c r="C924" t="n">
+        <v>160</v>
+      </c>
+      <c r="D924" t="n">
+        <v>161.5</v>
+      </c>
+      <c r="E924" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F924" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>2026-05-13 13:39:29</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>NIFTY2651923700CE</t>
+        </is>
+      </c>
+      <c r="C925" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="D925" t="n">
+        <v>160.4</v>
+      </c>
+      <c r="E925" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F925" t="n">
+        <v>650</v>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>2026-05-13 13:48:15</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>NIFTY2651923700CE</t>
+        </is>
+      </c>
+      <c r="C926" t="n">
+        <v>158.2</v>
+      </c>
+      <c r="D926" t="n">
+        <v>159.3</v>
+      </c>
+      <c r="E926" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F926" t="n">
+        <v>1430</v>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>2026-05-13 13:56:09</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>NIFTY2651923300PE</t>
+        </is>
+      </c>
+      <c r="C927" t="n">
+        <v>140.5</v>
+      </c>
+      <c r="D927" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="E927" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F927" t="n">
+        <v>6110</v>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>2026-05-13 13:58:36</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>NIFTY2651923700CE</t>
+        </is>
+      </c>
+      <c r="C928" t="n">
+        <v>148.35</v>
+      </c>
+      <c r="D928" t="n">
+        <v>148.05</v>
+      </c>
+      <c r="E928" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F928" t="n">
+        <v>-390</v>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>2026-05-13 14:02:29</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>NIFTY2651923700CE</t>
+        </is>
+      </c>
+      <c r="C929" t="n">
+        <v>147.75</v>
+      </c>
+      <c r="D929" t="n">
+        <v>141.65</v>
+      </c>
+      <c r="E929" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F929" t="n">
+        <v>-7930</v>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>2026-05-13 14:04:56</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>NIFTY2651923300PE</t>
+        </is>
+      </c>
+      <c r="C930" t="n">
+        <v>137.2</v>
+      </c>
+      <c r="D930" t="n">
+        <v>142.35</v>
+      </c>
+      <c r="E930" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F930" t="n">
+        <v>6695</v>
+      </c>
+      <c r="G930" t="n">
+        <v>178360</v>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>2026-05-13 14:57:17</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>NIFTY2651923700CE</t>
+        </is>
+      </c>
+      <c r="C931" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="D931" t="n">
+        <v>135.75</v>
+      </c>
+      <c r="E931" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F931" t="n">
+        <v>1495</v>
+      </c>
+      <c r="G931" t="n">
+        <v>174980</v>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
         <is>
           <t>PAPER</t>
         </is>

--- a/Lakshmi.xlsx
+++ b/Lakshmi.xlsx
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H921"/>
+  <dimension ref="A1:I997"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="24.33203125" customWidth="1" style="1" min="1" max="1"/>
@@ -25963,6 +25963,2818 @@
       <c r="G921" t="inlineStr">
         <is>
           <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>2026-05-14 14:04:55</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>NIFTY2651923750CE</t>
+        </is>
+      </c>
+      <c r="C922" t="n">
+        <v>192.87</v>
+      </c>
+      <c r="D922" t="n">
+        <v>194.37</v>
+      </c>
+      <c r="E922" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F922" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G922" t="n">
+        <v>250731</v>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>2026-05-14 14:21:35</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>NIFTY2651923700PE</t>
+        </is>
+      </c>
+      <c r="C923" t="n">
+        <v>166.54</v>
+      </c>
+      <c r="D923" t="n">
+        <v>159.07</v>
+      </c>
+      <c r="E923" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F923" t="n">
+        <v>-9711</v>
+      </c>
+      <c r="G923" t="n">
+        <v>216502</v>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>2026-05-14 14:23:16</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>NIFTY2651923800CE</t>
+        </is>
+      </c>
+      <c r="C924" t="n">
+        <v>158.31</v>
+      </c>
+      <c r="D924" t="n">
+        <v>158.69</v>
+      </c>
+      <c r="E924" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F924" t="n">
+        <v>494</v>
+      </c>
+      <c r="G924" t="n">
+        <v>205803</v>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>2026-05-19 10:57:16</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>NIFTY2651923650CE</t>
+        </is>
+      </c>
+      <c r="C925" t="n">
+        <v>125.38</v>
+      </c>
+      <c r="D925" t="n">
+        <v>130.31</v>
+      </c>
+      <c r="E925" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F925" t="n">
+        <v>6409</v>
+      </c>
+      <c r="G925" t="n">
+        <v>162994</v>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>2026-05-19 10:58:14</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>NIFTY2651923650CE</t>
+        </is>
+      </c>
+      <c r="C926" t="n">
+        <v>140.42</v>
+      </c>
+      <c r="D926" t="n">
+        <v>141.81</v>
+      </c>
+      <c r="E926" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F926" t="n">
+        <v>1807</v>
+      </c>
+      <c r="G926" t="n">
+        <v>182546</v>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>2026-05-19 10:59:12</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>NIFTY2651923650CE</t>
+        </is>
+      </c>
+      <c r="C927" t="n">
+        <v>145.06</v>
+      </c>
+      <c r="D927" t="n">
+        <v>145.01</v>
+      </c>
+      <c r="E927" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F927" t="n">
+        <v>-65</v>
+      </c>
+      <c r="G927" t="n">
+        <v>188578</v>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>2026-05-19 11:02:21</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>NIFTY2651923650CE</t>
+        </is>
+      </c>
+      <c r="C928" t="n">
+        <v>138.23</v>
+      </c>
+      <c r="D928" t="n">
+        <v>118.62</v>
+      </c>
+      <c r="E928" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F928" t="n">
+        <v>-25493</v>
+      </c>
+      <c r="G928" t="n">
+        <v>179699</v>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>2026-05-21 13:32:20</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>SENSEX2652175000PE</t>
+        </is>
+      </c>
+      <c r="C929" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="D929" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="E929" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F929" t="n">
+        <v>50</v>
+      </c>
+      <c r="G929" t="n">
+        <v>104400</v>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>2026-05-21 13:36:49</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23750CE</t>
+        </is>
+      </c>
+      <c r="C930" t="n">
+        <v>116.05</v>
+      </c>
+      <c r="D930" t="n">
+        <v>119.6</v>
+      </c>
+      <c r="E930" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F930" t="n">
+        <v>4615</v>
+      </c>
+      <c r="G930" t="n">
+        <v>150865</v>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:03:00</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23850CE</t>
+        </is>
+      </c>
+      <c r="C931" t="n">
+        <v>118.4</v>
+      </c>
+      <c r="D931" t="n">
+        <v>118.85</v>
+      </c>
+      <c r="E931" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F931" t="n">
+        <v>585</v>
+      </c>
+      <c r="G931" t="n">
+        <v>153920</v>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:04:16</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23850CE</t>
+        </is>
+      </c>
+      <c r="C932" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="D932" t="n">
+        <v>120.3</v>
+      </c>
+      <c r="E932" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F932" t="n">
+        <v>1170</v>
+      </c>
+      <c r="G932" t="n">
+        <v>155220</v>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:04:31</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23850CE</t>
+        </is>
+      </c>
+      <c r="C933" t="n">
+        <v>120.45</v>
+      </c>
+      <c r="D933" t="n">
+        <v>120.6</v>
+      </c>
+      <c r="E933" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F933" t="n">
+        <v>195</v>
+      </c>
+      <c r="G933" t="n">
+        <v>156585</v>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:05:12</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23850CE</t>
+        </is>
+      </c>
+      <c r="C934" t="n">
+        <v>120.65</v>
+      </c>
+      <c r="D934" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="E934" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F934" t="n">
+        <v>325</v>
+      </c>
+      <c r="G934" t="n">
+        <v>156845</v>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:07:00</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23850CE</t>
+        </is>
+      </c>
+      <c r="C935" t="n">
+        <v>120.3</v>
+      </c>
+      <c r="D935" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="E935" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F935" t="n">
+        <v>260</v>
+      </c>
+      <c r="G935" t="n">
+        <v>156390</v>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:07:40</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23700PE</t>
+        </is>
+      </c>
+      <c r="C936" t="n">
+        <v>114</v>
+      </c>
+      <c r="D936" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="E936" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F936" t="n">
+        <v>-650</v>
+      </c>
+      <c r="G936" t="n">
+        <v>148200</v>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:09:18</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23700PE</t>
+        </is>
+      </c>
+      <c r="C937" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="D937" t="n">
+        <v>115.6</v>
+      </c>
+      <c r="E937" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F937" t="n">
+        <v>-780</v>
+      </c>
+      <c r="G937" t="n">
+        <v>151060</v>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:20:55</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23750CE</t>
+        </is>
+      </c>
+      <c r="C938" t="n">
+        <v>161.55</v>
+      </c>
+      <c r="D938" t="n">
+        <v>161.8</v>
+      </c>
+      <c r="E938" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F938" t="n">
+        <v>325</v>
+      </c>
+      <c r="G938" t="n">
+        <v>210015</v>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:23:27</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23750CE</t>
+        </is>
+      </c>
+      <c r="C939" t="n">
+        <v>173</v>
+      </c>
+      <c r="D939" t="n">
+        <v>176.25</v>
+      </c>
+      <c r="E939" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F939" t="n">
+        <v>4225</v>
+      </c>
+      <c r="G939" t="n">
+        <v>224900</v>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:27:28</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23750PE</t>
+        </is>
+      </c>
+      <c r="C940" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="D940" t="n">
+        <v>142.95</v>
+      </c>
+      <c r="E940" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F940" t="n">
+        <v>1885</v>
+      </c>
+      <c r="G940" t="n">
+        <v>183950</v>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:27:50</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23750PE</t>
+        </is>
+      </c>
+      <c r="C941" t="n">
+        <v>141.95</v>
+      </c>
+      <c r="D941" t="n">
+        <v>142.4</v>
+      </c>
+      <c r="E941" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F941" t="n">
+        <v>585</v>
+      </c>
+      <c r="G941" t="n">
+        <v>184535</v>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:28:24</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23750PE</t>
+        </is>
+      </c>
+      <c r="C942" t="n">
+        <v>147</v>
+      </c>
+      <c r="D942" t="n">
+        <v>147.4</v>
+      </c>
+      <c r="E942" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F942" t="n">
+        <v>520</v>
+      </c>
+      <c r="G942" t="n">
+        <v>191100</v>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:30:42</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23750PE</t>
+        </is>
+      </c>
+      <c r="C943" t="n">
+        <v>143.65</v>
+      </c>
+      <c r="D943" t="n">
+        <v>145.6</v>
+      </c>
+      <c r="E943" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F943" t="n">
+        <v>2535</v>
+      </c>
+      <c r="G943" t="n">
+        <v>186745</v>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:32:43</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23750PE</t>
+        </is>
+      </c>
+      <c r="C944" t="n">
+        <v>145.6</v>
+      </c>
+      <c r="D944" t="n">
+        <v>136.15</v>
+      </c>
+      <c r="E944" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F944" t="n">
+        <v>-12285</v>
+      </c>
+      <c r="G944" t="n">
+        <v>189280</v>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:54:23</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23850CE</t>
+        </is>
+      </c>
+      <c r="C945" t="n">
+        <v>131.9</v>
+      </c>
+      <c r="D945" t="n">
+        <v>132.35</v>
+      </c>
+      <c r="E945" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F945" t="n">
+        <v>585</v>
+      </c>
+      <c r="G945" t="n">
+        <v>171470</v>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:31:02</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23700PE</t>
+        </is>
+      </c>
+      <c r="C946" t="n">
+        <v>115.8</v>
+      </c>
+      <c r="D946" t="n">
+        <v>116.75</v>
+      </c>
+      <c r="E946" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F946" t="n">
+        <v>1235</v>
+      </c>
+      <c r="G946" t="n">
+        <v>150540</v>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:49:31</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23850CE</t>
+        </is>
+      </c>
+      <c r="C947" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="D947" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="E947" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F947" t="n">
+        <v>0</v>
+      </c>
+      <c r="G947" t="n">
+        <v>173550</v>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:52:30</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23850CE</t>
+        </is>
+      </c>
+      <c r="C948" t="n">
+        <v>138.95</v>
+      </c>
+      <c r="D948" t="n">
+        <v>139.3</v>
+      </c>
+      <c r="E948" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F948" t="n">
+        <v>455</v>
+      </c>
+      <c r="G948" t="n">
+        <v>180635</v>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:52:59</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23850CE</t>
+        </is>
+      </c>
+      <c r="C949" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="D949" t="n">
+        <v>139.05</v>
+      </c>
+      <c r="E949" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F949" t="n">
+        <v>195</v>
+      </c>
+      <c r="G949" t="n">
+        <v>180570</v>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>2026-05-22 12:56:05</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23850CE</t>
+        </is>
+      </c>
+      <c r="C950" t="n">
+        <v>140.75</v>
+      </c>
+      <c r="D950" t="n">
+        <v>140.05</v>
+      </c>
+      <c r="E950" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F950" t="n">
+        <v>-910</v>
+      </c>
+      <c r="G950" t="n">
+        <v>182975</v>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:02:05</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23850CE</t>
+        </is>
+      </c>
+      <c r="C951" t="n">
+        <v>143.15</v>
+      </c>
+      <c r="D951" t="n">
+        <v>133.8</v>
+      </c>
+      <c r="E951" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F951" t="n">
+        <v>-12155</v>
+      </c>
+      <c r="G951" t="n">
+        <v>186095</v>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:47:16</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23850CE</t>
+        </is>
+      </c>
+      <c r="C952" t="n">
+        <v>132.3</v>
+      </c>
+      <c r="D952" t="n">
+        <v>132.65</v>
+      </c>
+      <c r="E952" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F952" t="n">
+        <v>455</v>
+      </c>
+      <c r="G952" t="n">
+        <v>171990</v>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:55:31</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23750PE</t>
+        </is>
+      </c>
+      <c r="C953" t="n">
+        <v>116.65</v>
+      </c>
+      <c r="D953" t="n">
+        <v>121.25</v>
+      </c>
+      <c r="E953" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F953" t="n">
+        <v>5980</v>
+      </c>
+      <c r="G953" t="n">
+        <v>151645</v>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:03:57</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23750PE</t>
+        </is>
+      </c>
+      <c r="C954" t="n">
+        <v>125.1</v>
+      </c>
+      <c r="D954" t="n">
+        <v>125.45</v>
+      </c>
+      <c r="E954" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F954" t="n">
+        <v>455</v>
+      </c>
+      <c r="G954" t="n">
+        <v>162630</v>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>2026-05-22 14:05:29</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23750PE</t>
+        </is>
+      </c>
+      <c r="C955" t="n">
+        <v>143.6</v>
+      </c>
+      <c r="D955" t="n">
+        <v>142.85</v>
+      </c>
+      <c r="E955" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F955" t="n">
+        <v>-975</v>
+      </c>
+      <c r="G955" t="n">
+        <v>186680</v>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>2026-05-25 12:46:46</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24000PE</t>
+        </is>
+      </c>
+      <c r="C956" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="D956" t="n">
+        <v>114.45</v>
+      </c>
+      <c r="E956" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F956" t="n">
+        <v>2210</v>
+      </c>
+      <c r="G956" t="n">
+        <v>146575</v>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>2026-05-25 12:52:50</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24000PE</t>
+        </is>
+      </c>
+      <c r="C957" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="D957" t="n">
+        <v>118.45</v>
+      </c>
+      <c r="E957" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F957" t="n">
+        <v>-11765</v>
+      </c>
+      <c r="G957" t="n">
+        <v>165750</v>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:19:55</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24150PE</t>
+        </is>
+      </c>
+      <c r="C958" t="n">
+        <v>122.15</v>
+      </c>
+      <c r="D958" t="n">
+        <v>122.65</v>
+      </c>
+      <c r="E958" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F958" t="n">
+        <v>650</v>
+      </c>
+      <c r="G958" t="n">
+        <v>158795</v>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:25:06</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24150PE</t>
+        </is>
+      </c>
+      <c r="C959" t="n">
+        <v>126.85</v>
+      </c>
+      <c r="D959" t="n">
+        <v>126.7</v>
+      </c>
+      <c r="E959" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F959" t="n">
+        <v>-195</v>
+      </c>
+      <c r="G959" t="n">
+        <v>164905</v>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:26:14</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24150PE</t>
+        </is>
+      </c>
+      <c r="C960" t="n">
+        <v>128.85</v>
+      </c>
+      <c r="D960" t="n">
+        <v>129.75</v>
+      </c>
+      <c r="E960" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F960" t="n">
+        <v>1170</v>
+      </c>
+      <c r="G960" t="n">
+        <v>167505</v>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:26:48</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24150PE</t>
+        </is>
+      </c>
+      <c r="C961" t="n">
+        <v>127.95</v>
+      </c>
+      <c r="D961" t="n">
+        <v>127.55</v>
+      </c>
+      <c r="E961" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F961" t="n">
+        <v>-520</v>
+      </c>
+      <c r="G961" t="n">
+        <v>166335</v>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:27:36</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24150PE</t>
+        </is>
+      </c>
+      <c r="C962" t="n">
+        <v>130</v>
+      </c>
+      <c r="D962" t="n">
+        <v>131.25</v>
+      </c>
+      <c r="E962" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F962" t="n">
+        <v>1625</v>
+      </c>
+      <c r="G962" t="n">
+        <v>169000</v>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:27:55</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24150PE</t>
+        </is>
+      </c>
+      <c r="C963" t="n">
+        <v>130.75</v>
+      </c>
+      <c r="D963" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="E963" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F963" t="n">
+        <v>1755</v>
+      </c>
+      <c r="G963" t="n">
+        <v>169975</v>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:28:25</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24150PE</t>
+        </is>
+      </c>
+      <c r="C964" t="n">
+        <v>136</v>
+      </c>
+      <c r="D964" t="n">
+        <v>137.7</v>
+      </c>
+      <c r="E964" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F964" t="n">
+        <v>2210</v>
+      </c>
+      <c r="G964" t="n">
+        <v>176800</v>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:28:50</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24150PE</t>
+        </is>
+      </c>
+      <c r="C965" t="n">
+        <v>136.55</v>
+      </c>
+      <c r="D965" t="n">
+        <v>137.9</v>
+      </c>
+      <c r="E965" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F965" t="n">
+        <v>1755</v>
+      </c>
+      <c r="G965" t="n">
+        <v>177515</v>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:29:46</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24150PE</t>
+        </is>
+      </c>
+      <c r="C966" t="n">
+        <v>140.3</v>
+      </c>
+      <c r="D966" t="n">
+        <v>140.5</v>
+      </c>
+      <c r="E966" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F966" t="n">
+        <v>260</v>
+      </c>
+      <c r="G966" t="n">
+        <v>182390</v>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:31:31</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23900CE</t>
+        </is>
+      </c>
+      <c r="C967" t="n">
+        <v>134</v>
+      </c>
+      <c r="D967" t="n">
+        <v>134.65</v>
+      </c>
+      <c r="E967" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F967" t="n">
+        <v>845</v>
+      </c>
+      <c r="G967" t="n">
+        <v>174200</v>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:31:52</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23900CE</t>
+        </is>
+      </c>
+      <c r="C968" t="n">
+        <v>135.4</v>
+      </c>
+      <c r="D968" t="n">
+        <v>136.35</v>
+      </c>
+      <c r="E968" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F968" t="n">
+        <v>1235</v>
+      </c>
+      <c r="G968" t="n">
+        <v>176020</v>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:32:26</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23900CE</t>
+        </is>
+      </c>
+      <c r="C969" t="n">
+        <v>137.6</v>
+      </c>
+      <c r="D969" t="n">
+        <v>137.75</v>
+      </c>
+      <c r="E969" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F969" t="n">
+        <v>195</v>
+      </c>
+      <c r="G969" t="n">
+        <v>178880</v>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:33:14</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23900CE</t>
+        </is>
+      </c>
+      <c r="C970" t="n">
+        <v>132.3</v>
+      </c>
+      <c r="D970" t="n">
+        <v>132.75</v>
+      </c>
+      <c r="E970" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F970" t="n">
+        <v>585</v>
+      </c>
+      <c r="G970" t="n">
+        <v>171990</v>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:33:53</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY23900CE</t>
+        </is>
+      </c>
+      <c r="C971" t="n">
+        <v>134.95</v>
+      </c>
+      <c r="D971" t="n">
+        <v>135</v>
+      </c>
+      <c r="E971" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F971" t="n">
+        <v>65</v>
+      </c>
+      <c r="G971" t="n">
+        <v>175435</v>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:34:23</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24150PE</t>
+        </is>
+      </c>
+      <c r="C972" t="n">
+        <v>133.1</v>
+      </c>
+      <c r="D972" t="n">
+        <v>135.7</v>
+      </c>
+      <c r="E972" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F972" t="n">
+        <v>3380</v>
+      </c>
+      <c r="G972" t="n">
+        <v>173030</v>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:35:01</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24150PE</t>
+        </is>
+      </c>
+      <c r="C973" t="n">
+        <v>136.4</v>
+      </c>
+      <c r="D973" t="n">
+        <v>137.1</v>
+      </c>
+      <c r="E973" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F973" t="n">
+        <v>910</v>
+      </c>
+      <c r="G973" t="n">
+        <v>177320</v>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:35:22</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24150PE</t>
+        </is>
+      </c>
+      <c r="C974" t="n">
+        <v>138.8</v>
+      </c>
+      <c r="D974" t="n">
+        <v>139.2</v>
+      </c>
+      <c r="E974" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F974" t="n">
+        <v>520</v>
+      </c>
+      <c r="G974" t="n">
+        <v>180440</v>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:35:45</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24150PE</t>
+        </is>
+      </c>
+      <c r="C975" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="D975" t="n">
+        <v>145.05</v>
+      </c>
+      <c r="E975" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F975" t="n">
+        <v>2015</v>
+      </c>
+      <c r="G975" t="n">
+        <v>186550</v>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:36:02</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24150PE</t>
+        </is>
+      </c>
+      <c r="C976" t="n">
+        <v>146.25</v>
+      </c>
+      <c r="D976" t="n">
+        <v>144.7</v>
+      </c>
+      <c r="E976" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F976" t="n">
+        <v>-2015</v>
+      </c>
+      <c r="G976" t="n">
+        <v>190125</v>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:42:44</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24150PE</t>
+        </is>
+      </c>
+      <c r="C977" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="D977" t="n">
+        <v>142.7</v>
+      </c>
+      <c r="E977" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F977" t="n">
+        <v>780</v>
+      </c>
+      <c r="G977" t="n">
+        <v>184730</v>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:43:12</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24150PE</t>
+        </is>
+      </c>
+      <c r="C978" t="n">
+        <v>144.7</v>
+      </c>
+      <c r="D978" t="n">
+        <v>149.1</v>
+      </c>
+      <c r="E978" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F978" t="n">
+        <v>5720</v>
+      </c>
+      <c r="G978" t="n">
+        <v>188110</v>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:43:33</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24150PE</t>
+        </is>
+      </c>
+      <c r="C979" t="n">
+        <v>151.55</v>
+      </c>
+      <c r="D979" t="n">
+        <v>150.35</v>
+      </c>
+      <c r="E979" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F979" t="n">
+        <v>-1560</v>
+      </c>
+      <c r="G979" t="n">
+        <v>197015</v>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:45:12</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24150PE</t>
+        </is>
+      </c>
+      <c r="C980" t="n">
+        <v>142.75</v>
+      </c>
+      <c r="D980" t="n">
+        <v>147.55</v>
+      </c>
+      <c r="E980" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F980" t="n">
+        <v>6240</v>
+      </c>
+      <c r="G980" t="n">
+        <v>185575</v>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:45:45</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24150PE</t>
+        </is>
+      </c>
+      <c r="C981" t="n">
+        <v>149.2</v>
+      </c>
+      <c r="D981" t="n">
+        <v>155.85</v>
+      </c>
+      <c r="E981" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F981" t="n">
+        <v>8645</v>
+      </c>
+      <c r="G981" t="n">
+        <v>193960</v>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:47:04</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24100PE</t>
+        </is>
+      </c>
+      <c r="C982" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="D982" t="n">
+        <v>112.15</v>
+      </c>
+      <c r="E982" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F982" t="n">
+        <v>455</v>
+      </c>
+      <c r="G982" t="n">
+        <v>145340</v>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:48:35</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24100PE</t>
+        </is>
+      </c>
+      <c r="C983" t="n">
+        <v>111.85</v>
+      </c>
+      <c r="D983" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="E983" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F983" t="n">
+        <v>2405</v>
+      </c>
+      <c r="G983" t="n">
+        <v>145405</v>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>2026-05-26 12:50:19</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24100PE</t>
+        </is>
+      </c>
+      <c r="C984" t="n">
+        <v>109.3</v>
+      </c>
+      <c r="D984" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="E984" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F984" t="n">
+        <v>11180</v>
+      </c>
+      <c r="G984" t="n">
+        <v>142090</v>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:58:04</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24050PE</t>
+        </is>
+      </c>
+      <c r="C985" t="n">
+        <v>117.55</v>
+      </c>
+      <c r="D985" t="n">
+        <v>117.8</v>
+      </c>
+      <c r="E985" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F985" t="n">
+        <v>325</v>
+      </c>
+      <c r="G985" t="n">
+        <v>152815</v>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:58:29</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24050PE</t>
+        </is>
+      </c>
+      <c r="C986" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="D986" t="n">
+        <v>119.25</v>
+      </c>
+      <c r="E986" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F986" t="n">
+        <v>7215</v>
+      </c>
+      <c r="G986" t="n">
+        <v>147810</v>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>2026-05-26 13:58:43</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24050PE</t>
+        </is>
+      </c>
+      <c r="C987" t="n">
+        <v>120.25</v>
+      </c>
+      <c r="D987" t="n">
+        <v>120.15</v>
+      </c>
+      <c r="E987" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F987" t="n">
+        <v>-130</v>
+      </c>
+      <c r="G987" t="n">
+        <v>156325</v>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:00:09</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24050PE</t>
+        </is>
+      </c>
+      <c r="C988" t="n">
+        <v>120.25</v>
+      </c>
+      <c r="D988" t="n">
+        <v>120.55</v>
+      </c>
+      <c r="E988" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F988" t="n">
+        <v>390</v>
+      </c>
+      <c r="G988" t="n">
+        <v>156325</v>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:00:39</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24050PE</t>
+        </is>
+      </c>
+      <c r="C989" t="n">
+        <v>120</v>
+      </c>
+      <c r="D989" t="n">
+        <v>120.45</v>
+      </c>
+      <c r="E989" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F989" t="n">
+        <v>585</v>
+      </c>
+      <c r="G989" t="n">
+        <v>156000</v>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:01:17</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24050PE</t>
+        </is>
+      </c>
+      <c r="C990" t="n">
+        <v>129</v>
+      </c>
+      <c r="D990" t="n">
+        <v>128.25</v>
+      </c>
+      <c r="E990" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F990" t="n">
+        <v>-975</v>
+      </c>
+      <c r="G990" t="n">
+        <v>167700</v>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:02:02</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24050PE</t>
+        </is>
+      </c>
+      <c r="C991" t="n">
+        <v>130.45</v>
+      </c>
+      <c r="D991" t="n">
+        <v>132.7</v>
+      </c>
+      <c r="E991" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F991" t="n">
+        <v>2925</v>
+      </c>
+      <c r="G991" t="n">
+        <v>169585</v>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:03:10</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24050PE</t>
+        </is>
+      </c>
+      <c r="C992" t="n">
+        <v>128</v>
+      </c>
+      <c r="D992" t="n">
+        <v>128.65</v>
+      </c>
+      <c r="E992" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F992" t="n">
+        <v>845</v>
+      </c>
+      <c r="G992" t="n">
+        <v>166400</v>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:03:42</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24050PE</t>
+        </is>
+      </c>
+      <c r="C993" t="n">
+        <v>132.55</v>
+      </c>
+      <c r="D993" t="n">
+        <v>133.75</v>
+      </c>
+      <c r="E993" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F993" t="n">
+        <v>1560</v>
+      </c>
+      <c r="G993" t="n">
+        <v>172315</v>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>2026-05-26 14:05:43</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>NIFTY26MAY24050PE</t>
+        </is>
+      </c>
+      <c r="C994" t="n">
+        <v>142.95</v>
+      </c>
+      <c r="D994" t="n">
+        <v>145.1</v>
+      </c>
+      <c r="E994" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F994" t="n">
+        <v>2795</v>
+      </c>
+      <c r="G994" t="n">
+        <v>185835</v>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:11:08</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>SENSEX26MAY76200CE</t>
+        </is>
+      </c>
+      <c r="C995" t="n">
+        <v>118.15</v>
+      </c>
+      <c r="D995" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="E995" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F995" t="n">
+        <v>-9350</v>
+      </c>
+      <c r="G995" t="n">
+        <v>118150</v>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:11:41</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>SENSEX26MAY76100PE</t>
+        </is>
+      </c>
+      <c r="C996" t="n">
+        <v>114.35</v>
+      </c>
+      <c r="D996" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="E996" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F996" t="n">
+        <v>5550</v>
+      </c>
+      <c r="G996" t="n">
+        <v>114350</v>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>2026-05-27 11:13:56</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>SENSEX26MAY76100PE</t>
+        </is>
+      </c>
+      <c r="C997" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="D997" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="E997" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F997" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="G997" t="n">
+        <v>118250</v>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>LIVE</t>
         </is>
       </c>
     </row>

--- a/Lakshmi.xlsx
+++ b/Lakshmi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Lakshmi" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="NSE_Indices_Monitor" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lakshmi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSE_Indices_Monitor" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lakshmi'!$C$1:$H$271</definedName>
@@ -519,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I997"/>
+  <dimension ref="A1:I1239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="24.33203125" customWidth="1" style="1" min="1" max="1"/>
@@ -28773,6 +28773,7600 @@
         </is>
       </c>
       <c r="I997" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>2026-05-29 11:56:36</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>NIFTY2660224000CE</t>
+        </is>
+      </c>
+      <c r="C998" t="n">
+        <v>119.55</v>
+      </c>
+      <c r="D998" t="n">
+        <v>110.55</v>
+      </c>
+      <c r="E998" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F998" t="n">
+        <v>-11700</v>
+      </c>
+      <c r="G998" t="n">
+        <v>155415</v>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>2026-05-29 11:58:20</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>NIFTY2660223900PE</t>
+        </is>
+      </c>
+      <c r="C999" t="n">
+        <v>106</v>
+      </c>
+      <c r="D999" t="n">
+        <v>107</v>
+      </c>
+      <c r="E999" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F999" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G999" t="n">
+        <v>137800</v>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:49:41</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>NIFTY2660223750PE</t>
+        </is>
+      </c>
+      <c r="C1000" t="n">
+        <v>113.65</v>
+      </c>
+      <c r="D1000" t="n">
+        <v>118.45</v>
+      </c>
+      <c r="E1000" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1000" t="n">
+        <v>6240</v>
+      </c>
+      <c r="G1000" t="n">
+        <v>147745</v>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:50:01</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>NIFTY2660223750PE</t>
+        </is>
+      </c>
+      <c r="C1001" t="n">
+        <v>121.05</v>
+      </c>
+      <c r="D1001" t="n">
+        <v>122.85</v>
+      </c>
+      <c r="E1001" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1001" t="n">
+        <v>2340</v>
+      </c>
+      <c r="G1001" t="n">
+        <v>157365</v>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:51:37</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>NIFTY2660223750PE</t>
+        </is>
+      </c>
+      <c r="C1002" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="D1002" t="n">
+        <v>120.45</v>
+      </c>
+      <c r="E1002" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1002" t="n">
+        <v>715</v>
+      </c>
+      <c r="G1002" t="n">
+        <v>155870</v>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:52:27</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>NIFTY2660223750PE</t>
+        </is>
+      </c>
+      <c r="C1003" t="n">
+        <v>123</v>
+      </c>
+      <c r="D1003" t="n">
+        <v>123.3</v>
+      </c>
+      <c r="E1003" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1003" t="n">
+        <v>390</v>
+      </c>
+      <c r="G1003" t="n">
+        <v>159900</v>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:53:00</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>NIFTY2660223750PE</t>
+        </is>
+      </c>
+      <c r="C1004" t="n">
+        <v>123.15</v>
+      </c>
+      <c r="D1004" t="n">
+        <v>123.35</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1004" t="n">
+        <v>260</v>
+      </c>
+      <c r="G1004" t="n">
+        <v>160095</v>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:53:54</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>NIFTY2660223750PE</t>
+        </is>
+      </c>
+      <c r="C1005" t="n">
+        <v>120.65</v>
+      </c>
+      <c r="D1005" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1005" t="n">
+        <v>2145</v>
+      </c>
+      <c r="G1005" t="n">
+        <v>156845</v>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:54:23</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>NIFTY2660223750PE</t>
+        </is>
+      </c>
+      <c r="C1006" t="n">
+        <v>124.8</v>
+      </c>
+      <c r="D1006" t="n">
+        <v>125.35</v>
+      </c>
+      <c r="E1006" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1006" t="n">
+        <v>715</v>
+      </c>
+      <c r="G1006" t="n">
+        <v>162240</v>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>2026-05-29 13:54:39</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>NIFTY2660223750PE</t>
+        </is>
+      </c>
+      <c r="C1007" t="n">
+        <v>125.65</v>
+      </c>
+      <c r="D1007" t="n">
+        <v>126.1</v>
+      </c>
+      <c r="E1007" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>585</v>
+      </c>
+      <c r="G1007" t="n">
+        <v>163345</v>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:04:29</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>NIFTY2660223600CE</t>
+        </is>
+      </c>
+      <c r="C1008" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="D1008" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="E1008" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1008" t="n">
+        <v>910</v>
+      </c>
+      <c r="G1008" t="n">
+        <v>147810</v>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:05:08</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>NIFTY2660223600CE</t>
+        </is>
+      </c>
+      <c r="C1009" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="D1009" t="n">
+        <v>114.45</v>
+      </c>
+      <c r="E1009" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1009" t="n">
+        <v>325</v>
+      </c>
+      <c r="G1009" t="n">
+        <v>148460</v>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:09:00</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>NIFTY2660223600CE</t>
+        </is>
+      </c>
+      <c r="C1010" t="n">
+        <v>117</v>
+      </c>
+      <c r="D1010" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="E1010" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1010" t="n">
+        <v>-1040</v>
+      </c>
+      <c r="G1010" t="n">
+        <v>152100</v>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>2026-06-01 11:09:45</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>NIFTY2660223600CE</t>
+        </is>
+      </c>
+      <c r="C1011" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="D1011" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="E1011" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1011" t="n">
+        <v>4030</v>
+      </c>
+      <c r="G1011" t="n">
+        <v>161330</v>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>2026-06-01 12:58:46</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>NIFTY2660223550PE</t>
+        </is>
+      </c>
+      <c r="C1012" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="D1012" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="E1012" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>130</v>
+      </c>
+      <c r="G1012" t="n">
+        <v>135850</v>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:02:24</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>NIFTY2660223550PE</t>
+        </is>
+      </c>
+      <c r="C1013" t="n">
+        <v>112.45</v>
+      </c>
+      <c r="D1013" t="n">
+        <v>113.05</v>
+      </c>
+      <c r="E1013" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1013" t="n">
+        <v>780</v>
+      </c>
+      <c r="G1013" t="n">
+        <v>146185</v>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:04:17</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>NIFTY2660223550PE</t>
+        </is>
+      </c>
+      <c r="C1014" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="D1014" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="E1014" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1014" t="n">
+        <v>-260</v>
+      </c>
+      <c r="G1014" t="n">
+        <v>150020</v>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>2026-06-01 13:04:57</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>NIFTY2660223550PE</t>
+        </is>
+      </c>
+      <c r="C1015" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="D1015" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="E1015" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1015" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1015" t="n">
+        <v>147030</v>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>2026-06-02 11:55:23</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>NIFTY2660223400PE</t>
+        </is>
+      </c>
+      <c r="C1016" t="n">
+        <v>101</v>
+      </c>
+      <c r="D1016" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="E1016" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1016" t="n">
+        <v>8840</v>
+      </c>
+      <c r="G1016" t="n">
+        <v>131300</v>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>2026-06-02 12:05:57</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>NIFTY2660223400PE</t>
+        </is>
+      </c>
+      <c r="C1017" t="n">
+        <v>121</v>
+      </c>
+      <c r="D1017" t="n">
+        <v>123.35</v>
+      </c>
+      <c r="E1017" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1017" t="n">
+        <v>3055</v>
+      </c>
+      <c r="G1017" t="n">
+        <v>157300</v>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>2026-06-03 01:12:26</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>NIFTY2660923550PE</t>
+        </is>
+      </c>
+      <c r="C1018" t="n">
+        <v>162.6</v>
+      </c>
+      <c r="D1018" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="E1018" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1018" t="n">
+        <v>3900</v>
+      </c>
+      <c r="G1018" t="n">
+        <v>211380</v>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>2026-06-03 01:13:06</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>NIFTY2660923500CE</t>
+        </is>
+      </c>
+      <c r="C1019" t="n">
+        <v>225.45</v>
+      </c>
+      <c r="D1019" t="n">
+        <v>228.45</v>
+      </c>
+      <c r="E1019" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1019" t="n">
+        <v>3900</v>
+      </c>
+      <c r="G1019" t="n">
+        <v>293085</v>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>2026-06-03 01:14:01</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>NIFTY2660923600PE</t>
+        </is>
+      </c>
+      <c r="C1020" t="n">
+        <v>184.45</v>
+      </c>
+      <c r="D1020" t="n">
+        <v>187.45</v>
+      </c>
+      <c r="E1020" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1020" t="n">
+        <v>3900</v>
+      </c>
+      <c r="G1020" t="n">
+        <v>239785</v>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>2026-06-03 01:14:35</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>NIFTY2660923500CE</t>
+        </is>
+      </c>
+      <c r="C1021" t="n">
+        <v>225.45</v>
+      </c>
+      <c r="D1021" t="n">
+        <v>228.45</v>
+      </c>
+      <c r="E1021" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1021" t="n">
+        <v>3900</v>
+      </c>
+      <c r="G1021" t="n">
+        <v>293085</v>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:26:04</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>NIFTY2660923250PE</t>
+        </is>
+      </c>
+      <c r="C1022" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="D1022" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="E1022" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1022" t="n">
+        <v>208845</v>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:33:04</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>SENSEX2660473400PE</t>
+        </is>
+      </c>
+      <c r="C1023" t="n">
+        <v>183.47</v>
+      </c>
+      <c r="D1023" t="n">
+        <v>189.39</v>
+      </c>
+      <c r="E1023" t="n">
+        <v>860</v>
+      </c>
+      <c r="F1023" t="n">
+        <v>5091.2</v>
+      </c>
+      <c r="G1023" t="n">
+        <v>157784.2</v>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:33:53</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>SENSEX2660473400PE</t>
+        </is>
+      </c>
+      <c r="C1024" t="n">
+        <v>195.75</v>
+      </c>
+      <c r="D1024" t="n">
+        <v>196.58</v>
+      </c>
+      <c r="E1024" t="n">
+        <v>860</v>
+      </c>
+      <c r="F1024" t="n">
+        <v>713.8</v>
+      </c>
+      <c r="G1024" t="n">
+        <v>168345</v>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:35:52</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>SENSEX2660473300PE</t>
+        </is>
+      </c>
+      <c r="C1025" t="n">
+        <v>170.34</v>
+      </c>
+      <c r="D1025" t="n">
+        <v>151.13</v>
+      </c>
+      <c r="E1025" t="n">
+        <v>860</v>
+      </c>
+      <c r="F1025" t="n">
+        <v>-16520.6</v>
+      </c>
+      <c r="G1025" t="n">
+        <v>146492.4</v>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:41:48</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>SENSEX2660474400CE</t>
+        </is>
+      </c>
+      <c r="C1026" t="n">
+        <v>166.45</v>
+      </c>
+      <c r="D1026" t="n">
+        <v>166.85</v>
+      </c>
+      <c r="E1026" t="n">
+        <v>860</v>
+      </c>
+      <c r="F1026" t="n">
+        <v>344</v>
+      </c>
+      <c r="G1026" t="n">
+        <v>143147</v>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>2026-06-08 13:41:45</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>NIFTY2660923200PE</t>
+        </is>
+      </c>
+      <c r="C1027" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="D1027" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="E1027" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1027" t="n">
+        <v>1352</v>
+      </c>
+      <c r="G1027" t="n">
+        <v>113984</v>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>2026-06-09 18:58:08</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>NIFTY2661623300PE</t>
+        </is>
+      </c>
+      <c r="C1028" t="n">
+        <v>168.15</v>
+      </c>
+      <c r="D1028" t="n">
+        <v>168.15</v>
+      </c>
+      <c r="E1028" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1028" t="n">
+        <v>174876</v>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1028" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>2026-06-09 18:58:24</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>NIFTY2661623300PE</t>
+        </is>
+      </c>
+      <c r="C1029" t="n">
+        <v>168.15</v>
+      </c>
+      <c r="D1029" t="n">
+        <v>168.15</v>
+      </c>
+      <c r="E1029" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1029" t="n">
+        <v>174876</v>
+      </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>2026-06-10 11:27:30</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>SENSEX2661174800CE</t>
+        </is>
+      </c>
+      <c r="C1030" t="n">
+        <v>173.15</v>
+      </c>
+      <c r="D1030" t="n">
+        <v>191.65</v>
+      </c>
+      <c r="E1030" t="n">
+        <v>320</v>
+      </c>
+      <c r="F1030" t="n">
+        <v>5920</v>
+      </c>
+      <c r="G1030" t="n">
+        <v>55408</v>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>2026-06-10 11:32:00</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>SENSEX2661174700CE</t>
+        </is>
+      </c>
+      <c r="C1031" t="n">
+        <v>220.75</v>
+      </c>
+      <c r="D1031" t="n">
+        <v>220.4</v>
+      </c>
+      <c r="E1031" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1031" t="n">
+        <v>-350</v>
+      </c>
+      <c r="G1031" t="n">
+        <v>220750</v>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>2026-06-10 11:36:05</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>SENSEX2661174800CE</t>
+        </is>
+      </c>
+      <c r="C1032" t="n">
+        <v>184.75</v>
+      </c>
+      <c r="D1032" t="n">
+        <v>185.7</v>
+      </c>
+      <c r="E1032" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1032" t="n">
+        <v>950</v>
+      </c>
+      <c r="G1032" t="n">
+        <v>184750</v>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>2026-06-10 11:59:29</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>SENSEX2661174900CE</t>
+        </is>
+      </c>
+      <c r="C1033" t="n">
+        <v>160.1</v>
+      </c>
+      <c r="D1033" t="n">
+        <v>161.8</v>
+      </c>
+      <c r="E1033" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1033" t="n">
+        <v>1700</v>
+      </c>
+      <c r="G1033" t="n">
+        <v>160100</v>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>2026-06-10 12:02:11</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>SENSEX2661174900CE</t>
+        </is>
+      </c>
+      <c r="C1034" t="n">
+        <v>164.55</v>
+      </c>
+      <c r="D1034" t="n">
+        <v>155.55</v>
+      </c>
+      <c r="E1034" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1034" t="n">
+        <v>-9000</v>
+      </c>
+      <c r="G1034" t="n">
+        <v>164550</v>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>2026-06-10 12:23:39</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>SENSEX2661174900CE</t>
+        </is>
+      </c>
+      <c r="C1035" t="n">
+        <v>149</v>
+      </c>
+      <c r="D1035" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="E1035" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1035" t="n">
+        <v>-9500</v>
+      </c>
+      <c r="G1035" t="n">
+        <v>149000</v>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>2026-06-10 12:24:21</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>SENSEX2661174100PE</t>
+        </is>
+      </c>
+      <c r="C1036" t="n">
+        <v>195.05</v>
+      </c>
+      <c r="D1036" t="n">
+        <v>196.7</v>
+      </c>
+      <c r="E1036" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1036" t="n">
+        <v>1650</v>
+      </c>
+      <c r="G1036" t="n">
+        <v>195050</v>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1036" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>2026-06-10 12:24:53</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>SENSEX2661174100PE</t>
+        </is>
+      </c>
+      <c r="C1037" t="n">
+        <v>200.45</v>
+      </c>
+      <c r="D1037" t="n">
+        <v>200.65</v>
+      </c>
+      <c r="E1037" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1037" t="n">
+        <v>200</v>
+      </c>
+      <c r="G1037" t="n">
+        <v>200450</v>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>2026-06-10 12:26:24</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>SENSEX2661174100PE</t>
+        </is>
+      </c>
+      <c r="C1038" t="n">
+        <v>200.7</v>
+      </c>
+      <c r="D1038" t="n">
+        <v>200.7</v>
+      </c>
+      <c r="E1038" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1038" t="n">
+        <v>200700</v>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>2026-06-10 12:28:15</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>SENSEX2661174100PE</t>
+        </is>
+      </c>
+      <c r="C1039" t="n">
+        <v>203.9</v>
+      </c>
+      <c r="D1039" t="n">
+        <v>194.65</v>
+      </c>
+      <c r="E1039" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1039" t="n">
+        <v>-9250</v>
+      </c>
+      <c r="G1039" t="n">
+        <v>203900</v>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>2026-06-10 12:32:02</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>SENSEX2661174100PE</t>
+        </is>
+      </c>
+      <c r="C1040" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="D1040" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="E1040" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1040" t="n">
+        <v>198900</v>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>2026-06-10 12:33:12</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>SENSEX2661174100PE</t>
+        </is>
+      </c>
+      <c r="C1041" t="n">
+        <v>197.15</v>
+      </c>
+      <c r="D1041" t="n">
+        <v>198.15</v>
+      </c>
+      <c r="E1041" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1041" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G1041" t="n">
+        <v>197150</v>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>2026-06-10 12:33:35</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>SENSEX2661174100PE</t>
+        </is>
+      </c>
+      <c r="C1042" t="n">
+        <v>202</v>
+      </c>
+      <c r="D1042" t="n">
+        <v>202.05</v>
+      </c>
+      <c r="E1042" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1042" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1042" t="n">
+        <v>202000</v>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>2026-06-10 12:35:17</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>SENSEX2661174100PE</t>
+        </is>
+      </c>
+      <c r="C1043" t="n">
+        <v>201.7</v>
+      </c>
+      <c r="D1043" t="n">
+        <v>200.85</v>
+      </c>
+      <c r="E1043" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1043" t="n">
+        <v>-850</v>
+      </c>
+      <c r="G1043" t="n">
+        <v>201700</v>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>2026-06-10 12:37:00</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>SENSEX2661174100PE</t>
+        </is>
+      </c>
+      <c r="C1044" t="n">
+        <v>199.45</v>
+      </c>
+      <c r="D1044" t="n">
+        <v>202</v>
+      </c>
+      <c r="E1044" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1044" t="n">
+        <v>2550</v>
+      </c>
+      <c r="G1044" t="n">
+        <v>199450</v>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>2026-06-10 12:37:57</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>SENSEX2661174100PE</t>
+        </is>
+      </c>
+      <c r="C1045" t="n">
+        <v>208.6</v>
+      </c>
+      <c r="D1045" t="n">
+        <v>197.4</v>
+      </c>
+      <c r="E1045" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F1045" t="n">
+        <v>-11200</v>
+      </c>
+      <c r="G1045" t="n">
+        <v>208600</v>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>2026-06-12 11:38:55</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>NIFTY2661623400CE</t>
+        </is>
+      </c>
+      <c r="C1046" t="n">
+        <v>118.55</v>
+      </c>
+      <c r="D1046" t="n">
+        <v>122.05</v>
+      </c>
+      <c r="E1046" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1046" t="n">
+        <v>4550</v>
+      </c>
+      <c r="G1046" t="n">
+        <v>154115</v>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>2026-06-12 11:41:44</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>NIFTY2661623400CE</t>
+        </is>
+      </c>
+      <c r="C1047" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="D1047" t="n">
+        <v>124</v>
+      </c>
+      <c r="E1047" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1047" t="n">
+        <v>2080</v>
+      </c>
+      <c r="G1047" t="n">
+        <v>159120</v>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>2026-06-12 11:45:38</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>NIFTY2661623400CE</t>
+        </is>
+      </c>
+      <c r="C1048" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="D1048" t="n">
+        <v>119.85</v>
+      </c>
+      <c r="E1048" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1048" t="n">
+        <v>-5655</v>
+      </c>
+      <c r="G1048" t="n">
+        <v>161460</v>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>2026-06-12 11:46:59</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>NIFTY2661623400CE</t>
+        </is>
+      </c>
+      <c r="C1049" t="n">
+        <v>123.45</v>
+      </c>
+      <c r="D1049" t="n">
+        <v>125</v>
+      </c>
+      <c r="E1049" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1049" t="n">
+        <v>2015</v>
+      </c>
+      <c r="G1049" t="n">
+        <v>160485</v>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1049" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>2026-06-12 11:48:37</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>NIFTY2661623400CE</t>
+        </is>
+      </c>
+      <c r="C1050" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="D1050" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="E1050" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1050" t="n">
+        <v>2210</v>
+      </c>
+      <c r="G1050" t="n">
+        <v>165230</v>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1050" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>2026-06-14 20:53:34</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>NIFTY2661623750CE</t>
+        </is>
+      </c>
+      <c r="C1051" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="D1051" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="E1051" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1051" t="n">
+        <v>195</v>
+      </c>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>2026-06-14 21:01:31</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>NIFTY2661623750CE</t>
+        </is>
+      </c>
+      <c r="C1052" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="D1052" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="E1052" t="n">
+        <v>910</v>
+      </c>
+      <c r="F1052" t="n">
+        <v>2730</v>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>2026-06-14 21:04:05</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>NIFTY2661623750CE</t>
+        </is>
+      </c>
+      <c r="C1053" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="D1053" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="E1053" t="n">
+        <v>910</v>
+      </c>
+      <c r="F1053" t="n">
+        <v>2730</v>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>2026-06-14 21:06:38</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>NIFTY2661623750CE</t>
+        </is>
+      </c>
+      <c r="C1054" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="D1054" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="E1054" t="n">
+        <v>910</v>
+      </c>
+      <c r="F1054" t="n">
+        <v>2730</v>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>2026-06-14 21:29:28</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>NIFTY2661623750CE</t>
+        </is>
+      </c>
+      <c r="C1055" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="D1055" t="n">
+        <v>112.15</v>
+      </c>
+      <c r="E1055" t="n">
+        <v>910</v>
+      </c>
+      <c r="F1055" t="n">
+        <v>4550</v>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>2026-06-14 21:45:09</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>NIFTY2661623850CE</t>
+        </is>
+      </c>
+      <c r="C1056" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="D1056" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="E1056" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1056" t="n">
+        <v>195</v>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>2026-06-14 21:49:18</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>NIFTY2661623750CE</t>
+        </is>
+      </c>
+      <c r="C1057" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="D1057" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="E1057" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1057" t="n">
+        <v>195</v>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>2026-06-14 22:29:34</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>NIFTY2661623750CE</t>
+        </is>
+      </c>
+      <c r="C1058" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="D1058" t="n">
+        <v>112.15</v>
+      </c>
+      <c r="E1058" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1058" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2026-06-14 22:32:02</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>NIFTY2661623750CE</t>
+        </is>
+      </c>
+      <c r="C1059" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="D1059" t="n">
+        <v>112.15</v>
+      </c>
+      <c r="E1059" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1059" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>2026-06-14 23:24:11</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>NIFTY2661623750CE</t>
+        </is>
+      </c>
+      <c r="C1060" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="D1060" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="E1060" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1060" t="n">
+        <v>195</v>
+      </c>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>2026-06-14 23:39:39</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>NIFTY2661623650PE</t>
+        </is>
+      </c>
+      <c r="C1061" t="n">
+        <v>137.05</v>
+      </c>
+      <c r="D1061" t="n">
+        <v>140.05</v>
+      </c>
+      <c r="E1061" t="n">
+        <v>2600</v>
+      </c>
+      <c r="F1061" t="n">
+        <v>7800</v>
+      </c>
+      <c r="G1061" t="n">
+        <v>356330</v>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1061" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>2026-06-14 23:43:01</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>NIFTY2661623650PE</t>
+        </is>
+      </c>
+      <c r="C1062" t="n">
+        <v>137.05</v>
+      </c>
+      <c r="D1062" t="n">
+        <v>140.05</v>
+      </c>
+      <c r="E1062" t="n">
+        <v>2600</v>
+      </c>
+      <c r="F1062" t="n">
+        <v>7800</v>
+      </c>
+      <c r="G1062" t="n">
+        <v>356330</v>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1062" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>2026-06-14 23:54:41</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>NIFTY2661623750PE</t>
+        </is>
+      </c>
+      <c r="C1063" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="D1063" t="n">
+        <v>194.9</v>
+      </c>
+      <c r="E1063" t="n">
+        <v>2600</v>
+      </c>
+      <c r="F1063" t="n">
+        <v>7800</v>
+      </c>
+      <c r="G1063" t="n">
+        <v>498940</v>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>MOCK</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>2026-06-15 11:34:17</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>NIFTY2661624000PE</t>
+        </is>
+      </c>
+      <c r="C1064" t="n">
+        <v>118</v>
+      </c>
+      <c r="D1064" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="E1064" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>624</v>
+      </c>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:15:42</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>NIFTY2661623950PE</t>
+        </is>
+      </c>
+      <c r="C1065" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="D1065" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="E1065" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1065" t="n">
+        <v>572</v>
+      </c>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:27:39</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>NIFTY2661623800CE</t>
+        </is>
+      </c>
+      <c r="C1066" t="n">
+        <v>162.8</v>
+      </c>
+      <c r="D1066" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="E1066" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1066" t="n">
+        <v>1144</v>
+      </c>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:34:38</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>NIFTY2661624000PE</t>
+        </is>
+      </c>
+      <c r="C1067" t="n">
+        <v>161.45</v>
+      </c>
+      <c r="D1067" t="n">
+        <v>152.75</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>-9048</v>
+      </c>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:37:14</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>NIFTY2661624050PE</t>
+        </is>
+      </c>
+      <c r="C1068" t="n">
+        <v>180.55</v>
+      </c>
+      <c r="D1068" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="E1068" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>1716</v>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:39:53</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>NIFTY2661623900PE</t>
+        </is>
+      </c>
+      <c r="C1069" t="n">
+        <v>93.45</v>
+      </c>
+      <c r="D1069" t="n">
+        <v>94.65000000000001</v>
+      </c>
+      <c r="E1069" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1069" t="n">
+        <v>1248</v>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:42:49</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>NIFTY2661623900CE</t>
+        </is>
+      </c>
+      <c r="C1070" t="n">
+        <v>102.35</v>
+      </c>
+      <c r="D1070" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="E1070" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>1612</v>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:48:02</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>NIFTY2661623850CE</t>
+        </is>
+      </c>
+      <c r="C1071" t="n">
+        <v>133.05</v>
+      </c>
+      <c r="D1071" t="n">
+        <v>133.4</v>
+      </c>
+      <c r="E1071" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>364</v>
+      </c>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:50:55</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>NIFTY2661623800CE</t>
+        </is>
+      </c>
+      <c r="C1072" t="n">
+        <v>160.65</v>
+      </c>
+      <c r="D1072" t="n">
+        <v>164.25</v>
+      </c>
+      <c r="E1072" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>3744</v>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:53:48</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>NIFTY2661623950PE</t>
+        </is>
+      </c>
+      <c r="C1073" t="n">
+        <v>121.85</v>
+      </c>
+      <c r="D1073" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="E1073" t="n">
+        <v>1040</v>
+      </c>
+      <c r="F1073" t="n">
+        <v>1716</v>
+      </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-06-15 12:56:19</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>NIFTY2661623900CE</t>
+        </is>
+      </c>
+      <c r="C1074" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="D1074" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="E1074" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1074" t="n">
+        <v>1755</v>
+      </c>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:01:53</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>NIFTY2661624050PE</t>
+        </is>
+      </c>
+      <c r="C1075" t="n">
+        <v>188.1</v>
+      </c>
+      <c r="D1075" t="n">
+        <v>192.25</v>
+      </c>
+      <c r="E1075" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1075" t="n">
+        <v>4855.5</v>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:06:29</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>NIFTY2661624000PE</t>
+        </is>
+      </c>
+      <c r="C1076" t="n">
+        <v>154.7</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>155</v>
+      </c>
+      <c r="E1076" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1076" t="n">
+        <v>351</v>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:10:06</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>NIFTY2661623900CE</t>
+        </is>
+      </c>
+      <c r="C1077" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="D1077" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1077" t="n">
+        <v>6376.5</v>
+      </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:14:27</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>NIFTY2661623950CE</t>
+        </is>
+      </c>
+      <c r="C1078" t="n">
+        <v>88.95</v>
+      </c>
+      <c r="D1078" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="E1078" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1078" t="n">
+        <v>234</v>
+      </c>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:17:31</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>NIFTY2661623800CE</t>
+        </is>
+      </c>
+      <c r="C1079" t="n">
+        <v>169</v>
+      </c>
+      <c r="D1079" t="n">
+        <v>175.1</v>
+      </c>
+      <c r="E1079" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1079" t="n">
+        <v>7137</v>
+      </c>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:20:31</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>NIFTY2661623750CE</t>
+        </is>
+      </c>
+      <c r="C1080" t="n">
+        <v>195.9</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>198.55</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1080" t="n">
+        <v>3100.5</v>
+      </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:24:00</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>NIFTY2661623850CE</t>
+        </is>
+      </c>
+      <c r="C1081" t="n">
+        <v>135.05</v>
+      </c>
+      <c r="D1081" t="n">
+        <v>136.25</v>
+      </c>
+      <c r="E1081" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1081" t="n">
+        <v>1404</v>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:27:10</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>NIFTY2661623950PE</t>
+        </is>
+      </c>
+      <c r="C1082" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="D1082" t="n">
+        <v>109.8</v>
+      </c>
+      <c r="E1082" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>-175.5</v>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:34:48</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>NIFTY2661623950PE</t>
+        </is>
+      </c>
+      <c r="C1083" t="n">
+        <v>114.55</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>115.05</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>585</v>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:37:49</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>NIFTY2661624050PE</t>
+        </is>
+      </c>
+      <c r="C1084" t="n">
+        <v>179</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>2047.5</v>
+      </c>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:41:10</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>NIFTY2661623950PE</t>
+        </is>
+      </c>
+      <c r="C1085" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="D1085" t="n">
+        <v>128.15</v>
+      </c>
+      <c r="E1085" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>11173.5</v>
+      </c>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:44:41</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>NIFTY2661624000PE</t>
+        </is>
+      </c>
+      <c r="C1086" t="n">
+        <v>148.25</v>
+      </c>
+      <c r="D1086" t="n">
+        <v>152.45</v>
+      </c>
+      <c r="E1086" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1086" t="n">
+        <v>4914</v>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:52:49</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>NIFTY2661623900PE</t>
+        </is>
+      </c>
+      <c r="C1087" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1087" t="n">
+        <v>1638</v>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:57:00</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>NIFTY2661624000PE</t>
+        </is>
+      </c>
+      <c r="C1088" t="n">
+        <v>155.85</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>146.25</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>-11232</v>
+      </c>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-06-15 13:59:49</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>NIFTY2661623850CE</t>
+        </is>
+      </c>
+      <c r="C1089" t="n">
+        <v>133.7</v>
+      </c>
+      <c r="D1089" t="n">
+        <v>135.15</v>
+      </c>
+      <c r="E1089" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1089" t="n">
+        <v>1696.5</v>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:02:59</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>NIFTY2661623950PE</t>
+        </is>
+      </c>
+      <c r="C1090" t="n">
+        <v>107</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1090" t="n">
+        <v>3217.5</v>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:05:05</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>NIFTY2661624000PE</t>
+        </is>
+      </c>
+      <c r="C1091" t="n">
+        <v>139.05</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>140</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1091" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:07:56</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>NIFTY2661624000PE</t>
+        </is>
+      </c>
+      <c r="C1092" t="n">
+        <v>147.3</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>148.05</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1092" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:11:51</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>NIFTY2661623800CE</t>
+        </is>
+      </c>
+      <c r="C1093" t="n">
+        <v>153.2</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>153.6</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1093" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:18:10</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>NIFTY2661623800CE</t>
+        </is>
+      </c>
+      <c r="C1094" t="n">
+        <v>157</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>156.8</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1094" t="n">
+        <v>-13</v>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:30:23</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>NIFTY2661623900CE</t>
+        </is>
+      </c>
+      <c r="C1095" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>105.55</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1095" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:32:42</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>NIFTY2661624000PE</t>
+        </is>
+      </c>
+      <c r="C1096" t="n">
+        <v>126</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>-11349</v>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:35:19</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>NIFTY2661623800CE</t>
+        </is>
+      </c>
+      <c r="C1097" t="n">
+        <v>184.45</v>
+      </c>
+      <c r="D1097" t="n">
+        <v>188.7</v>
+      </c>
+      <c r="E1097" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1097" t="n">
+        <v>4972.5</v>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:38:18</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>NIFTY2661623950PE</t>
+        </is>
+      </c>
+      <c r="C1098" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="D1098" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="E1098" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:42:15</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>NIFTY2661623900CE</t>
+        </is>
+      </c>
+      <c r="C1099" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="D1099" t="n">
+        <v>104</v>
+      </c>
+      <c r="E1099" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1099" t="n">
+        <v>-10296</v>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:48:48</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>NIFTY2661623900CE</t>
+        </is>
+      </c>
+      <c r="C1100" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="D1100" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="E1100" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>3276</v>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:52:16</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>NIFTY2661623950PE</t>
+        </is>
+      </c>
+      <c r="C1101" t="n">
+        <v>117.45</v>
+      </c>
+      <c r="D1101" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="E1101" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1101" t="n">
+        <v>-10003.5</v>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:55:10</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>NIFTY2661624000PE</t>
+        </is>
+      </c>
+      <c r="C1102" t="n">
+        <v>146.75</v>
+      </c>
+      <c r="D1102" t="n">
+        <v>144.7</v>
+      </c>
+      <c r="E1102" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>-2398.5</v>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:00:05</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>NIFTY2661623950PE</t>
+        </is>
+      </c>
+      <c r="C1103" t="n">
+        <v>124.05</v>
+      </c>
+      <c r="D1103" t="n">
+        <v>115.7</v>
+      </c>
+      <c r="E1103" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>-9769.5</v>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:02:55</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>NIFTY2661624000PE</t>
+        </is>
+      </c>
+      <c r="C1104" t="n">
+        <v>151.35</v>
+      </c>
+      <c r="D1104" t="n">
+        <v>155.55</v>
+      </c>
+      <c r="E1104" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>4914</v>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2026-06-15 15:06:12</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>NIFTY2661623950PE</t>
+        </is>
+      </c>
+      <c r="C1105" t="n">
+        <v>124.75</v>
+      </c>
+      <c r="D1105" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="E1105" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>2026-06-15 19:12:34</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>NIFTY2661623850CE</t>
+        </is>
+      </c>
+      <c r="C1106" t="n">
+        <v>98.84999999999999</v>
+      </c>
+      <c r="D1106" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="E1106" t="n">
+        <v>65</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>195</v>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>2026-06-15 19:13:11</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>NIFTY2661623850CE</t>
+        </is>
+      </c>
+      <c r="C1107" t="n">
+        <v>98.84999999999999</v>
+      </c>
+      <c r="D1107" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="E1107" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>3510</v>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>2026-06-15 19:13:48</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>NIFTY2661623850CE</t>
+        </is>
+      </c>
+      <c r="C1108" t="n">
+        <v>98.84999999999999</v>
+      </c>
+      <c r="D1108" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="E1108" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1108" t="n">
+        <v>3510</v>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>2026-06-15 19:14:38</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>NIFTY2661623850CE</t>
+        </is>
+      </c>
+      <c r="C1109" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="D1109" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="E1109" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1109" t="n">
+        <v>3510</v>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>2026-06-15 19:17:04</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>NIFTY2661623850CE</t>
+        </is>
+      </c>
+      <c r="C1110" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="D1110" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="E1110" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>3510</v>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>2026-06-15 19:18:49</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>NIFTY2661623850CE</t>
+        </is>
+      </c>
+      <c r="C1111" t="n">
+        <v>99.45</v>
+      </c>
+      <c r="D1111" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="E1111" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1111" t="n">
+        <v>3510</v>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:46:43</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>NIFTY2661623850CE</t>
+        </is>
+      </c>
+      <c r="C1112" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="D1112" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="E1112" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1112" t="n">
+        <v>-526.5</v>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:49:12</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>NIFTY2661624050PE</t>
+        </is>
+      </c>
+      <c r="C1113" t="n">
+        <v>132.8</v>
+      </c>
+      <c r="D1113" t="n">
+        <v>133.05</v>
+      </c>
+      <c r="E1113" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1113" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:51:45</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>NIFTY2661624000PE</t>
+        </is>
+      </c>
+      <c r="C1114" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="D1114" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="E1114" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1114" t="n">
+        <v>-819</v>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>2026-06-16 09:54:12</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>NIFTY2661623800CE</t>
+        </is>
+      </c>
+      <c r="C1115" t="n">
+        <v>146.1</v>
+      </c>
+      <c r="D1115" t="n">
+        <v>144</v>
+      </c>
+      <c r="E1115" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1115" t="n">
+        <v>-2457</v>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:00:17</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>NIFTY2661624100PE</t>
+        </is>
+      </c>
+      <c r="C1116" t="n">
+        <v>175.2</v>
+      </c>
+      <c r="D1116" t="n">
+        <v>165.55</v>
+      </c>
+      <c r="E1116" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1116" t="n">
+        <v>-11290.5</v>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:02:36</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>NIFTY2662323750PE</t>
+        </is>
+      </c>
+      <c r="C1117" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="D1117" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="E1117" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1117" t="n">
+        <v>526.5</v>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:07:24</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>NIFTY2662323800PE</t>
+        </is>
+      </c>
+      <c r="C1118" t="n">
+        <v>120.95</v>
+      </c>
+      <c r="D1118" t="n">
+        <v>121.2</v>
+      </c>
+      <c r="E1118" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1118" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:24:35</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>NIFTY2661624050PE</t>
+        </is>
+      </c>
+      <c r="C1119" t="n">
+        <v>126.65</v>
+      </c>
+      <c r="D1119" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="E1119" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1119" t="n">
+        <v>-1111.5</v>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:28:11</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>NIFTY2662323900PE</t>
+        </is>
+      </c>
+      <c r="C1120" t="n">
+        <v>155.95</v>
+      </c>
+      <c r="D1120" t="n">
+        <v>154.8</v>
+      </c>
+      <c r="E1120" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1120" t="n">
+        <v>-1345.5</v>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:42:26</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>NIFTY2662323950CE</t>
+        </is>
+      </c>
+      <c r="C1121" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="D1121" t="n">
+        <v>170.8</v>
+      </c>
+      <c r="E1121" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1121" t="n">
+        <v>-10062</v>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:51:56</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>NIFTY2661624050PE</t>
+        </is>
+      </c>
+      <c r="C1122" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="D1122" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="E1122" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1122" t="n">
+        <v>1170</v>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:56:55</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>NIFTY2661624050PE</t>
+        </is>
+      </c>
+      <c r="C1123" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="D1123" t="n">
+        <v>101.95</v>
+      </c>
+      <c r="E1123" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1123" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>2026-06-16 10:59:18</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>NIFTY2661624050PE</t>
+        </is>
+      </c>
+      <c r="C1124" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="D1124" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="E1124" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1124" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:04:56</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>NIFTY2661623850CE</t>
+        </is>
+      </c>
+      <c r="C1125" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="D1125" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="E1125" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1125" t="n">
+        <v>-9945</v>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:07:38</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>NIFTY2661623850CE</t>
+        </is>
+      </c>
+      <c r="C1126" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="D1126" t="n">
+        <v>107.95</v>
+      </c>
+      <c r="E1126" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1126" t="n">
+        <v>585</v>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:13:01</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>NIFTY2661624050PE</t>
+        </is>
+      </c>
+      <c r="C1127" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="D1127" t="n">
+        <v>126.7</v>
+      </c>
+      <c r="E1127" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1127" t="n">
+        <v>1170</v>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:17:59</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>NIFTY2661624100PE</t>
+        </is>
+      </c>
+      <c r="C1128" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="D1128" t="n">
+        <v>169.7</v>
+      </c>
+      <c r="E1128" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1128" t="n">
+        <v>234</v>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:27:00</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>NIFTY2661624050PE</t>
+        </is>
+      </c>
+      <c r="C1129" t="n">
+        <v>122.25</v>
+      </c>
+      <c r="D1129" t="n">
+        <v>125.55</v>
+      </c>
+      <c r="E1129" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1129" t="n">
+        <v>3861</v>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:29:54</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>NIFTY2661623800CE</t>
+        </is>
+      </c>
+      <c r="C1130" t="n">
+        <v>131</v>
+      </c>
+      <c r="D1130" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="E1130" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1130" t="n">
+        <v>-585</v>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:34:56</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>NIFTY2661624050PE</t>
+        </is>
+      </c>
+      <c r="C1131" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="D1131" t="n">
+        <v>126.4</v>
+      </c>
+      <c r="E1131" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1131" t="n">
+        <v>-9828</v>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:38:39</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>NIFTY2661624000PE</t>
+        </is>
+      </c>
+      <c r="C1132" t="n">
+        <v>95</v>
+      </c>
+      <c r="D1132" t="n">
+        <v>97.34999999999999</v>
+      </c>
+      <c r="E1132" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1132" t="n">
+        <v>2749.5</v>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:41:51</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>NIFTY2661623750CE</t>
+        </is>
+      </c>
+      <c r="C1133" t="n">
+        <v>168.75</v>
+      </c>
+      <c r="D1133" t="n">
+        <v>170.9</v>
+      </c>
+      <c r="E1133" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1133" t="n">
+        <v>2515.5</v>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:45:34</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>NIFTY2661623750CE</t>
+        </is>
+      </c>
+      <c r="C1134" t="n">
+        <v>174.85</v>
+      </c>
+      <c r="D1134" t="n">
+        <v>175.75</v>
+      </c>
+      <c r="E1134" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1134" t="n">
+        <v>1053</v>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:49:24</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>NIFTY2661624050PE</t>
+        </is>
+      </c>
+      <c r="C1135" t="n">
+        <v>129.05</v>
+      </c>
+      <c r="D1135" t="n">
+        <v>133.9</v>
+      </c>
+      <c r="E1135" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1135" t="n">
+        <v>5674.5</v>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:52:07</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>NIFTY2661624050PE</t>
+        </is>
+      </c>
+      <c r="C1136" t="n">
+        <v>128.85</v>
+      </c>
+      <c r="D1136" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="E1136" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1136" t="n">
+        <v>-10588.5</v>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>2026-06-16 11:59:00</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>NIFTY2662323950CE</t>
+        </is>
+      </c>
+      <c r="C1137" t="n">
+        <v>160.65</v>
+      </c>
+      <c r="D1137" t="n">
+        <v>162.75</v>
+      </c>
+      <c r="E1137" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1137" t="n">
+        <v>2457</v>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>2026-06-16 12:01:43</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>NIFTY2662323900CE</t>
+        </is>
+      </c>
+      <c r="C1138" t="n">
+        <v>189.1</v>
+      </c>
+      <c r="D1138" t="n">
+        <v>189.45</v>
+      </c>
+      <c r="E1138" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1138" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>2026-06-16 12:18:18</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>NIFTY2662323800PE</t>
+        </is>
+      </c>
+      <c r="C1139" t="n">
+        <v>119.65</v>
+      </c>
+      <c r="D1139" t="n">
+        <v>119.7</v>
+      </c>
+      <c r="E1139" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1139" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>2026-06-16 12:23:08</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>NIFTY2662323900PE</t>
+        </is>
+      </c>
+      <c r="C1140" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="D1140" t="n">
+        <v>163.75</v>
+      </c>
+      <c r="E1140" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1140" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>2026-06-16 12:29:25</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>NIFTY2662324050CE</t>
+        </is>
+      </c>
+      <c r="C1141" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="D1141" t="n">
+        <v>118.35</v>
+      </c>
+      <c r="E1141" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1141" t="n">
+        <v>-292.5</v>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>2026-06-16 12:32:08</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>NIFTY2662323900PE</t>
+        </is>
+      </c>
+      <c r="C1142" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="D1142" t="n">
+        <v>154</v>
+      </c>
+      <c r="E1142" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1142" t="n">
+        <v>1755</v>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>2026-06-16 12:53:49</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>NIFTY2662323950PE</t>
+        </is>
+      </c>
+      <c r="C1143" t="n">
+        <v>185</v>
+      </c>
+      <c r="D1143" t="n">
+        <v>185.65</v>
+      </c>
+      <c r="E1143" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1143" t="n">
+        <v>760.5</v>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:02:19</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>NIFTY2662323800PE</t>
+        </is>
+      </c>
+      <c r="C1144" t="n">
+        <v>112.45</v>
+      </c>
+      <c r="D1144" t="n">
+        <v>114.15</v>
+      </c>
+      <c r="E1144" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1144" t="n">
+        <v>1989</v>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:13:46</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>NIFTY2662323900PE</t>
+        </is>
+      </c>
+      <c r="C1145" t="n">
+        <v>146.75</v>
+      </c>
+      <c r="D1145" t="n">
+        <v>147.05</v>
+      </c>
+      <c r="E1145" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1145" t="n">
+        <v>351</v>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:17:02</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>NIFTY2662324000CE</t>
+        </is>
+      </c>
+      <c r="C1146" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="D1146" t="n">
+        <v>142.2</v>
+      </c>
+      <c r="E1146" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1146" t="n">
+        <v>-351</v>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:22:14</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>NIFTY2662323900PE</t>
+        </is>
+      </c>
+      <c r="C1147" t="n">
+        <v>151.2</v>
+      </c>
+      <c r="D1147" t="n">
+        <v>142.2</v>
+      </c>
+      <c r="E1147" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1147" t="n">
+        <v>-10530</v>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:28:19</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>NIFTY2662323900PE</t>
+        </is>
+      </c>
+      <c r="C1148" t="n">
+        <v>140.7</v>
+      </c>
+      <c r="D1148" t="n">
+        <v>140</v>
+      </c>
+      <c r="E1148" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1148" t="n">
+        <v>-819</v>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:32:05</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>NIFTY2662323850PE</t>
+        </is>
+      </c>
+      <c r="C1149" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="D1149" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="E1149" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1149" t="n">
+        <v>1755</v>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:37:08</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100CE</t>
+        </is>
+      </c>
+      <c r="C1150" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="D1150" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="E1150" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1150" t="n">
+        <v>1521</v>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:44:28</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>NIFTY2662323950CE</t>
+        </is>
+      </c>
+      <c r="C1151" t="n">
+        <v>172.55</v>
+      </c>
+      <c r="D1151" t="n">
+        <v>172.25</v>
+      </c>
+      <c r="E1151" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1151" t="n">
+        <v>-351</v>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>2026-06-16 13:57:14</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>NIFTY2662323950PE</t>
+        </is>
+      </c>
+      <c r="C1152" t="n">
+        <v>166.1</v>
+      </c>
+      <c r="D1152" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="E1152" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1152" t="n">
+        <v>-9360</v>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>2026-06-16 14:04:15</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100CE</t>
+        </is>
+      </c>
+      <c r="C1153" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="D1153" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="E1153" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1153" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>2026-06-17 10:09:13</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100CE</t>
+        </is>
+      </c>
+      <c r="C1154" t="n">
+        <v>137.1</v>
+      </c>
+      <c r="D1154" t="n">
+        <v>144.75</v>
+      </c>
+      <c r="E1154" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1154" t="n">
+        <v>8950.5</v>
+      </c>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>2026-06-17 10:13:14</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>NIFTY2662324000CE</t>
+        </is>
+      </c>
+      <c r="C1155" t="n">
+        <v>197.95</v>
+      </c>
+      <c r="D1155" t="n">
+        <v>189.75</v>
+      </c>
+      <c r="E1155" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1155" t="n">
+        <v>-9594</v>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>2026-06-17 10:20:12</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>NIFTY2662324000PE</t>
+        </is>
+      </c>
+      <c r="C1156" t="n">
+        <v>143.35</v>
+      </c>
+      <c r="D1156" t="n">
+        <v>135.35</v>
+      </c>
+      <c r="E1156" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1156" t="n">
+        <v>-9360</v>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>2026-06-17 10:27:44</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>NIFTY2662323950PE</t>
+        </is>
+      </c>
+      <c r="C1157" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="D1157" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="E1157" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1157" t="n">
+        <v>-351</v>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>2026-06-17 10:34:32</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>NIFTY2662324200CE</t>
+        </is>
+      </c>
+      <c r="C1158" t="n">
+        <v>104</v>
+      </c>
+      <c r="D1158" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="E1158" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1158" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>2026-06-17 10:53:53</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100PE</t>
+        </is>
+      </c>
+      <c r="C1159" t="n">
+        <v>181.1</v>
+      </c>
+      <c r="D1159" t="n">
+        <v>181.7</v>
+      </c>
+      <c r="E1159" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1159" t="n">
+        <v>702</v>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>2026-06-17 10:57:19</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>NIFTY2662323900PE</t>
+        </is>
+      </c>
+      <c r="C1160" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="D1160" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="E1160" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1160" t="n">
+        <v>234</v>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:01:49</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>NIFTY2662324050PE</t>
+        </is>
+      </c>
+      <c r="C1161" t="n">
+        <v>157.7</v>
+      </c>
+      <c r="D1161" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="E1161" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1161" t="n">
+        <v>3276</v>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:04:46</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>NIFTY2662324000PE</t>
+        </is>
+      </c>
+      <c r="C1162" t="n">
+        <v>137.65</v>
+      </c>
+      <c r="D1162" t="n">
+        <v>138</v>
+      </c>
+      <c r="E1162" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1162" t="n">
+        <v>409.5</v>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:08:28</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>NIFTY2662324200CE</t>
+        </is>
+      </c>
+      <c r="C1163" t="n">
+        <v>103</v>
+      </c>
+      <c r="D1163" t="n">
+        <v>100</v>
+      </c>
+      <c r="E1163" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1163" t="n">
+        <v>-3510</v>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:11:54</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>NIFTY2662324000PE</t>
+        </is>
+      </c>
+      <c r="C1164" t="n">
+        <v>139.2</v>
+      </c>
+      <c r="D1164" t="n">
+        <v>139.45</v>
+      </c>
+      <c r="E1164" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1164" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:15:05</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100CE</t>
+        </is>
+      </c>
+      <c r="C1165" t="n">
+        <v>144</v>
+      </c>
+      <c r="D1165" t="n">
+        <v>144.75</v>
+      </c>
+      <c r="E1165" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1165" t="n">
+        <v>877.5</v>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:19:51</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100CE</t>
+        </is>
+      </c>
+      <c r="C1166" t="n">
+        <v>146.65</v>
+      </c>
+      <c r="D1166" t="n">
+        <v>147.85</v>
+      </c>
+      <c r="E1166" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1166" t="n">
+        <v>1404</v>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:25:55</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>NIFTY2662323950PE</t>
+        </is>
+      </c>
+      <c r="C1167" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="D1167" t="n">
+        <v>114.15</v>
+      </c>
+      <c r="E1167" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1167" t="n">
+        <v>2223</v>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:32:00</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>NIFTY2662324200CE</t>
+        </is>
+      </c>
+      <c r="C1168" t="n">
+        <v>102.85</v>
+      </c>
+      <c r="D1168" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="E1168" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1168" t="n">
+        <v>5674.5</v>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:35:36</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>NIFTY2662324050PE</t>
+        </is>
+      </c>
+      <c r="C1169" t="n">
+        <v>150.1</v>
+      </c>
+      <c r="D1169" t="n">
+        <v>151</v>
+      </c>
+      <c r="E1169" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1169" t="n">
+        <v>1053</v>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:40:37</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>NIFTY2662323950PE</t>
+        </is>
+      </c>
+      <c r="C1170" t="n">
+        <v>115.7</v>
+      </c>
+      <c r="D1170" t="n">
+        <v>118</v>
+      </c>
+      <c r="E1170" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1170" t="n">
+        <v>2691</v>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:47:47</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>NIFTY2662324050CE</t>
+        </is>
+      </c>
+      <c r="C1171" t="n">
+        <v>170.05</v>
+      </c>
+      <c r="D1171" t="n">
+        <v>165.3</v>
+      </c>
+      <c r="E1171" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1171" t="n">
+        <v>-5557.5</v>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:50:44</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>NIFTY2662324000CE</t>
+        </is>
+      </c>
+      <c r="C1172" t="n">
+        <v>191.35</v>
+      </c>
+      <c r="D1172" t="n">
+        <v>191</v>
+      </c>
+      <c r="E1172" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1172" t="n">
+        <v>-409.5</v>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:53:53</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>NIFTY2662323900PE</t>
+        </is>
+      </c>
+      <c r="C1173" t="n">
+        <v>99</v>
+      </c>
+      <c r="D1173" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="E1173" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1173" t="n">
+        <v>468</v>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>2026-06-17 11:58:19</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>NIFTY2662324000PE</t>
+        </is>
+      </c>
+      <c r="C1174" t="n">
+        <v>138.95</v>
+      </c>
+      <c r="D1174" t="n">
+        <v>140.45</v>
+      </c>
+      <c r="E1174" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1174" t="n">
+        <v>1755</v>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:04:23</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>NIFTY2662324000PE</t>
+        </is>
+      </c>
+      <c r="C1175" t="n">
+        <v>145.95</v>
+      </c>
+      <c r="D1175" t="n">
+        <v>141.1</v>
+      </c>
+      <c r="E1175" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1175" t="n">
+        <v>-5674.5</v>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:08:18</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>NIFTY2662324050CE</t>
+        </is>
+      </c>
+      <c r="C1176" t="n">
+        <v>158.55</v>
+      </c>
+      <c r="D1176" t="n">
+        <v>159.05</v>
+      </c>
+      <c r="E1176" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1176" t="n">
+        <v>585</v>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:12:08</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>NIFTY2662323900PE</t>
+        </is>
+      </c>
+      <c r="C1177" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="D1177" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="E1177" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1177" t="n">
+        <v>702</v>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:16:37</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>NIFTY2662324150CE</t>
+        </is>
+      </c>
+      <c r="C1178" t="n">
+        <v>113</v>
+      </c>
+      <c r="D1178" t="n">
+        <v>110</v>
+      </c>
+      <c r="E1178" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1178" t="n">
+        <v>-3510</v>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:24:53</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>NIFTY2662324050PE</t>
+        </is>
+      </c>
+      <c r="C1179" t="n">
+        <v>168.45</v>
+      </c>
+      <c r="D1179" t="n">
+        <v>169.7</v>
+      </c>
+      <c r="E1179" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1179" t="n">
+        <v>1462.5</v>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:28:42</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>NIFTY2662324000CE</t>
+        </is>
+      </c>
+      <c r="C1180" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="D1180" t="n">
+        <v>177.6</v>
+      </c>
+      <c r="E1180" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1180" t="n">
+        <v>4797</v>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:31:34</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100PE</t>
+        </is>
+      </c>
+      <c r="C1181" t="n">
+        <v>198.8</v>
+      </c>
+      <c r="D1181" t="n">
+        <v>197.95</v>
+      </c>
+      <c r="E1181" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1181" t="n">
+        <v>-994.5</v>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:37:16</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>NIFTY2662324000PE</t>
+        </is>
+      </c>
+      <c r="C1182" t="n">
+        <v>145.7</v>
+      </c>
+      <c r="D1182" t="n">
+        <v>146.9</v>
+      </c>
+      <c r="E1182" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1182" t="n">
+        <v>1404</v>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:41:52</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>NIFTY2662324150CE</t>
+        </is>
+      </c>
+      <c r="C1183" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="D1183" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="E1183" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1183" t="n">
+        <v>3159</v>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>2026-06-17 12:45:49</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100PE</t>
+        </is>
+      </c>
+      <c r="C1184" t="n">
+        <v>193.4</v>
+      </c>
+      <c r="D1184" t="n">
+        <v>190.1</v>
+      </c>
+      <c r="E1184" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1184" t="n">
+        <v>-3861</v>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>2026-06-17 13:00:33</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>NIFTY2662324050PE</t>
+        </is>
+      </c>
+      <c r="C1185" t="n">
+        <v>175.45</v>
+      </c>
+      <c r="D1185" t="n">
+        <v>175.75</v>
+      </c>
+      <c r="E1185" t="n">
+        <v>2925</v>
+      </c>
+      <c r="F1185" t="n">
+        <v>877.5</v>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>2026-06-17 13:04:18</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>NIFTY2662324000CE</t>
+        </is>
+      </c>
+      <c r="C1186" t="n">
+        <v>173.5</v>
+      </c>
+      <c r="D1186" t="n">
+        <v>173.45</v>
+      </c>
+      <c r="E1186" t="n">
+        <v>2925</v>
+      </c>
+      <c r="F1186" t="n">
+        <v>-146.25</v>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>2026-06-17 13:07:27</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>NIFTY2662323900PE</t>
+        </is>
+      </c>
+      <c r="C1187" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="D1187" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="E1187" t="n">
+        <v>2925</v>
+      </c>
+      <c r="F1187" t="n">
+        <v>2047.5</v>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>2026-06-17 13:14:06</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>NIFTY2662324000PE</t>
+        </is>
+      </c>
+      <c r="C1188" t="n">
+        <v>154.05</v>
+      </c>
+      <c r="D1188" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1188" t="n">
+        <v>526.5</v>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>2026-06-17 13:17:16</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>NIFTY2662324150CE</t>
+        </is>
+      </c>
+      <c r="C1189" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="D1189" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="E1189" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1189" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>2026-06-17 13:30:59</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>NIFTY2662323950CE</t>
+        </is>
+      </c>
+      <c r="C1190" t="n">
+        <v>201.55</v>
+      </c>
+      <c r="D1190" t="n">
+        <v>202</v>
+      </c>
+      <c r="E1190" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1190" t="n">
+        <v>585</v>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>2026-06-17 13:35:58</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>NIFTY2662323900PE</t>
+        </is>
+      </c>
+      <c r="C1191" t="n">
+        <v>102</v>
+      </c>
+      <c r="D1191" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="E1191" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1191" t="n">
+        <v>-10790</v>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>2026-06-17 13:40:15</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>NIFTY2662324050PE</t>
+        </is>
+      </c>
+      <c r="C1192" t="n">
+        <v>154.95</v>
+      </c>
+      <c r="D1192" t="n">
+        <v>155.75</v>
+      </c>
+      <c r="E1192" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1192" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>2026-06-17 13:51:44</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>NIFTY2662323950PE</t>
+        </is>
+      </c>
+      <c r="C1193" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="D1193" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="E1193" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1193" t="n">
+        <v>5720</v>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>2026-06-17 13:54:42</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100PE</t>
+        </is>
+      </c>
+      <c r="C1194" t="n">
+        <v>189.6</v>
+      </c>
+      <c r="D1194" t="n">
+        <v>190.4</v>
+      </c>
+      <c r="E1194" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1194" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>2026-06-17 14:09:40</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>NIFTY2662324050CE</t>
+        </is>
+      </c>
+      <c r="C1195" t="n">
+        <v>154.4</v>
+      </c>
+      <c r="D1195" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="E1195" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1195" t="n">
+        <v>-11570</v>
+      </c>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>2026-06-17 14:12:45</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>NIFTY2662324000CE</t>
+        </is>
+      </c>
+      <c r="C1196" t="n">
+        <v>169.65</v>
+      </c>
+      <c r="D1196" t="n">
+        <v>171.2</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1196" t="n">
+        <v>2015</v>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>2026-06-17 14:17:11</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>NIFTY2662323900PE</t>
+        </is>
+      </c>
+      <c r="C1197" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="D1197" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1197" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>2026-06-17 14:20:22</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>NIFTY2662323900PE</t>
+        </is>
+      </c>
+      <c r="C1198" t="n">
+        <v>98.05</v>
+      </c>
+      <c r="D1198" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="E1198" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1198" t="n">
+        <v>715</v>
+      </c>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>2026-06-17 14:24:44</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>NIFTY2662324000CE</t>
+        </is>
+      </c>
+      <c r="C1199" t="n">
+        <v>171.4</v>
+      </c>
+      <c r="D1199" t="n">
+        <v>172</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1199" t="n">
+        <v>780</v>
+      </c>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>2026-06-17 14:29:26</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>NIFTY2662324150CE</t>
+        </is>
+      </c>
+      <c r="C1200" t="n">
+        <v>98.15000000000001</v>
+      </c>
+      <c r="D1200" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1200" t="n">
+        <v>455</v>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>2026-06-17 14:37:38</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100CE</t>
+        </is>
+      </c>
+      <c r="C1201" t="n">
+        <v>121.25</v>
+      </c>
+      <c r="D1201" t="n">
+        <v>121.75</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>650</v>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>2026-06-17 14:46:40</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>NIFTY2662324150CE</t>
+        </is>
+      </c>
+      <c r="C1202" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="D1202" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="E1202" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1202" t="n">
+        <v>195</v>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>2026-06-17 14:54:30</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>NIFTY2662324150CE</t>
+        </is>
+      </c>
+      <c r="C1203" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>1690</v>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>2026-06-17 14:58:08</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100CE</t>
+        </is>
+      </c>
+      <c r="C1204" t="n">
+        <v>127.7</v>
+      </c>
+      <c r="D1204" t="n">
+        <v>132.1</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>5720</v>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>2026-06-18 09:38:08</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100CE</t>
+        </is>
+      </c>
+      <c r="C1205" t="n">
+        <v>115.45</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>115.65</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>234</v>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>2026-06-18 09:42:28</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>NIFTY2662324000CE</t>
+        </is>
+      </c>
+      <c r="C1206" t="n">
+        <v>185</v>
+      </c>
+      <c r="D1206" t="n">
+        <v>187.25</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1206" t="n">
+        <v>2632.5</v>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>2026-06-18 09:47:12</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100PE</t>
+        </is>
+      </c>
+      <c r="C1207" t="n">
+        <v>131.05</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>122.35</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1207" t="n">
+        <v>-10179</v>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>2026-06-18 09:53:51</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>NIFTY2662324200CE</t>
+        </is>
+      </c>
+      <c r="C1208" t="n">
+        <v>94.75</v>
+      </c>
+      <c r="D1208" t="n">
+        <v>95.84999999999999</v>
+      </c>
+      <c r="E1208" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1208" t="n">
+        <v>1287</v>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>2026-06-18 09:59:03</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>NIFTY2662324050PE</t>
+        </is>
+      </c>
+      <c r="C1209" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="D1209" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="E1209" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1209" t="n">
+        <v>234</v>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:02:37</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>NIFTY2662324050PE</t>
+        </is>
+      </c>
+      <c r="C1210" t="n">
+        <v>101.85</v>
+      </c>
+      <c r="D1210" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="E1210" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1210" t="n">
+        <v>994.5</v>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:10:28</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>NIFTY2662324150CE</t>
+        </is>
+      </c>
+      <c r="C1211" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="D1211" t="n">
+        <v>112.35</v>
+      </c>
+      <c r="E1211" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1211" t="n">
+        <v>3451.5</v>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:18:18</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>NIFTY2662324050PE</t>
+        </is>
+      </c>
+      <c r="C1212" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="D1212" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="E1212" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1212" t="n">
+        <v>3217.5</v>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:28:18</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100PE</t>
+        </is>
+      </c>
+      <c r="C1213" t="n">
+        <v>129.85</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1213" t="n">
+        <v>760.5</v>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:35:08</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>NIFTY2662324150PE</t>
+        </is>
+      </c>
+      <c r="C1214" t="n">
+        <v>161.4</v>
+      </c>
+      <c r="D1214" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="E1214" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1214" t="n">
+        <v>-9711</v>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:40:09</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>NIFTY2662324150PE</t>
+        </is>
+      </c>
+      <c r="C1215" t="n">
+        <v>165.25</v>
+      </c>
+      <c r="D1215" t="n">
+        <v>177.1</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1215" t="n">
+        <v>13864.5</v>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:44:38</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>NIFTY2662324000PE</t>
+        </is>
+      </c>
+      <c r="C1216" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="D1216" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="E1216" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1216" t="n">
+        <v>1287</v>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:48:01</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>NIFTY2662324150PE</t>
+        </is>
+      </c>
+      <c r="C1217" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="D1217" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="E1217" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1217" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:51:27</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100PE</t>
+        </is>
+      </c>
+      <c r="C1218" t="n">
+        <v>154.95</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>146.6</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1218" t="n">
+        <v>-9769.5</v>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:55:10</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>NIFTY2662324050CE</t>
+        </is>
+      </c>
+      <c r="C1219" t="n">
+        <v>137.15</v>
+      </c>
+      <c r="D1219" t="n">
+        <v>137.45</v>
+      </c>
+      <c r="E1219" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1219" t="n">
+        <v>351</v>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:06:25</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>NIFTY2662324000PE</t>
+        </is>
+      </c>
+      <c r="C1220" t="n">
+        <v>99.55</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1220" t="n">
+        <v>643.5</v>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:15:21</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>NIFTY2662324150PE</t>
+        </is>
+      </c>
+      <c r="C1221" t="n">
+        <v>188.9</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>190.5</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1221" t="n">
+        <v>1872</v>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:20:00</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>NIFTY2662324050PE</t>
+        </is>
+      </c>
+      <c r="C1222" t="n">
+        <v>141.9</v>
+      </c>
+      <c r="D1222" t="n">
+        <v>142.75</v>
+      </c>
+      <c r="E1222" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1222" t="n">
+        <v>994.5</v>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:24:07</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>NIFTY2662324000CE</t>
+        </is>
+      </c>
+      <c r="C1223" t="n">
+        <v>149.1</v>
+      </c>
+      <c r="D1223" t="n">
+        <v>150.55</v>
+      </c>
+      <c r="E1223" t="n">
+        <v>1170</v>
+      </c>
+      <c r="F1223" t="n">
+        <v>1696.5</v>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>MOMENTUM_BOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:32:56</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100CE</t>
+        </is>
+      </c>
+      <c r="C1224" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="D1224" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="E1224" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1224" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1224" t="n">
+        <v>132860</v>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1224" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:33:36</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100CE</t>
+        </is>
+      </c>
+      <c r="C1225" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="D1225" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="E1225" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1225" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1225" t="n">
+        <v>134940</v>
+      </c>
+      <c r="H1225" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1225" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:36:55</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100CE</t>
+        </is>
+      </c>
+      <c r="C1226" t="n">
+        <v>103.95</v>
+      </c>
+      <c r="D1226" t="n">
+        <v>105.45</v>
+      </c>
+      <c r="E1226" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1226" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1226" t="n">
+        <v>135135</v>
+      </c>
+      <c r="H1226" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1226" t="inlineStr">
+        <is>
+          <t>PAPER</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:39:55</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100CE</t>
+        </is>
+      </c>
+      <c r="C1227" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1227" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1227" t="n">
+        <v>131885</v>
+      </c>
+      <c r="H1227" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1227" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:42:09</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100CE</t>
+        </is>
+      </c>
+      <c r="C1228" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="D1228" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="E1228" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1228" t="n">
+        <v>1690</v>
+      </c>
+      <c r="G1228" t="n">
+        <v>131950</v>
+      </c>
+      <c r="H1228" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1228" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:44:30</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100CE</t>
+        </is>
+      </c>
+      <c r="C1229" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>105.15</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1229" t="n">
+        <v>134745</v>
+      </c>
+      <c r="H1229" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1229" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>2026-06-18 11:51:03</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100CE</t>
+        </is>
+      </c>
+      <c r="C1230" t="n">
+        <v>106</v>
+      </c>
+      <c r="D1230" t="n">
+        <v>102</v>
+      </c>
+      <c r="E1230" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1230" t="n">
+        <v>-5200</v>
+      </c>
+      <c r="G1230" t="n">
+        <v>137800</v>
+      </c>
+      <c r="H1230" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I1230" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>2026-06-18 12:15:52</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>NIFTY2662324050PE</t>
+        </is>
+      </c>
+      <c r="C1231" t="n">
+        <v>115.35</v>
+      </c>
+      <c r="D1231" t="n">
+        <v>116.85</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1231" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1231" t="n">
+        <v>149955</v>
+      </c>
+      <c r="H1231" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1231" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>2026-06-18 12:18:47</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>NIFTY2662324050PE</t>
+        </is>
+      </c>
+      <c r="C1232" t="n">
+        <v>115.9</v>
+      </c>
+      <c r="D1232" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="E1232" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1232" t="n">
+        <v>-6890</v>
+      </c>
+      <c r="G1232" t="n">
+        <v>150670</v>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I1232" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>2026-06-18 12:26:04</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100CE</t>
+        </is>
+      </c>
+      <c r="C1233" t="n">
+        <v>117.65</v>
+      </c>
+      <c r="D1233" t="n">
+        <v>119.15</v>
+      </c>
+      <c r="E1233" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1233" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1233" t="n">
+        <v>152945</v>
+      </c>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1233" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>2026-06-18 12:26:49</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100CE</t>
+        </is>
+      </c>
+      <c r="C1234" t="n">
+        <v>116.65</v>
+      </c>
+      <c r="D1234" t="n">
+        <v>118.15</v>
+      </c>
+      <c r="E1234" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1234" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1234" t="n">
+        <v>151645</v>
+      </c>
+      <c r="H1234" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1234" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>2026-06-18 12:27:44</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>NIFTY2662324100CE</t>
+        </is>
+      </c>
+      <c r="C1235" t="n">
+        <v>119.15</v>
+      </c>
+      <c r="D1235" t="n">
+        <v>120.65</v>
+      </c>
+      <c r="E1235" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1235" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1235" t="n">
+        <v>154895</v>
+      </c>
+      <c r="H1235" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1235" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>2026-06-18 12:28:52</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>NIFTY2662324150CE</t>
+        </is>
+      </c>
+      <c r="C1236" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="D1236" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="E1236" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1236" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1236" t="n">
+        <v>129740</v>
+      </c>
+      <c r="H1236" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1236" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>2026-06-18 12:29:41</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>NIFTY2662324150CE</t>
+        </is>
+      </c>
+      <c r="C1237" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="D1237" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="E1237" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1237" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G1237" t="n">
+        <v>133640</v>
+      </c>
+      <c r="H1237" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1237" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>2026-06-18 12:30:49</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>NIFTY2662324150CE</t>
+        </is>
+      </c>
+      <c r="C1238" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="D1238" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="E1238" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1238" t="n">
+        <v>-6305</v>
+      </c>
+      <c r="G1238" t="n">
+        <v>142220</v>
+      </c>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="I1238" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>2026-06-18 13:07:58</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>NIFTY2662324150CE</t>
+        </is>
+      </c>
+      <c r="C1239" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="D1239" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="E1239" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F1239" t="n">
+        <v>4550</v>
+      </c>
+      <c r="G1239" t="n">
+        <v>136370</v>
+      </c>
+      <c r="H1239" t="inlineStr">
+        <is>
+          <t>PROFIT</t>
+        </is>
+      </c>
+      <c r="I1239" t="inlineStr">
         <is>
           <t>LIVE</t>
         </is>
